--- a/src/data/FML-Data.xlsx
+++ b/src/data/FML-Data.xlsx
@@ -931,7 +931,7 @@
         <v>Amey</v>
       </c>
       <c r="C6">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -942,7 +942,7 @@
         <v>Mala</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -953,7 +953,7 @@
         <v>Siddharth</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -964,7 +964,7 @@
         <v>Supriya</v>
       </c>
       <c r="C9">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -1604,7 +1604,7 @@
         <v>Home - News</v>
       </c>
       <c r="D41" t="str">
-        <v>done</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="42">
@@ -1618,7 +1618,7 @@
         <v>Home - Videos</v>
       </c>
       <c r="D42" t="str">
-        <v>done</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="43">
@@ -1632,7 +1632,7 @@
         <v>Points Table</v>
       </c>
       <c r="D43" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="44">
@@ -1646,7 +1646,7 @@
         <v>Stats</v>
       </c>
       <c r="D44" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="45">
@@ -1660,7 +1660,7 @@
         <v>Showcase</v>
       </c>
       <c r="D45" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="46">
@@ -1702,7 +1702,7 @@
         <v>Home - Fixtures</v>
       </c>
       <c r="D48" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="49">
@@ -1716,7 +1716,7 @@
         <v>Header &amp; Footer, Sponsors</v>
       </c>
       <c r="D49" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="50">
@@ -1730,7 +1730,7 @@
         <v>Home - Players</v>
       </c>
       <c r="D50" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="51">
@@ -1744,7 +1744,7 @@
         <v>FREE Due Blocker</v>
       </c>
       <c r="D51" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="52">
@@ -1758,7 +1758,7 @@
         <v>Wf fixses</v>
       </c>
       <c r="D52" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="53">
@@ -1800,7 +1800,7 @@
         <v>player Profile</v>
       </c>
       <c r="D55" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="56">
@@ -1814,7 +1814,7 @@
         <v>Fixses</v>
       </c>
       <c r="D56" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="57">
@@ -1828,7 +1828,7 @@
         <v>Support</v>
       </c>
       <c r="D57" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="58">
@@ -1842,7 +1842,7 @@
         <v>GO Live</v>
       </c>
       <c r="D58" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="59">
@@ -1856,7 +1856,7 @@
         <v>Top Menu, Bottom Menu</v>
       </c>
       <c r="D59" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="60">
@@ -1870,7 +1870,7 @@
         <v>Footer</v>
       </c>
       <c r="D60" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="61">
@@ -1884,7 +1884,7 @@
         <v>Both Standings css</v>
       </c>
       <c r="D61" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="62">
@@ -1898,7 +1898,7 @@
         <v>HP News</v>
       </c>
       <c r="D62" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="63">
@@ -1912,7 +1912,7 @@
         <v>HP Videos</v>
       </c>
       <c r="D63" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="64">
@@ -1926,7 +1926,7 @@
         <v>HP Photos</v>
       </c>
       <c r="D64" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="65">
@@ -1940,7 +1940,7 @@
         <v>News Listing &amp; Detail</v>
       </c>
       <c r="D65" t="str">
-        <v>done</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="66">
@@ -1954,7 +1954,7 @@
         <v>Video Listing and Detail</v>
       </c>
       <c r="D66" t="str">
-        <v>done</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="67">
@@ -1968,7 +1968,7 @@
         <v>Photos Listing &amp; Detail</v>
       </c>
       <c r="D67" t="str">
-        <v>done</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="68">
@@ -1996,7 +1996,7 @@
         <v>Privacy Policy</v>
       </c>
       <c r="D69" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="70">
@@ -2010,7 +2010,7 @@
         <v>Thank you</v>
       </c>
       <c r="D70" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="71">
@@ -2024,7 +2024,7 @@
         <v>404</v>
       </c>
       <c r="D71" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="72">
@@ -2038,7 +2038,7 @@
         <v>Partnership Framework</v>
       </c>
       <c r="D72" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="73">
@@ -2052,7 +2052,7 @@
         <v>Where to Watch</v>
       </c>
       <c r="D73" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="74">
@@ -2066,7 +2066,7 @@
         <v>Womens t20 exhibition</v>
       </c>
       <c r="D74" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="75">
@@ -2080,7 +2080,7 @@
         <v>Wallpapers</v>
       </c>
       <c r="D75" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="76">
@@ -2122,7 +2122,7 @@
         <v>Boundary Builder page + form</v>
       </c>
       <c r="D78" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="79">
@@ -2136,7 +2136,7 @@
         <v>Unit testing fixses of all form</v>
       </c>
       <c r="D79" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="80">
@@ -2150,7 +2150,7 @@
         <v>Videos - Listing</v>
       </c>
       <c r="D80" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="81">
@@ -2164,7 +2164,7 @@
         <v>Photos - Listing</v>
       </c>
       <c r="D81" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="82">
@@ -2178,7 +2178,7 @@
         <v>News - Listing</v>
       </c>
       <c r="D82" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="83">
@@ -2192,7 +2192,7 @@
         <v>Photos - Detail</v>
       </c>
       <c r="D83" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="84">
@@ -2206,7 +2206,7 @@
         <v>News - Detail</v>
       </c>
       <c r="D84" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="85">
@@ -2220,7 +2220,7 @@
         <v>Videos - Detail</v>
       </c>
       <c r="D85" t="str">
-        <v>inprogress</v>
+        <v>done</v>
       </c>
     </row>
     <row r="86">
@@ -2234,7 +2234,7 @@
         <v>Showcase</v>
       </c>
       <c r="D86" t="str">
-        <v>inprogress</v>
+        <v>pending</v>
       </c>
     </row>
     <row r="87">

--- a/src/data/FML-Data.xlsx
+++ b/src/data/FML-Data.xlsx
@@ -488,88 +488,88 @@
     <t>Home - News</t>
   </si>
   <si>
+    <t>FNS-101</t>
+  </si>
+  <si>
+    <t>Home - Videos</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>FNS-51</t>
+  </si>
+  <si>
+    <t>Points Table</t>
+  </si>
+  <si>
+    <t>FNS-49</t>
+  </si>
+  <si>
+    <t>Stats</t>
+  </si>
+  <si>
+    <t>FNS-6</t>
+  </si>
+  <si>
+    <t>Showcase</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>FNS-13</t>
+  </si>
+  <si>
+    <t>Home - shop</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>FNS-41</t>
+  </si>
+  <si>
+    <t>Schedule</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>FNS-8</t>
+  </si>
+  <si>
+    <t>Home - Fixtures</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>FNS-5</t>
+  </si>
+  <si>
+    <t>Header &amp; Footer, Sponsors</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>FNS-12</t>
+  </si>
+  <si>
+    <t>Home - Players</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>FREE Due Blocker</t>
+  </si>
+  <si>
     <t>pending</t>
-  </si>
-  <si>
-    <t>FNS-101</t>
-  </si>
-  <si>
-    <t>Home - Videos</t>
-  </si>
-  <si>
-    <t>2026-08-11</t>
-  </si>
-  <si>
-    <t>FNS-51</t>
-  </si>
-  <si>
-    <t>Points Table</t>
-  </si>
-  <si>
-    <t>FNS-49</t>
-  </si>
-  <si>
-    <t>Stats</t>
-  </si>
-  <si>
-    <t>FNS-6</t>
-  </si>
-  <si>
-    <t>Showcase</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>FNS-13</t>
-  </si>
-  <si>
-    <t>Home - shop</t>
-  </si>
-  <si>
-    <t>2026-08-13</t>
-  </si>
-  <si>
-    <t>FNS-41</t>
-  </si>
-  <si>
-    <t>Schedule</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>FNS-8</t>
-  </si>
-  <si>
-    <t>Home - Fixtures</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>FNS-5</t>
-  </si>
-  <si>
-    <t>Header &amp; Footer, Sponsors</t>
-  </si>
-  <si>
-    <t>2026-08-17</t>
-  </si>
-  <si>
-    <t>FNS-12</t>
-  </si>
-  <si>
-    <t>Home - Players</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-08-19</t>
-  </si>
-  <si>
-    <t>FREE Due Blocker</t>
   </si>
   <si>
     <t>Wf fixses</t>
@@ -1535,7 +1535,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1871,7 +1871,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2036,7 +2036,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2046,7 +2046,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3109,7 +3109,7 @@
         <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H28" t="s">
         <v>39</v>
@@ -4495,206 +4495,206 @@
         <v>75</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="4:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="8">
     <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid date" error="Please enter a valid date." sqref="A10:A264">
@@ -4791,7 +4791,7 @@
     <hyperlink ref="D64" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <tableParts count="1">
     <tablePart r:id="rId63"/>
   </tableParts>
@@ -4869,7 +4869,7 @@
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="H2" t="s">
         <v>39</v>
@@ -4898,16 +4898,16 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E3" t="s">
         <v>157</v>
       </c>
-      <c r="E3" t="s">
-        <v>158</v>
-      </c>
       <c r="F3" t="s">
         <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="H3" t="s">
         <v>39</v>
@@ -4927,7 +4927,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -4936,10 +4936,10 @@
         <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" t="s">
         <v>160</v>
-      </c>
-      <c r="E4" t="s">
-        <v>161</v>
       </c>
       <c r="F4" t="s">
         <v>39</v>
@@ -4951,10 +4951,10 @@
         <v>39</v>
       </c>
       <c r="I4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -4965,7 +4965,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -4974,25 +4974,25 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" t="s">
         <v>162</v>
       </c>
-      <c r="E5" t="s">
-        <v>163</v>
-      </c>
       <c r="F5" t="s">
         <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="H5" t="s">
         <v>39</v>
       </c>
       <c r="I5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K5" t="s">
         <v>39</v>
@@ -5003,7 +5003,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -5012,25 +5012,25 @@
         <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E6" t="s">
         <v>164</v>
       </c>
-      <c r="E6" t="s">
-        <v>165</v>
-      </c>
       <c r="F6" t="s">
         <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H6" t="s">
         <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K6" t="s">
         <v>39</v>
@@ -5041,7 +5041,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -5050,36 +5050,36 @@
         <v>40</v>
       </c>
       <c r="D7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E7" t="s">
         <v>167</v>
       </c>
-      <c r="E7" t="s">
-        <v>168</v>
-      </c>
       <c r="F7" t="s">
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
         <v>39</v>
       </c>
       <c r="I7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K7" t="s">
         <v>39</v>
       </c>
       <c r="L7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
@@ -5088,10 +5088,10 @@
         <v>40</v>
       </c>
       <c r="D8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E8" t="s">
         <v>170</v>
-      </c>
-      <c r="E8" t="s">
-        <v>171</v>
       </c>
       <c r="F8" t="s">
         <v>39</v>
@@ -5103,10 +5103,10 @@
         <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K8" t="s">
         <v>39</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
@@ -5126,25 +5126,25 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E9" t="s">
         <v>173</v>
       </c>
-      <c r="E9" t="s">
-        <v>174</v>
-      </c>
       <c r="F9" t="s">
         <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H9" t="s">
         <v>39</v>
       </c>
       <c r="I9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K9" t="s">
         <v>39</v>
@@ -5155,7 +5155,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
@@ -5164,25 +5164,25 @@
         <v>40</v>
       </c>
       <c r="D10" t="s">
+        <v>175</v>
+      </c>
+      <c r="E10" t="s">
         <v>176</v>
       </c>
-      <c r="E10" t="s">
-        <v>177</v>
-      </c>
       <c r="F10" t="s">
         <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s">
         <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K10" t="s">
         <v>39</v>
@@ -5193,7 +5193,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -5202,22 +5202,22 @@
         <v>40</v>
       </c>
       <c r="D11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" t="s">
         <v>179</v>
       </c>
-      <c r="E11" t="s">
-        <v>180</v>
-      </c>
       <c r="F11" t="s">
         <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H11" t="s">
         <v>39</v>
       </c>
       <c r="I11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J11" t="s">
         <v>38</v>
@@ -5231,7 +5231,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -5240,22 +5240,22 @@
         <v>40</v>
       </c>
       <c r="D12" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" t="s">
         <v>179</v>
       </c>
-      <c r="E12" t="s">
-        <v>180</v>
-      </c>
       <c r="F12" t="s">
         <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H12" t="s">
         <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J12" t="s">
         <v>38</v>
@@ -5269,7 +5269,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
@@ -5281,22 +5281,22 @@
         <v>39</v>
       </c>
       <c r="E13" t="s">
+        <v>182</v>
+      </c>
+      <c r="F13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" t="s">
         <v>183</v>
       </c>
-      <c r="F13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>156</v>
-      </c>
       <c r="H13" t="s">
         <v>39</v>
       </c>
       <c r="I13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K13" t="s">
         <v>39</v>
@@ -5325,7 +5325,7 @@
         <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H14" t="s">
         <v>39</v>
@@ -5354,22 +5354,22 @@
         <v>40</v>
       </c>
       <c r="D15" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" t="s">
         <v>179</v>
       </c>
-      <c r="E15" t="s">
-        <v>180</v>
-      </c>
       <c r="F15" t="s">
         <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H15" t="s">
         <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J15" t="s">
         <v>38</v>
@@ -5392,10 +5392,10 @@
         <v>40</v>
       </c>
       <c r="D16" t="s">
+        <v>169</v>
+      </c>
+      <c r="E16" t="s">
         <v>170</v>
-      </c>
-      <c r="E16" t="s">
-        <v>171</v>
       </c>
       <c r="F16" t="s">
         <v>39</v>
@@ -5407,10 +5407,10 @@
         <v>39</v>
       </c>
       <c r="I16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K16" t="s">
         <v>39</v>
@@ -5506,10 +5506,10 @@
         <v>40</v>
       </c>
       <c r="D19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E19" t="s">
         <v>170</v>
-      </c>
-      <c r="E19" t="s">
-        <v>171</v>
       </c>
       <c r="F19" t="s">
         <v>39</v>
@@ -5521,10 +5521,10 @@
         <v>39</v>
       </c>
       <c r="I19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K19" t="s">
         <v>39</v>
@@ -5535,7 +5535,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
@@ -5544,10 +5544,10 @@
         <v>40</v>
       </c>
       <c r="D20" t="s">
+        <v>169</v>
+      </c>
+      <c r="E20" t="s">
         <v>170</v>
-      </c>
-      <c r="E20" t="s">
-        <v>171</v>
       </c>
       <c r="F20" t="s">
         <v>39</v>
@@ -5559,10 +5559,10 @@
         <v>39</v>
       </c>
       <c r="I20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K20" t="s">
         <v>39</v>
@@ -5573,7 +5573,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B21" t="s">
         <v>2</v>
@@ -5597,10 +5597,10 @@
         <v>39</v>
       </c>
       <c r="I21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K21" t="s">
         <v>39</v>
@@ -5629,7 +5629,7 @@
         <v>39</v>
       </c>
       <c r="G22" t="s">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="H22" t="s">
         <v>39</v>
@@ -5667,7 +5667,7 @@
         <v>39</v>
       </c>
       <c r="G23" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H23" t="s">
         <v>39</v>
@@ -5705,7 +5705,7 @@
         <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H24" t="s">
         <v>39</v>
@@ -5743,7 +5743,7 @@
         <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H25" t="s">
         <v>39</v>
@@ -5781,7 +5781,7 @@
         <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H26" t="s">
         <v>39</v>
@@ -5819,7 +5819,7 @@
         <v>39</v>
       </c>
       <c r="G27" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H27" t="s">
         <v>39</v>
@@ -5857,7 +5857,7 @@
         <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H28" t="s">
         <v>39</v>
@@ -5895,7 +5895,7 @@
         <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H29" t="s">
         <v>39</v>
@@ -5933,7 +5933,7 @@
         <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H30" t="s">
         <v>39</v>
@@ -6047,7 +6047,7 @@
         <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H33" t="s">
         <v>39</v>
@@ -6085,7 +6085,7 @@
         <v>39</v>
       </c>
       <c r="G34" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H34" t="s">
         <v>39</v>
@@ -6123,7 +6123,7 @@
         <v>39</v>
       </c>
       <c r="G35" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H35" t="s">
         <v>39</v>
@@ -6161,7 +6161,7 @@
         <v>39</v>
       </c>
       <c r="G36" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H36" t="s">
         <v>39</v>
@@ -6199,7 +6199,7 @@
         <v>39</v>
       </c>
       <c r="G37" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H37" t="s">
         <v>39</v>
@@ -6237,7 +6237,7 @@
         <v>39</v>
       </c>
       <c r="G38" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H38" t="s">
         <v>39</v>
@@ -6257,7 +6257,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
@@ -6275,16 +6275,16 @@
         <v>39</v>
       </c>
       <c r="G39" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H39" t="s">
         <v>39</v>
       </c>
       <c r="I39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K39" t="s">
         <v>39</v>
@@ -6295,7 +6295,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
@@ -6313,16 +6313,16 @@
         <v>39</v>
       </c>
       <c r="G40" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H40" t="s">
         <v>39</v>
       </c>
       <c r="I40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K40" t="s">
         <v>39</v>
@@ -6351,7 +6351,7 @@
         <v>39</v>
       </c>
       <c r="G41" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H41" t="s">
         <v>39</v>
@@ -6389,7 +6389,7 @@
         <v>39</v>
       </c>
       <c r="G42" t="s">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="H42" t="s">
         <v>39</v>
@@ -6427,7 +6427,7 @@
         <v>39</v>
       </c>
       <c r="G43" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H43" t="s">
         <v>39</v>
@@ -6465,7 +6465,7 @@
         <v>39</v>
       </c>
       <c r="G44" t="s">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="H44" t="s">
         <v>39</v>
@@ -6541,7 +6541,7 @@
         <v>39</v>
       </c>
       <c r="G46" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H46" t="s">
         <v>39</v>
@@ -6617,7 +6617,7 @@
         <v>39</v>
       </c>
       <c r="G48" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H48" t="s">
         <v>39</v>
@@ -6637,7 +6637,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
@@ -6655,16 +6655,16 @@
         <v>39</v>
       </c>
       <c r="G49" t="s">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="H49" t="s">
         <v>39</v>
       </c>
       <c r="I49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K49" t="s">
         <v>39</v>
@@ -6693,7 +6693,7 @@
         <v>39</v>
       </c>
       <c r="G50" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H50" t="s">
         <v>39</v>
@@ -6713,7 +6713,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
@@ -6731,16 +6731,16 @@
         <v>39</v>
       </c>
       <c r="G51" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H51" t="s">
         <v>39</v>
       </c>
       <c r="I51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K51" t="s">
         <v>39</v>
@@ -6751,7 +6751,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
@@ -6769,16 +6769,16 @@
         <v>39</v>
       </c>
       <c r="G52" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H52" t="s">
         <v>39</v>
       </c>
       <c r="I52" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K52" t="s">
         <v>39</v>
@@ -6789,7 +6789,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
@@ -6807,16 +6807,16 @@
         <v>39</v>
       </c>
       <c r="G53" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H53" t="s">
         <v>39</v>
       </c>
       <c r="I53" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J53" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K53" t="s">
         <v>39</v>
@@ -6827,7 +6827,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
@@ -6845,16 +6845,16 @@
         <v>39</v>
       </c>
       <c r="G54" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H54" t="s">
         <v>39</v>
       </c>
       <c r="I54" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J54" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K54" t="s">
         <v>39</v>
@@ -6865,7 +6865,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
@@ -6883,16 +6883,16 @@
         <v>39</v>
       </c>
       <c r="G55" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H55" t="s">
         <v>39</v>
       </c>
       <c r="I55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K55" t="s">
         <v>39</v>
@@ -6921,7 +6921,7 @@
         <v>39</v>
       </c>
       <c r="G56" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H56" t="s">
         <v>39</v>
@@ -6959,7 +6959,7 @@
         <v>39</v>
       </c>
       <c r="G57" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H57" t="s">
         <v>39</v>
@@ -6997,7 +6997,7 @@
         <v>39</v>
       </c>
       <c r="G58" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H58" t="s">
         <v>39</v>
@@ -7029,7 +7029,7 @@
         <v>39</v>
       </c>
       <c r="E59" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F59" t="s">
         <v>39</v>
@@ -7093,7 +7093,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B61" t="s">
         <v>10</v>
@@ -7167,206 +7167,206 @@
         <v>39</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="4:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="8">
     <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid date" error="Please enter a valid date." sqref="A10:A262">
@@ -7443,7 +7443,7 @@
     <hyperlink ref="D62" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <tableParts count="1">
     <tablePart r:id="rId43"/>
   </tableParts>
@@ -7521,7 +7521,7 @@
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H2" t="s">
         <v>39</v>
@@ -7559,7 +7559,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H3" t="s">
         <v>39</v>
@@ -7597,7 +7597,7 @@
         <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H4" t="s">
         <v>39</v>
@@ -7635,7 +7635,7 @@
         <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H5" t="s">
         <v>39</v>
@@ -7673,7 +7673,7 @@
         <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H6" t="s">
         <v>39</v>
@@ -7711,7 +7711,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H7" t="s">
         <v>39</v>
@@ -7749,7 +7749,7 @@
         <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H8" t="s">
         <v>39</v>
@@ -7787,7 +7787,7 @@
         <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H9" t="s">
         <v>39</v>
@@ -7825,7 +7825,7 @@
         <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H10" t="s">
         <v>39</v>
@@ -7863,7 +7863,7 @@
         <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H11" t="s">
         <v>39</v>
@@ -7901,7 +7901,7 @@
         <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H12" t="s">
         <v>39</v>
@@ -7939,7 +7939,7 @@
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H13" t="s">
         <v>39</v>
@@ -7977,7 +7977,7 @@
         <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H14" t="s">
         <v>39</v>
@@ -8015,7 +8015,7 @@
         <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H15" t="s">
         <v>39</v>
@@ -8053,7 +8053,7 @@
         <v>39</v>
       </c>
       <c r="G16" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H16" t="s">
         <v>39</v>
@@ -8091,7 +8091,7 @@
         <v>39</v>
       </c>
       <c r="G17" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H17" t="s">
         <v>39</v>
@@ -8129,7 +8129,7 @@
         <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H18" t="s">
         <v>39</v>
@@ -8167,7 +8167,7 @@
         <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H19" t="s">
         <v>39</v>
@@ -8205,7 +8205,7 @@
         <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H20" t="s">
         <v>39</v>
@@ -8243,7 +8243,7 @@
         <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H21" t="s">
         <v>39</v>
@@ -8281,7 +8281,7 @@
         <v>39</v>
       </c>
       <c r="G22" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H22" t="s">
         <v>39</v>
@@ -8319,7 +8319,7 @@
         <v>39</v>
       </c>
       <c r="G23" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H23" t="s">
         <v>39</v>
@@ -8357,7 +8357,7 @@
         <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H24" t="s">
         <v>39</v>
@@ -8395,7 +8395,7 @@
         <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H25" t="s">
         <v>39</v>
@@ -8433,7 +8433,7 @@
         <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H26" t="s">
         <v>39</v>
@@ -8471,7 +8471,7 @@
         <v>39</v>
       </c>
       <c r="G27" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H27" t="s">
         <v>39</v>
@@ -8509,7 +8509,7 @@
         <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H28" t="s">
         <v>39</v>
@@ -8547,7 +8547,7 @@
         <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H29" t="s">
         <v>39</v>
@@ -8585,7 +8585,7 @@
         <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H30" t="s">
         <v>39</v>
@@ -8623,7 +8623,7 @@
         <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H31" t="s">
         <v>39</v>
@@ -8661,7 +8661,7 @@
         <v>39</v>
       </c>
       <c r="G32" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H32" t="s">
         <v>39</v>
@@ -8699,7 +8699,7 @@
         <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H33" t="s">
         <v>39</v>
@@ -8737,7 +8737,7 @@
         <v>39</v>
       </c>
       <c r="G34" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H34" t="s">
         <v>39</v>
@@ -8775,7 +8775,7 @@
         <v>39</v>
       </c>
       <c r="G35" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H35" t="s">
         <v>39</v>
@@ -8813,7 +8813,7 @@
         <v>39</v>
       </c>
       <c r="G36" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H36" t="s">
         <v>39</v>
@@ -8851,7 +8851,7 @@
         <v>39</v>
       </c>
       <c r="G37" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H37" t="s">
         <v>39</v>
@@ -8889,7 +8889,7 @@
         <v>39</v>
       </c>
       <c r="G38" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H38" t="s">
         <v>39</v>
@@ -8927,7 +8927,7 @@
         <v>39</v>
       </c>
       <c r="G39" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H39" t="s">
         <v>39</v>
@@ -8945,206 +8945,206 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="4:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="8">
     <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid date" error="Please enter a valid date." sqref="A10:A239">
@@ -9177,7 +9177,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -9255,7 +9255,7 @@
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H2" t="s">
         <v>39</v>
@@ -9293,7 +9293,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H3" t="s">
         <v>39</v>
@@ -9331,7 +9331,7 @@
         <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H4" t="s">
         <v>39</v>
@@ -9369,7 +9369,7 @@
         <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H5" t="s">
         <v>39</v>
@@ -9407,7 +9407,7 @@
         <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H6" t="s">
         <v>39</v>
@@ -9445,7 +9445,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H7" t="s">
         <v>39</v>
@@ -9483,7 +9483,7 @@
         <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H8" t="s">
         <v>39</v>
@@ -9556,7 +9556,7 @@
         <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H10" t="s">
         <v>39</v>
@@ -9588,13 +9588,13 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F11" t="s">
         <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H11" t="s">
         <v>39</v>
@@ -9632,7 +9632,7 @@
         <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H12" t="s">
         <v>39</v>
@@ -9670,7 +9670,7 @@
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H13" t="s">
         <v>39</v>
@@ -9708,7 +9708,7 @@
         <v>-0.5</v>
       </c>
       <c r="G14" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H14" t="s">
         <v>39</v>
@@ -9746,7 +9746,7 @@
         <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H15" t="s">
         <v>39</v>
@@ -9784,7 +9784,7 @@
         <v>39</v>
       </c>
       <c r="G16" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H16" t="s">
         <v>39</v>
@@ -9822,7 +9822,7 @@
         <v>-0.5</v>
       </c>
       <c r="G17" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H17" t="s">
         <v>39</v>
@@ -9860,7 +9860,7 @@
         <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H18" t="s">
         <v>39</v>
@@ -9898,7 +9898,7 @@
         <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H19" t="s">
         <v>39</v>
@@ -9936,7 +9936,7 @@
         <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H20" t="s">
         <v>39</v>
@@ -9974,7 +9974,7 @@
         <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H21" t="s">
         <v>39</v>
@@ -10012,7 +10012,7 @@
         <v>39</v>
       </c>
       <c r="G22" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H22" t="s">
         <v>39</v>
@@ -10050,7 +10050,7 @@
         <v>-6</v>
       </c>
       <c r="G23" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H23" t="s">
         <v>39</v>
@@ -10088,7 +10088,7 @@
         <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H24" t="s">
         <v>39</v>
@@ -10126,7 +10126,7 @@
         <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H25" t="s">
         <v>39</v>
@@ -10164,7 +10164,7 @@
         <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H26" t="s">
         <v>39</v>
@@ -10202,7 +10202,7 @@
         <v>39</v>
       </c>
       <c r="G27" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H27" t="s">
         <v>39</v>
@@ -10240,7 +10240,7 @@
         <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H28" t="s">
         <v>39</v>
@@ -10278,7 +10278,7 @@
         <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H29" t="s">
         <v>39</v>
@@ -10316,7 +10316,7 @@
         <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H30" t="s">
         <v>39</v>
@@ -10354,7 +10354,7 @@
         <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H31" t="s">
         <v>39</v>
@@ -10392,7 +10392,7 @@
         <v>39</v>
       </c>
       <c r="G32" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H32" t="s">
         <v>39</v>
@@ -10430,7 +10430,7 @@
         <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H33" t="s">
         <v>39</v>
@@ -10468,7 +10468,7 @@
         <v>-4</v>
       </c>
       <c r="G34" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H34" t="s">
         <v>39</v>
@@ -10506,7 +10506,7 @@
         <v>-4</v>
       </c>
       <c r="G35" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H35" t="s">
         <v>39</v>
@@ -10544,7 +10544,7 @@
         <v>-2</v>
       </c>
       <c r="G36" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H36" t="s">
         <v>39</v>
@@ -10582,7 +10582,7 @@
         <v>-2</v>
       </c>
       <c r="G37" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H37" t="s">
         <v>39</v>
@@ -10620,7 +10620,7 @@
         <v>-2</v>
       </c>
       <c r="G38" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H38" t="s">
         <v>39</v>
@@ -10658,7 +10658,7 @@
         <v>-4</v>
       </c>
       <c r="G39" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H39" t="s">
         <v>39</v>
@@ -10696,7 +10696,7 @@
         <v>-2</v>
       </c>
       <c r="G40" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H40" t="s">
         <v>39</v>
@@ -10734,7 +10734,7 @@
         <v>-2</v>
       </c>
       <c r="G41" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H41" t="s">
         <v>39</v>
@@ -10772,7 +10772,7 @@
         <v>-4</v>
       </c>
       <c r="G42" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H42" t="s">
         <v>39</v>
@@ -10810,7 +10810,7 @@
         <v>39</v>
       </c>
       <c r="G43" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H43" t="s">
         <v>39</v>
@@ -10848,7 +10848,7 @@
         <v>39</v>
       </c>
       <c r="G44" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H44" t="s">
         <v>39</v>
@@ -10886,7 +10886,7 @@
         <v>39</v>
       </c>
       <c r="G45" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H45" t="s">
         <v>39</v>
@@ -10924,7 +10924,7 @@
         <v>39</v>
       </c>
       <c r="G46" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H46" t="s">
         <v>39</v>
@@ -10962,7 +10962,7 @@
         <v>39</v>
       </c>
       <c r="G47" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H47" t="s">
         <v>39</v>
@@ -11000,7 +11000,7 @@
         <v>39</v>
       </c>
       <c r="G48" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H48" t="s">
         <v>39</v>
@@ -11038,7 +11038,7 @@
         <v>39</v>
       </c>
       <c r="G49" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H49" t="s">
         <v>39</v>
@@ -11076,7 +11076,7 @@
         <v>39</v>
       </c>
       <c r="G50" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H50" t="s">
         <v>39</v>
@@ -11114,7 +11114,7 @@
         <v>39</v>
       </c>
       <c r="G51" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H51" t="s">
         <v>39</v>
@@ -11152,7 +11152,7 @@
         <v>39</v>
       </c>
       <c r="G52" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="H52" t="s">
         <v>39</v>
@@ -11170,206 +11170,206 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="4:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="8">
     <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid date" error="Please enter a valid date." sqref="A10:A252">
@@ -11402,7 +11402,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/src/data/FML-Data.xlsx
+++ b/src/data/FML-Data.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2705" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2813" uniqueCount="320">
   <si>
     <t>Name</t>
   </si>
@@ -224,6 +224,9 @@
     <t>Actual end date</t>
   </si>
   <si>
+    <t>JiraStatus</t>
+  </si>
+  <si>
     <t>2026-07-30</t>
   </si>
   <si>
@@ -239,6 +242,9 @@
     <t>2026-07-31</t>
   </si>
   <si>
+    <t>Ready for Prod</t>
+  </si>
+  <si>
     <t>FNS-74</t>
   </si>
   <si>
@@ -317,6 +323,9 @@
     <t>Video Redirect Bug</t>
   </si>
   <si>
+    <t>Done</t>
+  </si>
+  <si>
     <t>FNS-125</t>
   </si>
   <si>
@@ -350,6 +359,9 @@
     <t>QA sanity fixes</t>
   </si>
   <si>
+    <t>Need Clarification</t>
+  </si>
+  <si>
     <t>GO Live</t>
   </si>
   <si>
@@ -488,6 +500,9 @@
     <t>Home - News</t>
   </si>
   <si>
+    <t>In QA</t>
+  </si>
+  <si>
     <t>FNS-101</t>
   </si>
   <si>
@@ -602,6 +617,9 @@
     <t>player Profile</t>
   </si>
   <si>
+    <t>In Dev</t>
+  </si>
+  <si>
     <t>2026-08-31</t>
   </si>
   <si>
@@ -668,6 +686,9 @@
     <t>Terms and Conditions</t>
   </si>
   <si>
+    <t>Ready for QA</t>
+  </si>
+  <si>
     <t>FNS-28</t>
   </si>
   <si>
@@ -711,6 +732,9 @@
   </si>
   <si>
     <t>Registration form (popup)</t>
+  </si>
+  <si>
+    <t>Code Review</t>
   </si>
   <si>
     <t>FNS-34</t>
@@ -2052,7 +2076,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L264"/>
+  <dimension ref="A1:M264"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2063,7 +2087,7 @@
     <col min="6" max="12" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -2100,10 +2124,13 @@
       <c r="L1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -2112,36 +2139,39 @@
         <v>32</v>
       </c>
       <c r="D2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" t="s">
         <v>69</v>
       </c>
-      <c r="E2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" t="s">
-        <v>68</v>
-      </c>
       <c r="J2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K2" t="s">
         <v>39</v>
       </c>
       <c r="L2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="M2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -2150,36 +2180,39 @@
         <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" t="s">
+        <v>77</v>
+      </c>
+      <c r="M3" t="s">
         <v>74</v>
       </c>
-      <c r="F3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" t="s">
-        <v>68</v>
-      </c>
-      <c r="J3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K3" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -2188,36 +2221,39 @@
         <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" t="s">
         <v>77</v>
       </c>
-      <c r="F4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" t="s">
-        <v>68</v>
-      </c>
-      <c r="J4" t="s">
-        <v>75</v>
-      </c>
       <c r="K4" t="s">
         <v>39</v>
       </c>
       <c r="L4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -2226,36 +2262,39 @@
         <v>32</v>
       </c>
       <c r="D5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" t="s">
         <v>69</v>
       </c>
-      <c r="E5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" t="s">
-        <v>68</v>
-      </c>
       <c r="J5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K5" t="s">
         <v>39</v>
       </c>
       <c r="L5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="M5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -2264,36 +2303,39 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>73</v>
-      </c>
-      <c r="E6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" t="s">
-        <v>68</v>
-      </c>
-      <c r="J6" t="s">
-        <v>75</v>
-      </c>
-      <c r="K6" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>72</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -2302,36 +2344,39 @@
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H7" t="s">
         <v>39</v>
       </c>
       <c r="I7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K7" t="s">
         <v>39</v>
       </c>
       <c r="L7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
@@ -2340,34 +2385,37 @@
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" t="s">
         <v>77</v>
       </c>
-      <c r="F8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" t="s">
-        <v>68</v>
-      </c>
-      <c r="J8" t="s">
-        <v>75</v>
-      </c>
       <c r="K8" t="s">
         <v>39</v>
       </c>
       <c r="L8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -2378,16 +2426,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F9" t="s">
         <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" t="s">
         <v>39</v>
@@ -2396,16 +2444,19 @@
         <v>53</v>
       </c>
       <c r="J9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K9" t="s">
         <v>39</v>
       </c>
       <c r="L9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="M9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -2416,16 +2467,16 @@
         <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F10" t="s">
         <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H10" t="s">
         <v>39</v>
@@ -2434,16 +2485,19 @@
         <v>53</v>
       </c>
       <c r="J10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K10" t="s">
         <v>39</v>
       </c>
       <c r="L10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -2454,16 +2508,16 @@
         <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F11" t="s">
         <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H11" t="s">
         <v>39</v>
@@ -2472,16 +2526,19 @@
         <v>53</v>
       </c>
       <c r="J11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K11" t="s">
         <v>39</v>
       </c>
       <c r="L11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="M11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -2492,36 +2549,39 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H12" t="s">
         <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K12" t="s">
         <v>39</v>
       </c>
       <c r="L12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
@@ -2530,16 +2590,16 @@
         <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H13" t="s">
         <v>39</v>
@@ -2548,18 +2608,21 @@
         <v>53</v>
       </c>
       <c r="J13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K13" t="s">
         <v>39</v>
       </c>
       <c r="L13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
@@ -2568,36 +2631,39 @@
         <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" t="s">
+        <v>69</v>
+      </c>
+      <c r="J14" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" t="s">
+        <v>39</v>
+      </c>
+      <c r="L14" t="s">
+        <v>77</v>
+      </c>
+      <c r="M14" t="s">
         <v>74</v>
       </c>
-      <c r="F14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" t="s">
-        <v>71</v>
-      </c>
-      <c r="H14" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" t="s">
-        <v>68</v>
-      </c>
-      <c r="J14" t="s">
-        <v>75</v>
-      </c>
-      <c r="K14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
@@ -2606,36 +2672,39 @@
         <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F15" t="s">
         <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" t="s">
         <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K15" t="s">
         <v>39</v>
       </c>
       <c r="L15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
@@ -2644,36 +2713,39 @@
         <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" t="s">
+        <v>69</v>
+      </c>
+      <c r="J16" t="s">
         <v>77</v>
       </c>
-      <c r="F16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16" t="s">
-        <v>71</v>
-      </c>
-      <c r="H16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I16" t="s">
-        <v>68</v>
-      </c>
-      <c r="J16" t="s">
-        <v>75</v>
-      </c>
       <c r="K16" t="s">
         <v>39</v>
       </c>
       <c r="L16" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
@@ -2682,16 +2754,16 @@
         <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s">
         <v>39</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H17" t="s">
         <v>39</v>
@@ -2700,18 +2772,21 @@
         <v>53</v>
       </c>
       <c r="J17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K17" t="s">
         <v>39</v>
       </c>
       <c r="L17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="M17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -2720,36 +2795,39 @@
         <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F18" t="s">
         <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
         <v>39</v>
       </c>
       <c r="I18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K18" t="s">
         <v>39</v>
       </c>
       <c r="L18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="M18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
@@ -2758,36 +2836,39 @@
         <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F19" t="s">
         <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H19" t="s">
         <v>39</v>
       </c>
       <c r="I19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K19" t="s">
         <v>39</v>
       </c>
       <c r="L19" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="M19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
@@ -2796,16 +2877,16 @@
         <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F20" t="s">
         <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H20" t="s">
         <v>39</v>
@@ -2814,18 +2895,21 @@
         <v>53</v>
       </c>
       <c r="J20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K20" t="s">
         <v>39</v>
       </c>
       <c r="L20" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="M20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s">
         <v>2</v>
@@ -2834,36 +2918,39 @@
         <v>32</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E21" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" t="s">
         <v>93</v>
       </c>
-      <c r="F21" t="s">
-        <v>39</v>
-      </c>
-      <c r="G21" t="s">
-        <v>71</v>
-      </c>
-      <c r="H21" t="s">
-        <v>39</v>
-      </c>
-      <c r="I21" t="s">
-        <v>91</v>
-      </c>
       <c r="J21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K21" t="s">
         <v>39</v>
       </c>
       <c r="L21" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="M21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B22" t="s">
         <v>2</v>
@@ -2872,36 +2959,39 @@
         <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F22" t="s">
         <v>39</v>
       </c>
       <c r="G22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H22" t="s">
         <v>39</v>
       </c>
       <c r="I22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K22" t="s">
         <v>39</v>
       </c>
       <c r="L22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="M22" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B23" t="s">
         <v>2</v>
@@ -2910,36 +3000,39 @@
         <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" t="s">
         <v>98</v>
       </c>
-      <c r="F23" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" t="s">
-        <v>71</v>
-      </c>
-      <c r="H23" t="s">
-        <v>39</v>
-      </c>
-      <c r="I23" t="s">
-        <v>96</v>
-      </c>
       <c r="J23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K23" t="s">
         <v>39</v>
       </c>
       <c r="L23" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="M23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B24" t="s">
         <v>2</v>
@@ -2948,36 +3041,39 @@
         <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F24" t="s">
         <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H24" t="s">
         <v>39</v>
       </c>
       <c r="I24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K24" t="s">
         <v>39</v>
       </c>
       <c r="L24" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="M24" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B25" t="s">
         <v>2</v>
@@ -2986,36 +3082,39 @@
         <v>32</v>
       </c>
       <c r="D25" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" t="s">
+        <v>39</v>
+      </c>
+      <c r="I25" t="s">
+        <v>98</v>
+      </c>
+      <c r="J25" t="s">
+        <v>98</v>
+      </c>
+      <c r="K25" t="s">
+        <v>39</v>
+      </c>
+      <c r="L25" t="s">
+        <v>98</v>
+      </c>
+      <c r="M25" t="s">
         <v>101</v>
       </c>
-      <c r="E25" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" t="s">
-        <v>39</v>
-      </c>
-      <c r="G25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H25" t="s">
-        <v>39</v>
-      </c>
-      <c r="I25" t="s">
-        <v>96</v>
-      </c>
-      <c r="J25" t="s">
-        <v>96</v>
-      </c>
-      <c r="K25" t="s">
-        <v>39</v>
-      </c>
-      <c r="L25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
         <v>2</v>
@@ -3024,36 +3123,39 @@
         <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E26" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F26" t="s">
         <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H26" t="s">
         <v>39</v>
       </c>
       <c r="I26" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J26" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K26" t="s">
         <v>39</v>
       </c>
       <c r="L26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="M26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B27" t="s">
         <v>2</v>
@@ -3062,36 +3164,39 @@
         <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F27" t="s">
         <v>39</v>
       </c>
       <c r="G27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H27" t="s">
         <v>39</v>
       </c>
       <c r="I27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K27" t="s">
         <v>39</v>
       </c>
       <c r="L27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="M27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B28" t="s">
         <v>2</v>
@@ -3100,10 +3205,10 @@
         <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E28" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F28" t="s">
         <v>39</v>
@@ -3115,21 +3220,24 @@
         <v>39</v>
       </c>
       <c r="I28" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J28" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K28" t="s">
         <v>39</v>
       </c>
       <c r="L28" t="s">
-        <v>107</v>
+        <v>110</v>
+      </c>
+      <c r="M28" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
         <v>2</v>
@@ -3141,31 +3249,31 @@
         <v>39</v>
       </c>
       <c r="E29" t="s">
+        <v>114</v>
+      </c>
+      <c r="F29" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" t="s">
+        <v>72</v>
+      </c>
+      <c r="H29" t="s">
+        <v>39</v>
+      </c>
+      <c r="I29" t="s">
         <v>110</v>
       </c>
-      <c r="F29" t="s">
-        <v>39</v>
-      </c>
-      <c r="G29" t="s">
-        <v>71</v>
-      </c>
-      <c r="H29" t="s">
-        <v>39</v>
-      </c>
-      <c r="I29" t="s">
-        <v>107</v>
-      </c>
       <c r="J29" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K29" t="s">
         <v>39</v>
       </c>
       <c r="L29" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>36</v>
       </c>
@@ -3176,16 +3284,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E30" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F30" t="s">
         <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H30" t="s">
         <v>39</v>
@@ -3194,16 +3302,19 @@
         <v>36</v>
       </c>
       <c r="J30" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K30" t="s">
         <v>39</v>
       </c>
       <c r="L30" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="M30" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -3214,16 +3325,16 @@
         <v>32</v>
       </c>
       <c r="D31" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E31" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F31" t="s">
         <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H31" t="s">
         <v>39</v>
@@ -3232,18 +3343,21 @@
         <v>36</v>
       </c>
       <c r="J31" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K31" t="s">
         <v>39</v>
       </c>
       <c r="L31" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="M31" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
@@ -3252,36 +3366,39 @@
         <v>32</v>
       </c>
       <c r="D32" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E32" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F32" t="s">
         <v>39</v>
       </c>
       <c r="G32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H32" t="s">
         <v>39</v>
       </c>
       <c r="I32" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J32" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K32" t="s">
         <v>39</v>
       </c>
       <c r="L32" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="M32" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
@@ -3290,16 +3407,16 @@
         <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F33" t="s">
         <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H33" t="s">
         <v>39</v>
@@ -3308,18 +3425,21 @@
         <v>36</v>
       </c>
       <c r="J33" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K33" t="s">
         <v>39</v>
       </c>
       <c r="L33" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="M33" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
@@ -3328,36 +3448,39 @@
         <v>32</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E34" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F34" t="s">
         <v>39</v>
       </c>
       <c r="G34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H34" t="s">
         <v>39</v>
       </c>
       <c r="I34" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K34" t="s">
         <v>39</v>
       </c>
       <c r="L34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="M34" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
@@ -3366,34 +3489,37 @@
         <v>32</v>
       </c>
       <c r="D35" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F35" t="s">
         <v>39</v>
       </c>
       <c r="G35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H35" t="s">
         <v>39</v>
       </c>
       <c r="I35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K35" t="s">
         <v>39</v>
       </c>
       <c r="L35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="M35" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>53</v>
       </c>
@@ -3404,16 +3530,16 @@
         <v>32</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E36" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F36" t="s">
         <v>39</v>
       </c>
       <c r="G36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H36" t="s">
         <v>39</v>
@@ -3430,8 +3556,11 @@
       <c r="L36" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>53</v>
       </c>
@@ -3442,16 +3571,16 @@
         <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E37" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F37" t="s">
         <v>39</v>
       </c>
       <c r="G37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H37" t="s">
         <v>39</v>
@@ -3468,10 +3597,13 @@
       <c r="L37" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M37" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s">
         <v>4</v>
@@ -3480,22 +3612,22 @@
         <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E38" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F38" t="s">
         <v>39</v>
       </c>
       <c r="G38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H38" t="s">
         <v>39</v>
       </c>
       <c r="I38" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J38" t="s">
         <v>48</v>
@@ -3506,10 +3638,13 @@
       <c r="L38" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B39" t="s">
         <v>4</v>
@@ -3518,22 +3653,22 @@
         <v>32</v>
       </c>
       <c r="D39" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E39" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F39" t="s">
         <v>39</v>
       </c>
       <c r="G39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H39" t="s">
         <v>39</v>
       </c>
       <c r="I39" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J39" t="s">
         <v>48</v>
@@ -3544,10 +3679,13 @@
       <c r="L39" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M39" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
@@ -3556,22 +3694,22 @@
         <v>32</v>
       </c>
       <c r="D40" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E40" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F40" t="s">
         <v>39</v>
       </c>
       <c r="G40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H40" t="s">
         <v>39</v>
       </c>
       <c r="I40" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J40" t="s">
         <v>48</v>
@@ -3582,10 +3720,13 @@
       <c r="L40" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B41" t="s">
         <v>4</v>
@@ -3594,22 +3735,22 @@
         <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E41" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F41" t="s">
         <v>39</v>
       </c>
       <c r="G41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H41" t="s">
         <v>39</v>
       </c>
       <c r="I41" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J41" t="s">
         <v>48</v>
@@ -3620,8 +3761,11 @@
       <c r="L41" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M41" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>48</v>
       </c>
@@ -3632,22 +3776,22 @@
         <v>32</v>
       </c>
       <c r="D42" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E42" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F42" t="s">
         <v>39</v>
       </c>
       <c r="G42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H42" t="s">
         <v>39</v>
       </c>
       <c r="I42" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J42" t="s">
         <v>48</v>
@@ -3658,8 +3802,11 @@
       <c r="L42" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M42" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>53</v>
       </c>
@@ -3670,16 +3817,16 @@
         <v>32</v>
       </c>
       <c r="D43" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E43" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F43" t="s">
         <v>39</v>
       </c>
       <c r="G43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H43" t="s">
         <v>39</v>
@@ -3688,16 +3835,19 @@
         <v>53</v>
       </c>
       <c r="J43" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s">
         <v>39</v>
       </c>
       <c r="L43" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M43" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -3708,16 +3858,16 @@
         <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E44" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F44" t="s">
         <v>39</v>
       </c>
       <c r="G44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H44" t="s">
         <v>39</v>
@@ -3726,16 +3876,19 @@
         <v>53</v>
       </c>
       <c r="J44" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K44" t="s">
         <v>39</v>
       </c>
       <c r="L44" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M44" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -3746,16 +3899,16 @@
         <v>32</v>
       </c>
       <c r="D45" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E45" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
       </c>
       <c r="G45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H45" t="s">
         <v>39</v>
@@ -3764,18 +3917,21 @@
         <v>53</v>
       </c>
       <c r="J45" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K45" t="s">
         <v>39</v>
       </c>
       <c r="L45" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M45" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B46" t="s">
         <v>7</v>
@@ -3784,16 +3940,16 @@
         <v>32</v>
       </c>
       <c r="D46" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E46" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F46" t="s">
         <v>39</v>
       </c>
       <c r="G46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H46" t="s">
         <v>39</v>
@@ -3802,18 +3958,21 @@
         <v>53</v>
       </c>
       <c r="J46" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K46" t="s">
         <v>39</v>
       </c>
       <c r="L46" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M46" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B47" t="s">
         <v>7</v>
@@ -3822,16 +3981,16 @@
         <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E47" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F47" t="s">
         <v>39</v>
       </c>
       <c r="G47" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H47" t="s">
         <v>39</v>
@@ -3840,18 +3999,21 @@
         <v>53</v>
       </c>
       <c r="J47" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K47" t="s">
         <v>39</v>
       </c>
       <c r="L47" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M47" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B48" t="s">
         <v>7</v>
@@ -3860,16 +4022,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E48" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F48" t="s">
         <v>39</v>
       </c>
       <c r="G48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H48" t="s">
         <v>39</v>
@@ -3878,18 +4040,21 @@
         <v>53</v>
       </c>
       <c r="J48" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K48" t="s">
         <v>39</v>
       </c>
       <c r="L48" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M48" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B49" t="s">
         <v>7</v>
@@ -3898,36 +4063,39 @@
         <v>32</v>
       </c>
       <c r="D49" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E49" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F49" t="s">
         <v>39</v>
       </c>
       <c r="G49" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H49" t="s">
         <v>39</v>
       </c>
       <c r="I49" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J49" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K49" t="s">
         <v>39</v>
       </c>
       <c r="L49" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="M49" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B50" t="s">
         <v>7</v>
@@ -3936,36 +4104,39 @@
         <v>32</v>
       </c>
       <c r="D50" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E50" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F50" t="s">
         <v>39</v>
       </c>
       <c r="G50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H50" t="s">
         <v>39</v>
       </c>
       <c r="I50" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K50" t="s">
         <v>39</v>
       </c>
       <c r="L50" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="M50" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B51" t="s">
         <v>7</v>
@@ -3974,36 +4145,39 @@
         <v>32</v>
       </c>
       <c r="D51" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E51" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F51" t="s">
         <v>39</v>
       </c>
       <c r="G51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H51" t="s">
         <v>39</v>
       </c>
       <c r="I51" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K51" t="s">
         <v>39</v>
       </c>
       <c r="L51" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="M51" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B52" t="s">
         <v>7</v>
@@ -4012,34 +4186,37 @@
         <v>32</v>
       </c>
       <c r="D52" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E52" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F52" t="s">
         <v>39</v>
       </c>
       <c r="G52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H52" t="s">
         <v>39</v>
       </c>
       <c r="I52" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J52" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K52" t="s">
         <v>39</v>
       </c>
       <c r="L52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="M52" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>36</v>
       </c>
@@ -4050,16 +4227,16 @@
         <v>32</v>
       </c>
       <c r="D53" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E53" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F53" t="s">
         <v>39</v>
       </c>
       <c r="G53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H53" t="s">
         <v>39</v>
@@ -4076,8 +4253,11 @@
       <c r="L53" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M53" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>36</v>
       </c>
@@ -4088,16 +4268,16 @@
         <v>32</v>
       </c>
       <c r="D54" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E54" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F54" t="s">
         <v>39</v>
       </c>
       <c r="G54" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H54" t="s">
         <v>39</v>
@@ -4114,8 +4294,11 @@
       <c r="L54" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M54" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>42</v>
       </c>
@@ -4126,16 +4309,16 @@
         <v>32</v>
       </c>
       <c r="D55" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E55" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F55" t="s">
         <v>39</v>
       </c>
       <c r="G55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H55" t="s">
         <v>39</v>
@@ -4152,8 +4335,11 @@
       <c r="L55" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M55" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>42</v>
       </c>
@@ -4164,16 +4350,16 @@
         <v>32</v>
       </c>
       <c r="D56" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E56" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F56" t="s">
         <v>39</v>
       </c>
       <c r="G56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H56" t="s">
         <v>39</v>
@@ -4190,10 +4376,13 @@
       <c r="L56" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M56" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B57" t="s">
         <v>8</v>
@@ -4202,36 +4391,39 @@
         <v>32</v>
       </c>
       <c r="D57" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E57" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F57" t="s">
         <v>39</v>
       </c>
       <c r="G57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H57" t="s">
         <v>39</v>
       </c>
       <c r="I57" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J57" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K57" t="s">
         <v>39</v>
       </c>
       <c r="L57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="M57" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B58" t="s">
         <v>8</v>
@@ -4240,36 +4432,39 @@
         <v>32</v>
       </c>
       <c r="D58" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E58" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F58" t="s">
         <v>39</v>
       </c>
       <c r="G58" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H58" t="s">
         <v>39</v>
       </c>
       <c r="I58" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J58" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K58" t="s">
         <v>39</v>
       </c>
       <c r="L58" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="M58" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B59" t="s">
         <v>8</v>
@@ -4278,36 +4473,39 @@
         <v>32</v>
       </c>
       <c r="D59" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E59" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F59" t="s">
         <v>39</v>
       </c>
       <c r="G59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H59" t="s">
         <v>39</v>
       </c>
       <c r="I59" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J59" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K59" t="s">
         <v>39</v>
       </c>
       <c r="L59" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="M59" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B60" t="s">
         <v>8</v>
@@ -4316,36 +4514,39 @@
         <v>32</v>
       </c>
       <c r="D60" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E60" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F60" t="s">
         <v>39</v>
       </c>
       <c r="G60" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H60" t="s">
         <v>39</v>
       </c>
       <c r="I60" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J60" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K60" t="s">
         <v>39</v>
       </c>
       <c r="L60" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="M60" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B61" t="s">
         <v>8</v>
@@ -4354,22 +4555,22 @@
         <v>32</v>
       </c>
       <c r="D61" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E61" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F61" t="s">
         <v>39</v>
       </c>
       <c r="G61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H61" t="s">
         <v>39</v>
       </c>
       <c r="I61" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J61" t="s">
         <v>53</v>
@@ -4380,8 +4581,11 @@
       <c r="L61" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>53</v>
       </c>
@@ -4392,22 +4596,22 @@
         <v>32</v>
       </c>
       <c r="D62" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E62" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F62" t="s">
         <v>39</v>
       </c>
       <c r="G62" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H62" t="s">
         <v>39</v>
       </c>
       <c r="I62" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J62" t="s">
         <v>53</v>
@@ -4418,8 +4622,11 @@
       <c r="L62" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M62" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>53</v>
       </c>
@@ -4430,16 +4637,16 @@
         <v>32</v>
       </c>
       <c r="D63" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E63" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F63" t="s">
         <v>39</v>
       </c>
       <c r="G63" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H63" t="s">
         <v>39</v>
@@ -4448,18 +4655,21 @@
         <v>53</v>
       </c>
       <c r="J63" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K63" t="s">
         <v>39</v>
       </c>
       <c r="L63" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M63" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B64" t="s">
         <v>8</v>
@@ -4468,16 +4678,16 @@
         <v>32</v>
       </c>
       <c r="D64" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E64" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F64" t="s">
         <v>39</v>
       </c>
       <c r="G64" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H64" t="s">
         <v>39</v>
@@ -4486,13 +4696,16 @@
         <v>53</v>
       </c>
       <c r="J64" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K64" t="s">
         <v>39</v>
       </c>
       <c r="L64" t="s">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="M64" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.25"/>
@@ -4800,7 +5013,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L262"/>
+  <dimension ref="A1:M262"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4811,7 +5024,7 @@
     <col min="6" max="12" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -4848,8 +5061,11 @@
       <c r="L1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -4860,10 +5076,10 @@
         <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F2" t="s">
         <v>39</v>
@@ -4886,8 +5102,11 @@
       <c r="L2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -4898,10 +5117,10 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F3" t="s">
         <v>39</v>
@@ -4924,10 +5143,13 @@
       <c r="L3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -4936,10 +5158,10 @@
         <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F4" t="s">
         <v>39</v>
@@ -4951,10 +5173,10 @@
         <v>39</v>
       </c>
       <c r="I4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -4962,10 +5184,13 @@
       <c r="L4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -4974,10 +5199,10 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E5" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F5" t="s">
         <v>39</v>
@@ -4989,10 +5214,10 @@
         <v>39</v>
       </c>
       <c r="I5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K5" t="s">
         <v>39</v>
@@ -5000,10 +5225,13 @@
       <c r="L5" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -5012,10 +5240,10 @@
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E6" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
@@ -5027,10 +5255,10 @@
         <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J6" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K6" t="s">
         <v>39</v>
@@ -5038,10 +5266,13 @@
       <c r="L6" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -5050,10 +5281,10 @@
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E7" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
@@ -5065,21 +5296,24 @@
         <v>39</v>
       </c>
       <c r="I7" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J7" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="K7" t="s">
         <v>39</v>
       </c>
       <c r="L7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="M7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
@@ -5088,10 +5322,10 @@
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F8" t="s">
         <v>39</v>
@@ -5103,10 +5337,10 @@
         <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J8" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K8" t="s">
         <v>39</v>
@@ -5114,10 +5348,13 @@
       <c r="L8" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
@@ -5126,10 +5363,10 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E9" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F9" t="s">
         <v>39</v>
@@ -5141,10 +5378,10 @@
         <v>39</v>
       </c>
       <c r="I9" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J9" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K9" t="s">
         <v>39</v>
@@ -5152,10 +5389,13 @@
       <c r="L9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
@@ -5164,10 +5404,10 @@
         <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E10" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F10" t="s">
         <v>39</v>
@@ -5179,10 +5419,10 @@
         <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J10" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K10" t="s">
         <v>39</v>
@@ -5190,10 +5430,13 @@
       <c r="L10" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -5202,10 +5445,10 @@
         <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E11" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F11" t="s">
         <v>39</v>
@@ -5217,7 +5460,7 @@
         <v>39</v>
       </c>
       <c r="I11" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J11" t="s">
         <v>38</v>
@@ -5228,10 +5471,13 @@
       <c r="L11" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -5240,10 +5486,10 @@
         <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E12" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
@@ -5255,7 +5501,7 @@
         <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J12" t="s">
         <v>38</v>
@@ -5266,10 +5512,13 @@
       <c r="L12" t="s">
         <v>39</v>
       </c>
+      <c r="M12" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
@@ -5281,22 +5530,22 @@
         <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H13" t="s">
         <v>39</v>
       </c>
       <c r="I13" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J13" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K13" t="s">
         <v>39</v>
@@ -5307,7 +5556,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
@@ -5319,22 +5568,22 @@
         <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F14" t="s">
         <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H14" t="s">
         <v>39</v>
       </c>
       <c r="I14" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J14" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K14" t="s">
         <v>39</v>
@@ -5343,7 +5592,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -5354,10 +5603,10 @@
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E15" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F15" t="s">
         <v>39</v>
@@ -5369,7 +5618,7 @@
         <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J15" t="s">
         <v>38</v>
@@ -5380,8 +5629,11 @@
       <c r="L15" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -5392,10 +5644,10 @@
         <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E16" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F16" t="s">
         <v>39</v>
@@ -5407,10 +5659,10 @@
         <v>39</v>
       </c>
       <c r="I16" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J16" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K16" t="s">
         <v>39</v>
@@ -5418,8 +5670,11 @@
       <c r="L16" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -5430,10 +5685,10 @@
         <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E17" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F17" t="s">
         <v>39</v>
@@ -5448,7 +5703,7 @@
         <v>38</v>
       </c>
       <c r="J17" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K17" t="s">
         <v>39</v>
@@ -5456,10 +5711,13 @@
       <c r="L17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -5468,10 +5726,10 @@
         <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E18" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F18" t="s">
         <v>39</v>
@@ -5486,7 +5744,7 @@
         <v>38</v>
       </c>
       <c r="J18" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K18" t="s">
         <v>39</v>
@@ -5494,10 +5752,13 @@
       <c r="L18" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
@@ -5506,10 +5767,10 @@
         <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E19" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F19" t="s">
         <v>39</v>
@@ -5521,10 +5782,10 @@
         <v>39</v>
       </c>
       <c r="I19" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J19" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K19" t="s">
         <v>39</v>
@@ -5532,10 +5793,13 @@
       <c r="L19" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
@@ -5544,10 +5808,10 @@
         <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E20" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F20" t="s">
         <v>39</v>
@@ -5559,10 +5823,10 @@
         <v>39</v>
       </c>
       <c r="I20" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J20" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K20" t="s">
         <v>39</v>
@@ -5570,10 +5834,13 @@
       <c r="L20" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B21" t="s">
         <v>2</v>
@@ -5582,10 +5849,10 @@
         <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E21" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F21" t="s">
         <v>39</v>
@@ -5597,10 +5864,10 @@
         <v>39</v>
       </c>
       <c r="I21" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J21" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K21" t="s">
         <v>39</v>
@@ -5608,10 +5875,13 @@
       <c r="L21" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B22" t="s">
         <v>2</v>
@@ -5620,10 +5890,10 @@
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E22" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F22" t="s">
         <v>39</v>
@@ -5635,21 +5905,24 @@
         <v>39</v>
       </c>
       <c r="I22" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J22" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K22" t="s">
         <v>39</v>
       </c>
       <c r="L22" t="s">
         <v>39</v>
+      </c>
+      <c r="M22" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B23" t="s">
         <v>2</v>
@@ -5661,22 +5934,22 @@
         <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F23" t="s">
         <v>39</v>
       </c>
       <c r="G23" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H23" t="s">
         <v>39</v>
       </c>
       <c r="I23" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J23" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="K23" t="s">
         <v>39</v>
@@ -5687,7 +5960,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s">
         <v>2</v>
@@ -5699,22 +5972,22 @@
         <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F24" t="s">
         <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H24" t="s">
         <v>39</v>
       </c>
       <c r="I24" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J24" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="K24" t="s">
         <v>39</v>
@@ -5725,7 +5998,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B25" t="s">
         <v>2</v>
@@ -5737,22 +6010,22 @@
         <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F25" t="s">
         <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H25" t="s">
         <v>39</v>
       </c>
       <c r="I25" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J25" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="K25" t="s">
         <v>39</v>
@@ -5763,7 +6036,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B26" t="s">
         <v>2</v>
@@ -5775,22 +6048,22 @@
         <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F26" t="s">
         <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H26" t="s">
         <v>39</v>
       </c>
       <c r="I26" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="J26" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K26" t="s">
         <v>39</v>
@@ -5813,13 +6086,13 @@
         <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F27" t="s">
         <v>39</v>
       </c>
       <c r="G27" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H27" t="s">
         <v>39</v>
@@ -5839,7 +6112,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B28" t="s">
         <v>2</v>
@@ -5851,22 +6124,22 @@
         <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F28" t="s">
         <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H28" t="s">
         <v>39</v>
       </c>
       <c r="I28" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J28" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K28" t="s">
         <v>39</v>
@@ -5877,7 +6150,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B29" t="s">
         <v>2</v>
@@ -5889,22 +6162,22 @@
         <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F29" t="s">
         <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H29" t="s">
         <v>39</v>
       </c>
       <c r="I29" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J29" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K29" t="s">
         <v>39</v>
@@ -5915,7 +6188,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B30" t="s">
         <v>2</v>
@@ -5927,22 +6200,22 @@
         <v>39</v>
       </c>
       <c r="E30" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F30" t="s">
         <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H30" t="s">
         <v>39</v>
       </c>
       <c r="I30" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J30" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K30" t="s">
         <v>39</v>
@@ -5953,7 +6226,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B31" t="s">
         <v>2</v>
@@ -5965,22 +6238,22 @@
         <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F31" t="s">
         <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H31" t="s">
         <v>39</v>
       </c>
       <c r="I31" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J31" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K31" t="s">
         <v>39</v>
@@ -5991,7 +6264,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B32" t="s">
         <v>2</v>
@@ -6003,22 +6276,22 @@
         <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F32" t="s">
         <v>39</v>
       </c>
       <c r="G32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H32" t="s">
         <v>39</v>
       </c>
       <c r="I32" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J32" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K32" t="s">
         <v>39</v>
@@ -6029,7 +6302,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B33" t="s">
         <v>2</v>
@@ -6041,22 +6314,22 @@
         <v>39</v>
       </c>
       <c r="E33" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F33" t="s">
         <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H33" t="s">
         <v>39</v>
       </c>
       <c r="I33" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J33" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K33" t="s">
         <v>39</v>
@@ -6067,7 +6340,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B34" t="s">
         <v>2</v>
@@ -6079,33 +6352,33 @@
         <v>39</v>
       </c>
       <c r="E34" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F34" t="s">
         <v>39</v>
       </c>
       <c r="G34" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H34" t="s">
         <v>39</v>
       </c>
       <c r="I34" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J34" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K34" t="s">
         <v>39</v>
       </c>
       <c r="L34" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B35" t="s">
         <v>2</v>
@@ -6117,33 +6390,33 @@
         <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F35" t="s">
         <v>39</v>
       </c>
       <c r="G35" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H35" t="s">
         <v>39</v>
       </c>
       <c r="I35" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J35" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K35" t="s">
         <v>39</v>
       </c>
       <c r="L35" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B36" t="s">
         <v>2</v>
@@ -6155,33 +6428,33 @@
         <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F36" t="s">
         <v>39</v>
       </c>
       <c r="G36" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H36" t="s">
         <v>39</v>
       </c>
       <c r="I36" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="J36" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K36" t="s">
         <v>39</v>
       </c>
       <c r="L36" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
@@ -6190,10 +6463,10 @@
         <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="E37" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F37" t="s">
         <v>39</v>
@@ -6205,21 +6478,24 @@
         <v>39</v>
       </c>
       <c r="I37" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J37" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K37" t="s">
         <v>39</v>
       </c>
       <c r="L37" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+      <c r="M37" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B38" t="s">
         <v>6</v>
@@ -6228,10 +6504,10 @@
         <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="E38" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="F38" t="s">
         <v>39</v>
@@ -6243,10 +6519,10 @@
         <v>39</v>
       </c>
       <c r="I38" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J38" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K38" t="s">
         <v>39</v>
@@ -6254,10 +6530,13 @@
       <c r="L38" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M38" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
@@ -6266,10 +6545,10 @@
         <v>40</v>
       </c>
       <c r="D39" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="E39" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="F39" t="s">
         <v>39</v>
@@ -6281,10 +6560,10 @@
         <v>39</v>
       </c>
       <c r="I39" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J39" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K39" t="s">
         <v>39</v>
@@ -6292,10 +6571,13 @@
       <c r="L39" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M39" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
@@ -6304,10 +6586,10 @@
         <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E40" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F40" t="s">
         <v>39</v>
@@ -6319,10 +6601,10 @@
         <v>39</v>
       </c>
       <c r="I40" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J40" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K40" t="s">
         <v>39</v>
@@ -6330,10 +6612,13 @@
       <c r="L40" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M40" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
@@ -6342,10 +6627,10 @@
         <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="E41" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="F41" t="s">
         <v>39</v>
@@ -6357,10 +6642,10 @@
         <v>39</v>
       </c>
       <c r="I41" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J41" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K41" t="s">
         <v>39</v>
@@ -6368,10 +6653,13 @@
       <c r="L41" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M41" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B42" t="s">
         <v>6</v>
@@ -6380,10 +6668,10 @@
         <v>40</v>
       </c>
       <c r="D42" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E42" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="F42" t="s">
         <v>39</v>
@@ -6395,10 +6683,10 @@
         <v>39</v>
       </c>
       <c r="I42" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J42" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K42" t="s">
         <v>39</v>
@@ -6406,10 +6694,13 @@
       <c r="L42" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M42" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B43" t="s">
         <v>6</v>
@@ -6418,10 +6709,10 @@
         <v>40</v>
       </c>
       <c r="D43" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E43" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F43" t="s">
         <v>39</v>
@@ -6433,10 +6724,10 @@
         <v>39</v>
       </c>
       <c r="I43" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="J43" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K43" t="s">
         <v>39</v>
@@ -6444,10 +6735,13 @@
       <c r="L43" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M43" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B44" t="s">
         <v>6</v>
@@ -6456,10 +6750,10 @@
         <v>40</v>
       </c>
       <c r="D44" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E44" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F44" t="s">
         <v>39</v>
@@ -6471,10 +6765,10 @@
         <v>39</v>
       </c>
       <c r="I44" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="J44" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K44" t="s">
         <v>39</v>
@@ -6482,10 +6776,13 @@
       <c r="L44" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M44" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
@@ -6494,10 +6791,10 @@
         <v>40</v>
       </c>
       <c r="D45" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E45" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
@@ -6509,10 +6806,10 @@
         <v>39</v>
       </c>
       <c r="I45" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J45" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K45" t="s">
         <v>39</v>
@@ -6520,10 +6817,13 @@
       <c r="L45" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M45" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
@@ -6532,7 +6832,7 @@
         <v>40</v>
       </c>
       <c r="D46" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="E46" t="s">
         <v>39</v>
@@ -6547,10 +6847,10 @@
         <v>39</v>
       </c>
       <c r="I46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K46" t="s">
         <v>39</v>
@@ -6558,10 +6858,13 @@
       <c r="L46" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M46" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B47" t="s">
         <v>9</v>
@@ -6570,10 +6873,10 @@
         <v>40</v>
       </c>
       <c r="D47" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E47" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="F47" t="s">
         <v>39</v>
@@ -6585,10 +6888,10 @@
         <v>39</v>
       </c>
       <c r="I47" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J47" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K47" t="s">
         <v>39</v>
@@ -6596,10 +6899,13 @@
       <c r="L47" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M47" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
@@ -6608,7 +6914,7 @@
         <v>40</v>
       </c>
       <c r="D48" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E48" t="s">
         <v>39</v>
@@ -6623,10 +6929,10 @@
         <v>39</v>
       </c>
       <c r="I48" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J48" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K48" t="s">
         <v>39</v>
@@ -6634,10 +6940,13 @@
       <c r="L48" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M48" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
@@ -6646,10 +6955,10 @@
         <v>40</v>
       </c>
       <c r="D49" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="F49" t="s">
         <v>39</v>
@@ -6661,21 +6970,24 @@
         <v>39</v>
       </c>
       <c r="I49" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J49" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K49" t="s">
         <v>39</v>
       </c>
       <c r="L49" t="s">
         <v>39</v>
+      </c>
+      <c r="M49" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B50" t="s">
         <v>9</v>
@@ -6687,22 +6999,22 @@
         <v>39</v>
       </c>
       <c r="E50" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="F50" t="s">
         <v>39</v>
       </c>
       <c r="G50" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H50" t="s">
         <v>39</v>
       </c>
       <c r="I50" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J50" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K50" t="s">
         <v>39</v>
@@ -6711,9 +7023,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
@@ -6722,10 +7034,10 @@
         <v>40</v>
       </c>
       <c r="D51" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="E51" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="F51" t="s">
         <v>39</v>
@@ -6737,10 +7049,10 @@
         <v>39</v>
       </c>
       <c r="I51" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J51" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="K51" t="s">
         <v>39</v>
@@ -6748,10 +7060,13 @@
       <c r="L51" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M51" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
@@ -6760,10 +7075,10 @@
         <v>40</v>
       </c>
       <c r="D52" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E52" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="F52" t="s">
         <v>39</v>
@@ -6775,10 +7090,10 @@
         <v>39</v>
       </c>
       <c r="I52" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J52" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K52" t="s">
         <v>39</v>
@@ -6786,10 +7101,13 @@
       <c r="L52" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M52" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
@@ -6798,10 +7116,10 @@
         <v>40</v>
       </c>
       <c r="D53" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="E53" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="F53" t="s">
         <v>39</v>
@@ -6813,10 +7131,10 @@
         <v>39</v>
       </c>
       <c r="I53" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J53" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K53" t="s">
         <v>39</v>
@@ -6824,10 +7142,13 @@
       <c r="L53" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M53" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
@@ -6836,10 +7157,10 @@
         <v>40</v>
       </c>
       <c r="D54" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E54" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="F54" t="s">
         <v>39</v>
@@ -6851,10 +7172,10 @@
         <v>39</v>
       </c>
       <c r="I54" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J54" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K54" t="s">
         <v>39</v>
@@ -6862,10 +7183,13 @@
       <c r="L54" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M54" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
@@ -6874,10 +7198,10 @@
         <v>40</v>
       </c>
       <c r="D55" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="E55" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="F55" t="s">
         <v>39</v>
@@ -6889,10 +7213,10 @@
         <v>39</v>
       </c>
       <c r="I55" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J55" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K55" t="s">
         <v>39</v>
@@ -6900,10 +7224,13 @@
       <c r="L55" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M55" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
@@ -6912,10 +7239,10 @@
         <v>40</v>
       </c>
       <c r="D56" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E56" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="F56" t="s">
         <v>39</v>
@@ -6927,21 +7254,24 @@
         <v>39</v>
       </c>
       <c r="I56" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J56" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K56" t="s">
         <v>39</v>
       </c>
       <c r="L56" t="s">
         <v>39</v>
+      </c>
+      <c r="M56" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B57" t="s">
         <v>10</v>
@@ -6953,22 +7283,22 @@
         <v>39</v>
       </c>
       <c r="E57" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F57" t="s">
         <v>39</v>
       </c>
       <c r="G57" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H57" t="s">
         <v>39</v>
       </c>
       <c r="I57" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J57" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="K57" t="s">
         <v>39</v>
@@ -6977,9 +7307,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
@@ -6988,10 +7318,10 @@
         <v>40</v>
       </c>
       <c r="D58" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="E58" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F58" t="s">
         <v>39</v>
@@ -7003,21 +7333,24 @@
         <v>39</v>
       </c>
       <c r="I58" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J58" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K58" t="s">
         <v>39</v>
       </c>
       <c r="L58" t="s">
         <v>39</v>
+      </c>
+      <c r="M58" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B59" t="s">
         <v>10</v>
@@ -7029,22 +7362,22 @@
         <v>39</v>
       </c>
       <c r="E59" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F59" t="s">
         <v>39</v>
       </c>
       <c r="G59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H59" t="s">
         <v>39</v>
       </c>
       <c r="I59" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J59" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K59" t="s">
         <v>39</v>
@@ -7053,9 +7386,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B60" t="s">
         <v>10</v>
@@ -7064,10 +7397,10 @@
         <v>40</v>
       </c>
       <c r="D60" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E60" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F60" t="s">
         <v>39</v>
@@ -7079,10 +7412,10 @@
         <v>39</v>
       </c>
       <c r="I60" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J60" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K60" t="s">
         <v>39</v>
@@ -7090,10 +7423,13 @@
       <c r="L60" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M60" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B61" t="s">
         <v>10</v>
@@ -7102,10 +7438,10 @@
         <v>40</v>
       </c>
       <c r="D61" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E61" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F61" t="s">
         <v>39</v>
@@ -7117,10 +7453,10 @@
         <v>39</v>
       </c>
       <c r="I61" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J61" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K61" t="s">
         <v>39</v>
@@ -7128,10 +7464,13 @@
       <c r="L61" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M61" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B62" t="s">
         <v>10</v>
@@ -7140,10 +7479,10 @@
         <v>40</v>
       </c>
       <c r="D62" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E62" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F62" t="s">
         <v>39</v>
@@ -7155,16 +7494,19 @@
         <v>39</v>
       </c>
       <c r="I62" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J62" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K62" t="s">
         <v>39</v>
       </c>
       <c r="L62" t="s">
         <v>39</v>
+      </c>
+      <c r="M62" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="63" spans="4:4" x14ac:dyDescent="0.25"/>
@@ -7452,7 +7794,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L239"/>
+  <dimension ref="A1:M239"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -7463,7 +7805,7 @@
     <col min="6" max="12" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -7500,10 +7842,13 @@
       <c r="L1" t="s">
         <v>67</v>
       </c>
+      <c r="M1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -7515,22 +7860,22 @@
         <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="F2" t="s">
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H2" t="s">
         <v>39</v>
       </c>
       <c r="I2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K2" t="s">
         <v>39</v>
@@ -7541,7 +7886,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -7553,22 +7898,22 @@
         <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="F3" t="s">
         <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H3" t="s">
         <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K3" t="s">
         <v>39</v>
@@ -7579,7 +7924,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -7591,22 +7936,22 @@
         <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="F4" t="s">
         <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H4" t="s">
         <v>39</v>
       </c>
       <c r="I4" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J4" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -7617,7 +7962,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -7629,22 +7974,22 @@
         <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F5" t="s">
         <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H5" t="s">
         <v>39</v>
       </c>
       <c r="I5" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J5" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K5" t="s">
         <v>39</v>
@@ -7655,7 +8000,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -7667,22 +8012,22 @@
         <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H6" t="s">
         <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="J6" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="K6" t="s">
         <v>39</v>
@@ -7693,7 +8038,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -7705,22 +8050,22 @@
         <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H7" t="s">
         <v>39</v>
       </c>
       <c r="I7" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="J7" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="K7" t="s">
         <v>39</v>
@@ -7731,7 +8076,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -7743,22 +8088,22 @@
         <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="F8" t="s">
         <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H8" t="s">
         <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="J8" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K8" t="s">
         <v>39</v>
@@ -7781,13 +8126,13 @@
         <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="F9" t="s">
         <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H9" t="s">
         <v>39</v>
@@ -7807,7 +8152,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
@@ -7819,22 +8164,22 @@
         <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F10" t="s">
         <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H10" t="s">
         <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J10" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K10" t="s">
         <v>39</v>
@@ -7845,7 +8190,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -7857,22 +8202,22 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="F11" t="s">
         <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H11" t="s">
         <v>39</v>
       </c>
       <c r="I11" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J11" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K11" t="s">
         <v>39</v>
@@ -7883,7 +8228,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
@@ -7895,22 +8240,22 @@
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H12" t="s">
         <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J12" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K12" t="s">
         <v>39</v>
@@ -7921,7 +8266,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
@@ -7933,22 +8278,22 @@
         <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H13" t="s">
         <v>39</v>
       </c>
       <c r="I13" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J13" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K13" t="s">
         <v>39</v>
@@ -7959,7 +8304,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
@@ -7971,22 +8316,22 @@
         <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="F14" t="s">
         <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H14" t="s">
         <v>39</v>
       </c>
       <c r="I14" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J14" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K14" t="s">
         <v>39</v>
@@ -7997,7 +8342,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B15" t="s">
         <v>6</v>
@@ -8009,22 +8354,22 @@
         <v>39</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F15" t="s">
         <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H15" t="s">
         <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J15" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K15" t="s">
         <v>39</v>
@@ -8035,7 +8380,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
@@ -8047,22 +8392,22 @@
         <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F16" t="s">
         <v>39</v>
       </c>
       <c r="G16" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H16" t="s">
         <v>39</v>
       </c>
       <c r="I16" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J16" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K16" t="s">
         <v>39</v>
@@ -8073,7 +8418,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
@@ -8085,22 +8430,22 @@
         <v>39</v>
       </c>
       <c r="E17" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="F17" t="s">
         <v>39</v>
       </c>
       <c r="G17" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H17" t="s">
         <v>39</v>
       </c>
       <c r="I17" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J17" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K17" t="s">
         <v>39</v>
@@ -8111,7 +8456,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B18" t="s">
         <v>6</v>
@@ -8123,22 +8468,22 @@
         <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="F18" t="s">
         <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H18" t="s">
         <v>39</v>
       </c>
       <c r="I18" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J18" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K18" t="s">
         <v>39</v>
@@ -8149,7 +8494,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
@@ -8161,22 +8506,22 @@
         <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="F19" t="s">
         <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H19" t="s">
         <v>39</v>
       </c>
       <c r="I19" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J19" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K19" t="s">
         <v>39</v>
@@ -8187,7 +8532,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
@@ -8199,22 +8544,22 @@
         <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="F20" t="s">
         <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H20" t="s">
         <v>39</v>
       </c>
       <c r="I20" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="J20" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K20" t="s">
         <v>39</v>
@@ -8225,7 +8570,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s">
         <v>6</v>
@@ -8237,22 +8582,22 @@
         <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="F21" t="s">
         <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H21" t="s">
         <v>39</v>
       </c>
       <c r="I21" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="J21" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K21" t="s">
         <v>39</v>
@@ -8263,10 +8608,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C22" t="s">
         <v>45</v>
@@ -8275,22 +8620,22 @@
         <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F22" t="s">
         <v>39</v>
       </c>
       <c r="G22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H22" t="s">
         <v>39</v>
       </c>
       <c r="I22" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="J22" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K22" t="s">
         <v>39</v>
@@ -8301,10 +8646,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B23" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C23" t="s">
         <v>45</v>
@@ -8313,22 +8658,22 @@
         <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F23" t="s">
         <v>39</v>
       </c>
       <c r="G23" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H23" t="s">
         <v>39</v>
       </c>
       <c r="I23" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J23" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K23" t="s">
         <v>39</v>
@@ -8339,7 +8684,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
@@ -8351,22 +8696,22 @@
         <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F24" t="s">
         <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H24" t="s">
         <v>39</v>
       </c>
       <c r="I24" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="J24" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K24" t="s">
         <v>39</v>
@@ -8377,7 +8722,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
@@ -8389,22 +8734,22 @@
         <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F25" t="s">
         <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H25" t="s">
         <v>39</v>
       </c>
       <c r="I25" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="J25" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K25" t="s">
         <v>39</v>
@@ -8415,7 +8760,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
@@ -8427,22 +8772,22 @@
         <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="F26" t="s">
         <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H26" t="s">
         <v>39</v>
       </c>
       <c r="I26" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="J26" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K26" t="s">
         <v>39</v>
@@ -8456,7 +8801,7 @@
         <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C27" t="s">
         <v>45</v>
@@ -8465,22 +8810,22 @@
         <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="F27" t="s">
         <v>39</v>
       </c>
       <c r="G27" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H27" t="s">
         <v>39</v>
       </c>
       <c r="I27" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="J27" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K27" t="s">
         <v>39</v>
@@ -8491,10 +8836,10 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B28" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
@@ -8503,22 +8848,22 @@
         <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F28" t="s">
         <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H28" t="s">
         <v>39</v>
       </c>
       <c r="I28" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J28" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K28" t="s">
         <v>39</v>
@@ -8529,10 +8874,10 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B29" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C29" t="s">
         <v>45</v>
@@ -8541,22 +8886,22 @@
         <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F29" t="s">
         <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H29" t="s">
         <v>39</v>
       </c>
       <c r="I29" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J29" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K29" t="s">
         <v>39</v>
@@ -8567,10 +8912,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B30" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
@@ -8579,22 +8924,22 @@
         <v>39</v>
       </c>
       <c r="E30" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F30" t="s">
         <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H30" t="s">
         <v>39</v>
       </c>
       <c r="I30" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J30" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K30" t="s">
         <v>39</v>
@@ -8605,10 +8950,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B31" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C31" t="s">
         <v>45</v>
@@ -8617,22 +8962,22 @@
         <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F31" t="s">
         <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H31" t="s">
         <v>39</v>
       </c>
       <c r="I31" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J31" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K31" t="s">
         <v>39</v>
@@ -8643,10 +8988,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B32" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C32" t="s">
         <v>45</v>
@@ -8655,22 +9000,22 @@
         <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="F32" t="s">
         <v>39</v>
       </c>
       <c r="G32" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H32" t="s">
         <v>39</v>
       </c>
       <c r="I32" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="J32" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K32" t="s">
         <v>39</v>
@@ -8681,10 +9026,10 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B33" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C33" t="s">
         <v>45</v>
@@ -8693,22 +9038,22 @@
         <v>39</v>
       </c>
       <c r="E33" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="F33" t="s">
         <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H33" t="s">
         <v>39</v>
       </c>
       <c r="I33" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="J33" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K33" t="s">
         <v>39</v>
@@ -8719,7 +9064,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
@@ -8731,22 +9076,22 @@
         <v>39</v>
       </c>
       <c r="E34" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F34" t="s">
         <v>39</v>
       </c>
       <c r="G34" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H34" t="s">
         <v>39</v>
       </c>
       <c r="I34" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J34" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K34" t="s">
         <v>39</v>
@@ -8757,7 +9102,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
@@ -8769,22 +9114,22 @@
         <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="F35" t="s">
         <v>39</v>
       </c>
       <c r="G35" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H35" t="s">
         <v>39</v>
       </c>
       <c r="I35" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="J35" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="K35" t="s">
         <v>39</v>
@@ -8795,7 +9140,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
@@ -8807,19 +9152,19 @@
         <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="F36" t="s">
         <v>39</v>
       </c>
       <c r="G36" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H36" t="s">
         <v>39</v>
       </c>
       <c r="I36" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="J36" t="s">
         <v>43</v>
@@ -8833,7 +9178,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
@@ -8845,19 +9190,19 @@
         <v>39</v>
       </c>
       <c r="E37" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="F37" t="s">
         <v>39</v>
       </c>
       <c r="G37" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H37" t="s">
         <v>39</v>
       </c>
       <c r="I37" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="J37" t="s">
         <v>43</v>
@@ -8871,10 +9216,10 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B38" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C38" t="s">
         <v>45</v>
@@ -8883,22 +9228,22 @@
         <v>39</v>
       </c>
       <c r="E38" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="F38" t="s">
         <v>39</v>
       </c>
       <c r="G38" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H38" t="s">
         <v>39</v>
       </c>
       <c r="I38" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="J38" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="K38" t="s">
         <v>39</v>
@@ -8921,13 +9266,13 @@
         <v>39</v>
       </c>
       <c r="E39" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="F39" t="s">
         <v>39</v>
       </c>
       <c r="G39" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H39" t="s">
         <v>39</v>
@@ -9186,7 +9531,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L252"/>
+  <dimension ref="A1:M252"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9197,7 +9542,7 @@
     <col min="6" max="12" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -9234,10 +9579,13 @@
       <c r="L1" t="s">
         <v>67</v>
       </c>
+      <c r="M1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -9249,22 +9597,22 @@
         <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F2" t="s">
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H2" t="s">
         <v>39</v>
       </c>
       <c r="I2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="J2" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="K2" t="s">
         <v>39</v>
@@ -9275,7 +9623,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -9287,22 +9635,22 @@
         <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F3" t="s">
         <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H3" t="s">
         <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="J3" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="K3" t="s">
         <v>39</v>
@@ -9313,7 +9661,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -9325,22 +9673,22 @@
         <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F4" t="s">
         <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H4" t="s">
         <v>39</v>
       </c>
       <c r="I4" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="J4" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -9351,7 +9699,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -9363,22 +9711,22 @@
         <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F5" t="s">
         <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H5" t="s">
         <v>39</v>
       </c>
       <c r="I5" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="J5" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="K5" t="s">
         <v>39</v>
@@ -9389,7 +9737,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -9401,22 +9749,22 @@
         <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H6" t="s">
         <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="J6" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="K6" t="s">
         <v>39</v>
@@ -9427,7 +9775,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -9439,22 +9787,22 @@
         <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H7" t="s">
         <v>39</v>
       </c>
       <c r="I7" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="J7" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="K7" t="s">
         <v>39</v>
@@ -9465,7 +9813,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -9477,22 +9825,22 @@
         <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F8" t="s">
         <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H8" t="s">
         <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="J8" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="K8" t="s">
         <v>39</v>
@@ -9512,13 +9860,13 @@
         <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="F9" t="s">
         <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" t="s">
         <v>39</v>
@@ -9538,7 +9886,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
@@ -9550,22 +9898,22 @@
         <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="F10" t="s">
         <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H10" t="s">
         <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J10" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K10" t="s">
         <v>39</v>
@@ -9576,7 +9924,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -9588,22 +9936,22 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F11" t="s">
         <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H11" t="s">
         <v>39</v>
       </c>
       <c r="I11" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="J11" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="K11" t="s">
         <v>39</v>
@@ -9614,7 +9962,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -9626,19 +9974,19 @@
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H12" t="s">
         <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="J12" t="s">
         <v>43</v>
@@ -9652,7 +10000,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -9664,22 +10012,22 @@
         <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H13" t="s">
         <v>39</v>
       </c>
       <c r="I13" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="J13" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K13" t="s">
         <v>39</v>
@@ -9690,7 +10038,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
@@ -9702,22 +10050,22 @@
         <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F14">
         <v>-0.5</v>
       </c>
       <c r="G14" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H14" t="s">
         <v>39</v>
       </c>
       <c r="I14" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J14" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K14" t="s">
         <v>39</v>
@@ -9728,7 +10076,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
@@ -9740,22 +10088,22 @@
         <v>39</v>
       </c>
       <c r="E15" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="F15" t="s">
         <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H15" t="s">
         <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J15" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K15" t="s">
         <v>39</v>
@@ -9766,10 +10114,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B16" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C16" t="s">
         <v>51</v>
@@ -9778,22 +10126,22 @@
         <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="F16" t="s">
         <v>39</v>
       </c>
       <c r="G16" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H16" t="s">
         <v>39</v>
       </c>
       <c r="I16" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="J16" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="K16" t="s">
         <v>39</v>
@@ -9804,7 +10152,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
@@ -9816,22 +10164,22 @@
         <v>39</v>
       </c>
       <c r="E17" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="F17">
         <v>-0.5</v>
       </c>
       <c r="G17" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H17" t="s">
         <v>39</v>
       </c>
       <c r="I17" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J17" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K17" t="s">
         <v>39</v>
@@ -9842,7 +10190,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -9854,22 +10202,22 @@
         <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="F18" t="s">
         <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H18" t="s">
         <v>39</v>
       </c>
       <c r="I18" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J18" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K18" t="s">
         <v>39</v>
@@ -9883,7 +10231,7 @@
         <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C19" t="s">
         <v>51</v>
@@ -9892,13 +10240,13 @@
         <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="F19" t="s">
         <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H19" t="s">
         <v>39</v>
@@ -9907,7 +10255,7 @@
         <v>49</v>
       </c>
       <c r="J19" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="K19" t="s">
         <v>39</v>
@@ -9918,7 +10266,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
@@ -9930,22 +10278,22 @@
         <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F20" t="s">
         <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H20" t="s">
         <v>39</v>
       </c>
       <c r="I20" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="J20" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="K20" t="s">
         <v>39</v>
@@ -9956,7 +10304,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s">
         <v>2</v>
@@ -9968,22 +10316,22 @@
         <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F21" t="s">
         <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H21" t="s">
         <v>39</v>
       </c>
       <c r="I21" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J21" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K21" t="s">
         <v>39</v>
@@ -10006,13 +10354,13 @@
         <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F22" t="s">
         <v>39</v>
       </c>
       <c r="G22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H22" t="s">
         <v>39</v>
@@ -10021,7 +10369,7 @@
         <v>43</v>
       </c>
       <c r="J22" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="K22" t="s">
         <v>39</v>
@@ -10032,7 +10380,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B23" t="s">
         <v>6</v>
@@ -10044,22 +10392,22 @@
         <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="F23">
         <v>-6</v>
       </c>
       <c r="G23" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H23" t="s">
         <v>39</v>
       </c>
       <c r="I23" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J23" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K23" t="s">
         <v>39</v>
@@ -10070,7 +10418,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s">
         <v>2</v>
@@ -10082,22 +10430,22 @@
         <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F24" t="s">
         <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H24" t="s">
         <v>39</v>
       </c>
       <c r="I24" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J24" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K24" t="s">
         <v>39</v>
@@ -10108,7 +10456,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B25" t="s">
         <v>2</v>
@@ -10120,22 +10468,22 @@
         <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F25" t="s">
         <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H25" t="s">
         <v>39</v>
       </c>
       <c r="I25" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J25" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K25" t="s">
         <v>39</v>
@@ -10146,7 +10494,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B26" t="s">
         <v>2</v>
@@ -10158,22 +10506,22 @@
         <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F26" t="s">
         <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H26" t="s">
         <v>39</v>
       </c>
       <c r="I26" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="J26" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K26" t="s">
         <v>39</v>
@@ -10184,7 +10532,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
@@ -10196,22 +10544,22 @@
         <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="F27" t="s">
         <v>39</v>
       </c>
       <c r="G27" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H27" t="s">
         <v>39</v>
       </c>
       <c r="I27" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J27" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K27" t="s">
         <v>39</v>
@@ -10222,7 +10570,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B28" t="s">
         <v>4</v>
@@ -10234,22 +10582,22 @@
         <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F28" t="s">
         <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H28" t="s">
         <v>39</v>
       </c>
       <c r="I28" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J28" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K28" t="s">
         <v>39</v>
@@ -10260,7 +10608,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B29" t="s">
         <v>6</v>
@@ -10272,22 +10620,22 @@
         <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F29" t="s">
         <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H29" t="s">
         <v>39</v>
       </c>
       <c r="I29" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="J29" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="K29" t="s">
         <v>39</v>
@@ -10298,7 +10646,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
@@ -10310,22 +10658,22 @@
         <v>39</v>
       </c>
       <c r="E30" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F30" t="s">
         <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H30" t="s">
         <v>39</v>
       </c>
       <c r="I30" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J30" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K30" t="s">
         <v>39</v>
@@ -10336,7 +10684,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B31" t="s">
         <v>2</v>
@@ -10348,22 +10696,22 @@
         <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F31" t="s">
         <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H31" t="s">
         <v>39</v>
       </c>
       <c r="I31" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J31" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K31" t="s">
         <v>39</v>
@@ -10374,7 +10722,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -10386,19 +10734,19 @@
         <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="F32" t="s">
         <v>39</v>
       </c>
       <c r="G32" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H32" t="s">
         <v>39</v>
       </c>
       <c r="I32" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="J32" t="s">
         <v>43</v>
@@ -10412,7 +10760,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
@@ -10424,22 +10772,22 @@
         <v>39</v>
       </c>
       <c r="E33" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F33" t="s">
         <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H33" t="s">
         <v>39</v>
       </c>
       <c r="I33" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J33" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K33" t="s">
         <v>39</v>
@@ -10450,7 +10798,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B34" t="s">
         <v>6</v>
@@ -10462,22 +10810,22 @@
         <v>39</v>
       </c>
       <c r="E34" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="F34">
         <v>-4</v>
       </c>
       <c r="G34" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H34" t="s">
         <v>39</v>
       </c>
       <c r="I34" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J34" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K34" t="s">
         <v>39</v>
@@ -10488,7 +10836,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
@@ -10500,22 +10848,22 @@
         <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="F35">
         <v>-4</v>
       </c>
       <c r="G35" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H35" t="s">
         <v>39</v>
       </c>
       <c r="I35" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J35" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K35" t="s">
         <v>39</v>
@@ -10526,7 +10874,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B36" t="s">
         <v>6</v>
@@ -10538,22 +10886,22 @@
         <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F36">
         <v>-2</v>
       </c>
       <c r="G36" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H36" t="s">
         <v>39</v>
       </c>
       <c r="I36" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J36" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K36" t="s">
         <v>39</v>
@@ -10564,7 +10912,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
@@ -10576,22 +10924,22 @@
         <v>39</v>
       </c>
       <c r="E37" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F37">
         <v>-2</v>
       </c>
       <c r="G37" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H37" t="s">
         <v>39</v>
       </c>
       <c r="I37" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J37" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K37" t="s">
         <v>39</v>
@@ -10602,7 +10950,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B38" t="s">
         <v>6</v>
@@ -10614,22 +10962,22 @@
         <v>39</v>
       </c>
       <c r="E38" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="F38">
         <v>-2</v>
       </c>
       <c r="G38" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H38" t="s">
         <v>39</v>
       </c>
       <c r="I38" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J38" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K38" t="s">
         <v>39</v>
@@ -10640,7 +10988,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
@@ -10652,22 +11000,22 @@
         <v>39</v>
       </c>
       <c r="E39" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="F39">
         <v>-4</v>
       </c>
       <c r="G39" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H39" t="s">
         <v>39</v>
       </c>
       <c r="I39" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J39" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K39" t="s">
         <v>39</v>
@@ -10678,7 +11026,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
@@ -10690,22 +11038,22 @@
         <v>39</v>
       </c>
       <c r="E40" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="F40">
         <v>-2</v>
       </c>
       <c r="G40" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H40" t="s">
         <v>39</v>
       </c>
       <c r="I40" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J40" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K40" t="s">
         <v>39</v>
@@ -10716,7 +11064,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
@@ -10728,22 +11076,22 @@
         <v>39</v>
       </c>
       <c r="E41" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="F41">
         <v>-2</v>
       </c>
       <c r="G41" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H41" t="s">
         <v>39</v>
       </c>
       <c r="I41" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="J41" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K41" t="s">
         <v>39</v>
@@ -10754,7 +11102,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B42" t="s">
         <v>6</v>
@@ -10766,22 +11114,22 @@
         <v>39</v>
       </c>
       <c r="E42" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="F42">
         <v>-4</v>
       </c>
       <c r="G42" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H42" t="s">
         <v>39</v>
       </c>
       <c r="I42" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="J42" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K42" t="s">
         <v>39</v>
@@ -10792,10 +11140,10 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B43" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C43" t="s">
         <v>51</v>
@@ -10804,22 +11152,22 @@
         <v>39</v>
       </c>
       <c r="E43" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="F43" t="s">
         <v>39</v>
       </c>
       <c r="G43" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H43" t="s">
         <v>39</v>
       </c>
       <c r="I43" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="J43" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="K43" t="s">
         <v>39</v>
@@ -10830,10 +11178,10 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B44" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C44" t="s">
         <v>51</v>
@@ -10842,22 +11190,22 @@
         <v>39</v>
       </c>
       <c r="E44" t="s">
+        <v>310</v>
+      </c>
+      <c r="F44" t="s">
+        <v>39</v>
+      </c>
+      <c r="G44" t="s">
+        <v>188</v>
+      </c>
+      <c r="H44" t="s">
+        <v>39</v>
+      </c>
+      <c r="I44" t="s">
         <v>302</v>
       </c>
-      <c r="F44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G44" t="s">
-        <v>183</v>
-      </c>
-      <c r="H44" t="s">
-        <v>39</v>
-      </c>
-      <c r="I44" t="s">
-        <v>294</v>
-      </c>
       <c r="J44" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="K44" t="s">
         <v>39</v>
@@ -10868,10 +11216,10 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B45" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C45" t="s">
         <v>51</v>
@@ -10880,22 +11228,22 @@
         <v>39</v>
       </c>
       <c r="E45" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
       </c>
       <c r="G45" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H45" t="s">
         <v>39</v>
       </c>
       <c r="I45" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="J45" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="K45" t="s">
         <v>39</v>
@@ -10906,10 +11254,10 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B46" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C46" t="s">
         <v>51</v>
@@ -10918,22 +11266,22 @@
         <v>39</v>
       </c>
       <c r="E46" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="F46" t="s">
         <v>39</v>
       </c>
       <c r="G46" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H46" t="s">
         <v>39</v>
       </c>
       <c r="I46" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="J46" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="K46" t="s">
         <v>39</v>
@@ -10944,10 +11292,10 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B47" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C47" t="s">
         <v>51</v>
@@ -10956,22 +11304,22 @@
         <v>39</v>
       </c>
       <c r="E47" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="F47" t="s">
         <v>39</v>
       </c>
       <c r="G47" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H47" t="s">
         <v>39</v>
       </c>
       <c r="I47" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="J47" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="K47" t="s">
         <v>39</v>
@@ -10982,10 +11330,10 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B48" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C48" t="s">
         <v>51</v>
@@ -10994,22 +11342,22 @@
         <v>39</v>
       </c>
       <c r="E48" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="F48" t="s">
         <v>39</v>
       </c>
       <c r="G48" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H48" t="s">
         <v>39</v>
       </c>
       <c r="I48" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="J48" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="K48" t="s">
         <v>39</v>
@@ -11020,10 +11368,10 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B49" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C49" t="s">
         <v>51</v>
@@ -11032,22 +11380,22 @@
         <v>39</v>
       </c>
       <c r="E49" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="F49" t="s">
         <v>39</v>
       </c>
       <c r="G49" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H49" t="s">
         <v>39</v>
       </c>
       <c r="I49" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="J49" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="K49" t="s">
         <v>39</v>
@@ -11058,10 +11406,10 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B50" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C50" t="s">
         <v>51</v>
@@ -11070,22 +11418,22 @@
         <v>39</v>
       </c>
       <c r="E50" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="F50" t="s">
         <v>39</v>
       </c>
       <c r="G50" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H50" t="s">
         <v>39</v>
       </c>
       <c r="I50" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="J50" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="K50" t="s">
         <v>39</v>
@@ -11096,10 +11444,10 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B51" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C51" t="s">
         <v>51</v>
@@ -11108,22 +11456,22 @@
         <v>39</v>
       </c>
       <c r="E51" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="F51" t="s">
         <v>39</v>
       </c>
       <c r="G51" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H51" t="s">
         <v>39</v>
       </c>
       <c r="I51" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="J51" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="K51" t="s">
         <v>39</v>
@@ -11146,13 +11494,13 @@
         <v>39</v>
       </c>
       <c r="E52" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F52" t="s">
         <v>39</v>
       </c>
       <c r="G52" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H52" t="s">
         <v>39</v>

--- a/src/data/FML-Data.xlsx
+++ b/src/data/FML-Data.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2813" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2705" uniqueCount="316">
   <si>
     <t>Name</t>
   </si>
@@ -578,292 +578,280 @@
     <t>2026-08-18</t>
   </si>
   <si>
+    <t>FNS-44</t>
+  </si>
+  <si>
+    <t>Players</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>FNS-45</t>
+  </si>
+  <si>
+    <t>Support Staff</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>FNS-46</t>
+  </si>
+  <si>
+    <t>player Profile</t>
+  </si>
+  <si>
+    <t>In Dev</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>Top Menu, Bottom Menu</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>Footer</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>Both Standings css</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>HP News</t>
+  </si>
+  <si>
+    <t>HP Videos</t>
+  </si>
+  <si>
+    <t>HP Photos</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>News Listing &amp; Detail</t>
+  </si>
+  <si>
+    <t>Video Listing and Detail</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>Photos Listing &amp; Detail</t>
+  </si>
+  <si>
+    <t>FNS-29</t>
+  </si>
+  <si>
+    <t>Terms and Conditions</t>
+  </si>
+  <si>
+    <t>Ready for QA</t>
+  </si>
+  <si>
+    <t>FNS-28</t>
+  </si>
+  <si>
+    <t>Privacy Policy</t>
+  </si>
+  <si>
+    <t>FNS-31</t>
+  </si>
+  <si>
+    <t>Thank you</t>
+  </si>
+  <si>
+    <t>FNS-30</t>
+  </si>
+  <si>
+    <t>FNS-32</t>
+  </si>
+  <si>
+    <t>Partnership Framework</t>
+  </si>
+  <si>
+    <t>FNS-24</t>
+  </si>
+  <si>
+    <t>Where to Watch</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>FNS-25</t>
+  </si>
+  <si>
+    <t>Womens t20 exhibition</t>
+  </si>
+  <si>
+    <t>FNS-23</t>
+  </si>
+  <si>
+    <t>Wallpapers</t>
+  </si>
+  <si>
+    <t>FNS-33</t>
+  </si>
+  <si>
+    <t>Registration form (popup)</t>
+  </si>
+  <si>
+    <t>Code Review</t>
+  </si>
+  <si>
+    <t>FNS-34</t>
+  </si>
+  <si>
+    <t>FNS-35</t>
+  </si>
+  <si>
+    <t>Contact Us</t>
+  </si>
+  <si>
+    <t>FNS-36</t>
+  </si>
+  <si>
+    <t>FNS-168</t>
+  </si>
+  <si>
+    <t>Boundary Builder page + form</t>
+  </si>
+  <si>
+    <t>FNS-20</t>
+  </si>
+  <si>
+    <t>Videos - Listing</t>
+  </si>
+  <si>
+    <t>FNS-18</t>
+  </si>
+  <si>
+    <t>Photos - Listing</t>
+  </si>
+  <si>
     <t>2026-08-19</t>
   </si>
   <si>
-    <t>FREE Due Blocker</t>
-  </si>
-  <si>
-    <t>pending</t>
-  </si>
-  <si>
-    <t>Wf fixses</t>
-  </si>
-  <si>
-    <t>FNS-44</t>
-  </si>
-  <si>
-    <t>Players</t>
-  </si>
-  <si>
-    <t>2026-08-24</t>
-  </si>
-  <si>
-    <t>2026-08-25</t>
-  </si>
-  <si>
-    <t>FNS-45</t>
-  </si>
-  <si>
-    <t>Support Staff</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>FNS-46</t>
-  </si>
-  <si>
-    <t>player Profile</t>
-  </si>
-  <si>
-    <t>In Dev</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
+    <t>FNS-16</t>
+  </si>
+  <si>
+    <t>News - Listing</t>
+  </si>
+  <si>
+    <t>FNS-19</t>
+  </si>
+  <si>
+    <t>Photos - Detail</t>
+  </si>
+  <si>
+    <t>FNS-17</t>
+  </si>
+  <si>
+    <t>News - Detail</t>
+  </si>
+  <si>
+    <t>FNS-21</t>
+  </si>
+  <si>
+    <t>Videos - Detail</t>
+  </si>
+  <si>
+    <t>FNS-43</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>Player registration embed</t>
+  </si>
+  <si>
+    <t>HP Static Banner</t>
+  </si>
+  <si>
+    <t>Team strip</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>T&amp;C page</t>
+  </si>
+  <si>
+    <t>About us</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>Hall of fame</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Buy Tickets banner</t>
+  </si>
+  <si>
+    <t>Islander Banner</t>
+  </si>
+  <si>
+    <t>Esports</t>
+  </si>
+  <si>
+    <t>Social Hub</t>
+  </si>
+  <si>
+    <t>Esports Player Profile</t>
+  </si>
+  <si>
+    <t>Ticket T&amp;C</t>
+  </si>
+  <si>
+    <t>Community</t>
+  </si>
+  <si>
+    <t>Safeguarding</t>
+  </si>
+  <si>
+    <t>Cookie Policy</t>
+  </si>
+  <si>
+    <t>Error Page</t>
+  </si>
+  <si>
+    <t>Siddharth N</t>
+  </si>
+  <si>
+    <t>Header &amp; Footer</t>
+  </si>
+  <si>
+    <t>Standings</t>
+  </si>
+  <si>
+    <t>Squad</t>
+  </si>
+  <si>
+    <t>External links - 1 ticket maybe</t>
+  </si>
+  <si>
+    <t>Buffer Due to New Module</t>
   </si>
   <si>
     <t>Fixses</t>
-  </si>
-  <si>
-    <t>2026-09-02</t>
-  </si>
-  <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
-    <t>2026-09-03</t>
-  </si>
-  <si>
-    <t>Support</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>Top Menu, Bottom Menu</t>
-  </si>
-  <si>
-    <t>Footer</t>
-  </si>
-  <si>
-    <t>2026-09-08</t>
-  </si>
-  <si>
-    <t>Both Standings css</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>HP News</t>
-  </si>
-  <si>
-    <t>HP Videos</t>
-  </si>
-  <si>
-    <t>HP Photos</t>
-  </si>
-  <si>
-    <t>2026-09-10</t>
-  </si>
-  <si>
-    <t>News Listing &amp; Detail</t>
-  </si>
-  <si>
-    <t>Video Listing and Detail</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
-  </si>
-  <si>
-    <t>Photos Listing &amp; Detail</t>
-  </si>
-  <si>
-    <t>FNS-29</t>
-  </si>
-  <si>
-    <t>Terms and Conditions</t>
-  </si>
-  <si>
-    <t>Ready for QA</t>
-  </si>
-  <si>
-    <t>FNS-28</t>
-  </si>
-  <si>
-    <t>Privacy Policy</t>
-  </si>
-  <si>
-    <t>FNS-31</t>
-  </si>
-  <si>
-    <t>Thank you</t>
-  </si>
-  <si>
-    <t>FNS-30</t>
-  </si>
-  <si>
-    <t>FNS-32</t>
-  </si>
-  <si>
-    <t>Partnership Framework</t>
-  </si>
-  <si>
-    <t>FNS-24</t>
-  </si>
-  <si>
-    <t>Where to Watch</t>
-  </si>
-  <si>
-    <t>FNS-25</t>
-  </si>
-  <si>
-    <t>Womens t20 exhibition</t>
-  </si>
-  <si>
-    <t>FNS-23</t>
-  </si>
-  <si>
-    <t>Wallpapers</t>
-  </si>
-  <si>
-    <t>FNS-33</t>
-  </si>
-  <si>
-    <t>Registration form (popup)</t>
-  </si>
-  <si>
-    <t>Code Review</t>
-  </si>
-  <si>
-    <t>FNS-34</t>
-  </si>
-  <si>
-    <t>FNS-35</t>
-  </si>
-  <si>
-    <t>Contact Us</t>
-  </si>
-  <si>
-    <t>FNS-36</t>
-  </si>
-  <si>
-    <t>FNS-168</t>
-  </si>
-  <si>
-    <t>Boundary Builder page + form</t>
-  </si>
-  <si>
-    <t>Unit testing fixses of all form</t>
-  </si>
-  <si>
-    <t>FNS-20</t>
-  </si>
-  <si>
-    <t>Videos - Listing</t>
-  </si>
-  <si>
-    <t>FNS-18</t>
-  </si>
-  <si>
-    <t>Photos - Listing</t>
-  </si>
-  <si>
-    <t>FNS-16</t>
-  </si>
-  <si>
-    <t>News - Listing</t>
-  </si>
-  <si>
-    <t>FNS-19</t>
-  </si>
-  <si>
-    <t>Photos - Detail</t>
-  </si>
-  <si>
-    <t>FNS-17</t>
-  </si>
-  <si>
-    <t>News - Detail</t>
-  </si>
-  <si>
-    <t>FNS-21</t>
-  </si>
-  <si>
-    <t>Videos - Detail</t>
-  </si>
-  <si>
-    <t>FNS-43</t>
-  </si>
-  <si>
-    <t>Player registration embed</t>
-  </si>
-  <si>
-    <t>HP Static Banner</t>
-  </si>
-  <si>
-    <t>Team strip</t>
-  </si>
-  <si>
-    <t>T&amp;C page</t>
-  </si>
-  <si>
-    <t>About us</t>
-  </si>
-  <si>
-    <t>Hall of fame</t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>Buy Tickets banner</t>
-  </si>
-  <si>
-    <t>Islander Banner</t>
-  </si>
-  <si>
-    <t>Esports</t>
-  </si>
-  <si>
-    <t>Social Hub</t>
-  </si>
-  <si>
-    <t>Esports Player Profile</t>
-  </si>
-  <si>
-    <t>Ticket T&amp;C</t>
-  </si>
-  <si>
-    <t>Community</t>
-  </si>
-  <si>
-    <t>Safeguarding</t>
-  </si>
-  <si>
-    <t>Cookie Policy</t>
-  </si>
-  <si>
-    <t>Error Page</t>
-  </si>
-  <si>
-    <t>Siddharth N</t>
-  </si>
-  <si>
-    <t>Header &amp; Footer</t>
-  </si>
-  <si>
-    <t>Standings</t>
-  </si>
-  <si>
-    <t>Squad</t>
-  </si>
-  <si>
-    <t>External links - 1 ticket maybe</t>
-  </si>
-  <si>
-    <t>Buffer Due to New Module</t>
   </si>
   <si>
     <t>Aapla 12th Man Poll</t>
@@ -2076,7 +2064,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M264"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4708,206 +4696,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="203" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="204" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="209" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="210" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="213" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="214" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="217" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="218" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="219" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="221" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="224" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="225" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="226" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="227" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="230" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="231" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="232" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="233" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="234" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="240" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="241" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="242" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="243" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="244" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="245" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="246" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="247" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="248" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="249" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="250" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="251" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="252" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="253" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="254" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="255" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="256" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="257" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="258" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="259" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="260" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="261" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="262" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="263" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="264" spans="4:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="8">
     <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid date" error="Please enter a valid date." sqref="A10:A264">
@@ -5516,82 +5304,8 @@
         <v>160</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>186</v>
-      </c>
-      <c r="B13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" t="s">
-        <v>187</v>
-      </c>
-      <c r="F13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>188</v>
-      </c>
-      <c r="H13" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" t="s">
-        <v>186</v>
-      </c>
-      <c r="J13" t="s">
-        <v>186</v>
-      </c>
-      <c r="K13" t="s">
-        <v>39</v>
-      </c>
-      <c r="L13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>110</v>
-      </c>
-      <c r="B14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" t="s">
-        <v>189</v>
-      </c>
-      <c r="F14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" t="s">
-        <v>188</v>
-      </c>
-      <c r="H14" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" t="s">
-        <v>110</v>
-      </c>
-      <c r="J14" t="s">
-        <v>110</v>
-      </c>
-      <c r="K14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L14" t="s">
-        <v>39</v>
-      </c>
-    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
@@ -5685,10 +5399,10 @@
         <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E17" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F17" t="s">
         <v>39</v>
@@ -5703,7 +5417,7 @@
         <v>38</v>
       </c>
       <c r="J17" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K17" t="s">
         <v>39</v>
@@ -5717,7 +5431,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -5726,10 +5440,10 @@
         <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E18" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F18" t="s">
         <v>39</v>
@@ -5744,7 +5458,7 @@
         <v>38</v>
       </c>
       <c r="J18" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K18" t="s">
         <v>39</v>
@@ -5758,7 +5472,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
@@ -5849,10 +5563,10 @@
         <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E21" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F21" t="s">
         <v>39</v>
@@ -5881,7 +5595,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B22" t="s">
         <v>2</v>
@@ -5890,10 +5604,10 @@
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E22" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F22" t="s">
         <v>39</v>
@@ -5905,10 +5619,10 @@
         <v>39</v>
       </c>
       <c r="I22" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="J22" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="K22" t="s">
         <v>39</v>
@@ -5917,202 +5631,17 @@
         <v>39</v>
       </c>
       <c r="M22" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>200</v>
-      </c>
-      <c r="B23" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" t="s">
-        <v>201</v>
-      </c>
-      <c r="F23" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" t="s">
-        <v>188</v>
-      </c>
-      <c r="H23" t="s">
-        <v>39</v>
-      </c>
-      <c r="I23" t="s">
-        <v>110</v>
-      </c>
-      <c r="J23" t="s">
-        <v>202</v>
-      </c>
-      <c r="K23" t="s">
-        <v>39</v>
-      </c>
-      <c r="L23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>203</v>
-      </c>
-      <c r="B24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" t="s">
-        <v>201</v>
-      </c>
-      <c r="F24" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" t="s">
-        <v>188</v>
-      </c>
-      <c r="H24" t="s">
-        <v>39</v>
-      </c>
-      <c r="I24" t="s">
-        <v>110</v>
-      </c>
-      <c r="J24" t="s">
-        <v>202</v>
-      </c>
-      <c r="K24" t="s">
-        <v>39</v>
-      </c>
-      <c r="L24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>202</v>
-      </c>
-      <c r="B25" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" t="s">
-        <v>201</v>
-      </c>
-      <c r="F25" t="s">
-        <v>39</v>
-      </c>
-      <c r="G25" t="s">
-        <v>188</v>
-      </c>
-      <c r="H25" t="s">
-        <v>39</v>
-      </c>
-      <c r="I25" t="s">
-        <v>110</v>
-      </c>
-      <c r="J25" t="s">
-        <v>202</v>
-      </c>
-      <c r="K25" t="s">
-        <v>39</v>
-      </c>
-      <c r="L25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>204</v>
-      </c>
-      <c r="B26" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" t="s">
-        <v>205</v>
-      </c>
-      <c r="F26" t="s">
-        <v>39</v>
-      </c>
-      <c r="G26" t="s">
-        <v>188</v>
-      </c>
-      <c r="H26" t="s">
-        <v>39</v>
-      </c>
-      <c r="I26" t="s">
-        <v>204</v>
-      </c>
-      <c r="J26" t="s">
-        <v>204</v>
-      </c>
-      <c r="K26" t="s">
-        <v>39</v>
-      </c>
-      <c r="L26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" t="s">
-        <v>114</v>
-      </c>
-      <c r="F27" t="s">
-        <v>39</v>
-      </c>
-      <c r="G27" t="s">
-        <v>188</v>
-      </c>
-      <c r="H27" t="s">
-        <v>39</v>
-      </c>
-      <c r="I27" t="s">
-        <v>43</v>
-      </c>
-      <c r="J27" t="s">
-        <v>43</v>
-      </c>
-      <c r="K27" t="s">
-        <v>39</v>
-      </c>
-      <c r="L27" t="s">
-        <v>39</v>
-      </c>
-    </row>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B28" t="s">
         <v>2</v>
@@ -6124,22 +5653,22 @@
         <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="F28" t="s">
         <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H28" t="s">
         <v>39</v>
       </c>
       <c r="I28" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="J28" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K28" t="s">
         <v>39</v>
@@ -6150,7 +5679,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B29" t="s">
         <v>2</v>
@@ -6162,22 +5691,22 @@
         <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="F29" t="s">
         <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H29" t="s">
         <v>39</v>
       </c>
       <c r="I29" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="J29" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K29" t="s">
         <v>39</v>
@@ -6188,7 +5717,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B30" t="s">
         <v>2</v>
@@ -6200,22 +5729,22 @@
         <v>39</v>
       </c>
       <c r="E30" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="F30" t="s">
         <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H30" t="s">
         <v>39</v>
       </c>
       <c r="I30" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="J30" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="K30" t="s">
         <v>39</v>
@@ -6226,7 +5755,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B31" t="s">
         <v>2</v>
@@ -6238,7 +5767,7 @@
         <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="F31" t="s">
         <v>39</v>
@@ -6250,10 +5779,10 @@
         <v>39</v>
       </c>
       <c r="I31" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J31" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K31" t="s">
         <v>39</v>
@@ -6264,7 +5793,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B32" t="s">
         <v>2</v>
@@ -6276,7 +5805,7 @@
         <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="F32" t="s">
         <v>39</v>
@@ -6288,10 +5817,10 @@
         <v>39</v>
       </c>
       <c r="I32" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J32" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K32" t="s">
         <v>39</v>
@@ -6302,7 +5831,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B33" t="s">
         <v>2</v>
@@ -6314,22 +5843,22 @@
         <v>39</v>
       </c>
       <c r="E33" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="F33" t="s">
         <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H33" t="s">
         <v>39</v>
       </c>
       <c r="I33" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J33" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K33" t="s">
         <v>39</v>
@@ -6340,7 +5869,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B34" t="s">
         <v>2</v>
@@ -6352,33 +5881,33 @@
         <v>39</v>
       </c>
       <c r="E34" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="F34" t="s">
         <v>39</v>
       </c>
       <c r="G34" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H34" t="s">
         <v>39</v>
       </c>
       <c r="I34" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="J34" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K34" t="s">
         <v>39</v>
       </c>
       <c r="L34" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B35" t="s">
         <v>2</v>
@@ -6390,33 +5919,33 @@
         <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="F35" t="s">
         <v>39</v>
       </c>
       <c r="G35" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H35" t="s">
         <v>39</v>
       </c>
       <c r="I35" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="J35" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K35" t="s">
         <v>39</v>
       </c>
       <c r="L35" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B36" t="s">
         <v>2</v>
@@ -6428,33 +5957,33 @@
         <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="F36" t="s">
         <v>39</v>
       </c>
       <c r="G36" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H36" t="s">
         <v>39</v>
       </c>
       <c r="I36" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="J36" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="K36" t="s">
         <v>39</v>
       </c>
       <c r="L36" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
@@ -6463,10 +5992,10 @@
         <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="E37" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="F37" t="s">
         <v>39</v>
@@ -6478,24 +6007,24 @@
         <v>39</v>
       </c>
       <c r="I37" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J37" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="K37" t="s">
         <v>39</v>
       </c>
       <c r="L37" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M37" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B38" t="s">
         <v>6</v>
@@ -6504,10 +6033,10 @@
         <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="E38" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="F38" t="s">
         <v>39</v>
@@ -6519,10 +6048,10 @@
         <v>39</v>
       </c>
       <c r="I38" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J38" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="K38" t="s">
         <v>39</v>
@@ -6531,7 +6060,7 @@
         <v>39</v>
       </c>
       <c r="M38" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -6545,10 +6074,10 @@
         <v>40</v>
       </c>
       <c r="D39" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="E39" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="F39" t="s">
         <v>39</v>
@@ -6572,7 +6101,7 @@
         <v>39</v>
       </c>
       <c r="M39" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -6586,7 +6115,7 @@
         <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E40" t="s">
         <v>153</v>
@@ -6613,12 +6142,12 @@
         <v>39</v>
       </c>
       <c r="M40" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
@@ -6627,10 +6156,10 @@
         <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="E41" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="F41" t="s">
         <v>39</v>
@@ -6642,10 +6171,10 @@
         <v>39</v>
       </c>
       <c r="I41" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="J41" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="K41" t="s">
         <v>39</v>
@@ -6654,12 +6183,12 @@
         <v>39</v>
       </c>
       <c r="M41" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B42" t="s">
         <v>6</v>
@@ -6668,10 +6197,10 @@
         <v>40</v>
       </c>
       <c r="D42" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E42" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="F42" t="s">
         <v>39</v>
@@ -6683,10 +6212,10 @@
         <v>39</v>
       </c>
       <c r="I42" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="J42" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="K42" t="s">
         <v>39</v>
@@ -6700,7 +6229,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="B43" t="s">
         <v>6</v>
@@ -6709,10 +6238,10 @@
         <v>40</v>
       </c>
       <c r="D43" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E43" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="F43" t="s">
         <v>39</v>
@@ -6724,10 +6253,10 @@
         <v>39</v>
       </c>
       <c r="I43" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="J43" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="K43" t="s">
         <v>39</v>
@@ -6736,12 +6265,12 @@
         <v>39</v>
       </c>
       <c r="M43" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="B44" t="s">
         <v>6</v>
@@ -6750,10 +6279,10 @@
         <v>40</v>
       </c>
       <c r="D44" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="E44" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="F44" t="s">
         <v>39</v>
@@ -6765,10 +6294,10 @@
         <v>39</v>
       </c>
       <c r="I44" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="J44" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="K44" t="s">
         <v>39</v>
@@ -6777,12 +6306,12 @@
         <v>39</v>
       </c>
       <c r="M44" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
@@ -6791,10 +6320,10 @@
         <v>40</v>
       </c>
       <c r="D45" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="E45" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
@@ -6806,10 +6335,10 @@
         <v>39</v>
       </c>
       <c r="I45" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="J45" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K45" t="s">
         <v>39</v>
@@ -6818,12 +6347,12 @@
         <v>39</v>
       </c>
       <c r="M45" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
@@ -6832,7 +6361,7 @@
         <v>40</v>
       </c>
       <c r="D46" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E46" t="s">
         <v>39</v>
@@ -6847,10 +6376,10 @@
         <v>39</v>
       </c>
       <c r="I46" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="J46" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K46" t="s">
         <v>39</v>
@@ -6859,12 +6388,12 @@
         <v>39</v>
       </c>
       <c r="M46" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B47" t="s">
         <v>9</v>
@@ -6873,10 +6402,10 @@
         <v>40</v>
       </c>
       <c r="D47" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E47" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="F47" t="s">
         <v>39</v>
@@ -6888,10 +6417,10 @@
         <v>39</v>
       </c>
       <c r="I47" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J47" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="K47" t="s">
         <v>39</v>
@@ -6900,12 +6429,12 @@
         <v>39</v>
       </c>
       <c r="M47" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
@@ -6914,7 +6443,7 @@
         <v>40</v>
       </c>
       <c r="D48" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E48" t="s">
         <v>39</v>
@@ -6929,10 +6458,10 @@
         <v>39</v>
       </c>
       <c r="I48" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J48" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="K48" t="s">
         <v>39</v>
@@ -6941,7 +6470,7 @@
         <v>39</v>
       </c>
       <c r="M48" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -6955,10 +6484,10 @@
         <v>40</v>
       </c>
       <c r="D49" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E49" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="F49" t="s">
         <v>39</v>
@@ -6982,47 +6511,10 @@
         <v>39</v>
       </c>
       <c r="M49" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>196</v>
-      </c>
-      <c r="B50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" t="s">
-        <v>40</v>
-      </c>
-      <c r="D50" t="s">
-        <v>39</v>
-      </c>
-      <c r="E50" t="s">
-        <v>245</v>
-      </c>
-      <c r="F50" t="s">
-        <v>39</v>
-      </c>
-      <c r="G50" t="s">
-        <v>188</v>
-      </c>
-      <c r="H50" t="s">
-        <v>39</v>
-      </c>
-      <c r="I50" t="s">
-        <v>196</v>
-      </c>
-      <c r="J50" t="s">
-        <v>196</v>
-      </c>
-      <c r="K50" t="s">
-        <v>39</v>
-      </c>
-      <c r="L50" t="s">
-        <v>39</v>
-      </c>
-    </row>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>182</v>
@@ -7034,10 +6526,10 @@
         <v>40</v>
       </c>
       <c r="D51" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="E51" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="F51" t="s">
         <v>39</v>
@@ -7075,10 +6567,10 @@
         <v>40</v>
       </c>
       <c r="D52" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="E52" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="F52" t="s">
         <v>39</v>
@@ -7093,7 +6585,7 @@
         <v>182</v>
       </c>
       <c r="J52" t="s">
-        <v>186</v>
+        <v>241</v>
       </c>
       <c r="K52" t="s">
         <v>39</v>
@@ -7116,10 +6608,10 @@
         <v>40</v>
       </c>
       <c r="D53" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E53" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="F53" t="s">
         <v>39</v>
@@ -7148,7 +6640,7 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>186</v>
+        <v>241</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
@@ -7157,10 +6649,10 @@
         <v>40</v>
       </c>
       <c r="D54" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="E54" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="F54" t="s">
         <v>39</v>
@@ -7175,7 +6667,7 @@
         <v>182</v>
       </c>
       <c r="J54" t="s">
-        <v>186</v>
+        <v>241</v>
       </c>
       <c r="K54" t="s">
         <v>39</v>
@@ -7189,7 +6681,7 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>186</v>
+        <v>241</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
@@ -7198,10 +6690,10 @@
         <v>40</v>
       </c>
       <c r="D55" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="E55" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F55" t="s">
         <v>39</v>
@@ -7213,10 +6705,10 @@
         <v>39</v>
       </c>
       <c r="I55" t="s">
-        <v>186</v>
+        <v>241</v>
       </c>
       <c r="J55" t="s">
-        <v>186</v>
+        <v>241</v>
       </c>
       <c r="K55" t="s">
         <v>39</v>
@@ -7239,10 +6731,10 @@
         <v>40</v>
       </c>
       <c r="D56" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E56" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="F56" t="s">
         <v>39</v>
@@ -7269,47 +6761,10 @@
         <v>160</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>110</v>
-      </c>
-      <c r="B57" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" t="s">
-        <v>40</v>
-      </c>
-      <c r="D57" t="s">
-        <v>39</v>
-      </c>
-      <c r="E57" t="s">
-        <v>201</v>
-      </c>
-      <c r="F57" t="s">
-        <v>39</v>
-      </c>
-      <c r="G57" t="s">
-        <v>188</v>
-      </c>
-      <c r="H57" t="s">
-        <v>39</v>
-      </c>
-      <c r="I57" t="s">
-        <v>110</v>
-      </c>
-      <c r="J57" t="s">
-        <v>202</v>
-      </c>
-      <c r="K57" t="s">
-        <v>39</v>
-      </c>
-      <c r="L57" t="s">
-        <v>39</v>
-      </c>
-    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
@@ -7318,10 +6773,10 @@
         <v>40</v>
       </c>
       <c r="D58" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="E58" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="F58" t="s">
         <v>39</v>
@@ -7333,10 +6788,10 @@
         <v>39</v>
       </c>
       <c r="I58" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="J58" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K58" t="s">
         <v>39</v>
@@ -7350,7 +6805,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B59" t="s">
         <v>10</v>
@@ -7374,10 +6829,10 @@
         <v>39</v>
       </c>
       <c r="I59" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="J59" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K59" t="s">
         <v>39</v>
@@ -7388,7 +6843,7 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B60" t="s">
         <v>10</v>
@@ -7397,7 +6852,7 @@
         <v>40</v>
       </c>
       <c r="D60" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E60" t="s">
         <v>127</v>
@@ -7412,10 +6867,10 @@
         <v>39</v>
       </c>
       <c r="I60" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J60" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="K60" t="s">
         <v>39</v>
@@ -7424,7 +6879,7 @@
         <v>39</v>
       </c>
       <c r="M60" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -7438,7 +6893,7 @@
         <v>40</v>
       </c>
       <c r="D61" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E61" t="s">
         <v>127</v>
@@ -7453,10 +6908,10 @@
         <v>39</v>
       </c>
       <c r="I61" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J61" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="K61" t="s">
         <v>39</v>
@@ -7465,12 +6920,12 @@
         <v>39</v>
       </c>
       <c r="M61" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B62" t="s">
         <v>10</v>
@@ -7479,7 +6934,7 @@
         <v>40</v>
       </c>
       <c r="D62" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E62" t="s">
         <v>127</v>
@@ -7494,10 +6949,10 @@
         <v>39</v>
       </c>
       <c r="I62" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J62" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="K62" t="s">
         <v>39</v>
@@ -7506,209 +6961,209 @@
         <v>39</v>
       </c>
       <c r="M62" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="203" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="204" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="209" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="210" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="213" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="214" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="217" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="218" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="219" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="221" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="224" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="225" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="226" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="227" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="230" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="231" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="232" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="233" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="234" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="240" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="241" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="242" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="243" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="244" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="245" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="246" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="247" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="248" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="249" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="250" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="251" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="252" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="253" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="254" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="255" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="256" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="257" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="258" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="259" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="260" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="261" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="262" spans="4:4" x14ac:dyDescent="0.25"/>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="5:5" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="8">
     <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid date" error="Please enter a valid date." sqref="A10:A262">
@@ -7794,7 +7249,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M239"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -7848,7 +7303,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -7860,22 +7315,22 @@
         <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F2" t="s">
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H2" t="s">
         <v>39</v>
       </c>
       <c r="I2" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="J2" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="K2" t="s">
         <v>39</v>
@@ -7886,7 +7341,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -7898,22 +7353,22 @@
         <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="F3" t="s">
         <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H3" t="s">
         <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="J3" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="K3" t="s">
         <v>39</v>
@@ -7924,7 +7379,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -7936,22 +7391,22 @@
         <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="F4" t="s">
         <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H4" t="s">
         <v>39</v>
       </c>
       <c r="I4" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="J4" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -7962,7 +7417,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -7980,16 +7435,16 @@
         <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H5" t="s">
         <v>39</v>
       </c>
       <c r="I5" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="J5" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="K5" t="s">
         <v>39</v>
@@ -8000,7 +7455,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -8012,22 +7467,22 @@
         <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H6" t="s">
         <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="J6" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="K6" t="s">
         <v>39</v>
@@ -8038,7 +7493,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -8050,22 +7505,22 @@
         <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H7" t="s">
         <v>39</v>
       </c>
       <c r="I7" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="J7" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="K7" t="s">
         <v>39</v>
@@ -8076,7 +7531,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -8088,22 +7543,22 @@
         <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="F8" t="s">
         <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H8" t="s">
         <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="J8" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="K8" t="s">
         <v>39</v>
@@ -8126,13 +7581,13 @@
         <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F9" t="s">
         <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H9" t="s">
         <v>39</v>
@@ -8152,7 +7607,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
@@ -8164,22 +7619,22 @@
         <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F10" t="s">
         <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H10" t="s">
         <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="J10" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K10" t="s">
         <v>39</v>
@@ -8190,7 +7645,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -8202,22 +7657,22 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F11" t="s">
         <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H11" t="s">
         <v>39</v>
       </c>
       <c r="I11" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="J11" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K11" t="s">
         <v>39</v>
@@ -8228,7 +7683,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
@@ -8240,22 +7695,22 @@
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H12" t="s">
         <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="J12" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K12" t="s">
         <v>39</v>
@@ -8266,7 +7721,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
@@ -8278,22 +7733,22 @@
         <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H13" t="s">
         <v>39</v>
       </c>
       <c r="I13" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="J13" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="K13" t="s">
         <v>39</v>
@@ -8304,7 +7759,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
@@ -8316,22 +7771,22 @@
         <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F14" t="s">
         <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H14" t="s">
         <v>39</v>
       </c>
       <c r="I14" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J14" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K14" t="s">
         <v>39</v>
@@ -8342,7 +7797,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B15" t="s">
         <v>6</v>
@@ -8360,16 +7815,16 @@
         <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H15" t="s">
         <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J15" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K15" t="s">
         <v>39</v>
@@ -8380,7 +7835,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
@@ -8392,22 +7847,22 @@
         <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F16" t="s">
         <v>39</v>
       </c>
       <c r="G16" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H16" t="s">
         <v>39</v>
       </c>
       <c r="I16" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J16" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K16" t="s">
         <v>39</v>
@@ -8418,7 +7873,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
@@ -8430,22 +7885,22 @@
         <v>39</v>
       </c>
       <c r="E17" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F17" t="s">
         <v>39</v>
       </c>
       <c r="G17" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H17" t="s">
         <v>39</v>
       </c>
       <c r="I17" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="J17" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K17" t="s">
         <v>39</v>
@@ -8456,7 +7911,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s">
         <v>6</v>
@@ -8468,22 +7923,22 @@
         <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F18" t="s">
         <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H18" t="s">
         <v>39</v>
       </c>
       <c r="I18" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="J18" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K18" t="s">
         <v>39</v>
@@ -8494,7 +7949,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
@@ -8506,22 +7961,22 @@
         <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="F19" t="s">
         <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H19" t="s">
         <v>39</v>
       </c>
       <c r="I19" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="J19" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K19" t="s">
         <v>39</v>
@@ -8532,7 +7987,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
@@ -8544,22 +7999,22 @@
         <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="F20" t="s">
         <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H20" t="s">
         <v>39</v>
       </c>
       <c r="I20" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="J20" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="K20" t="s">
         <v>39</v>
@@ -8570,7 +8025,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s">
         <v>6</v>
@@ -8582,22 +8037,22 @@
         <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F21" t="s">
         <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H21" t="s">
         <v>39</v>
       </c>
       <c r="I21" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="J21" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="K21" t="s">
         <v>39</v>
@@ -8608,10 +8063,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C22" t="s">
         <v>45</v>
@@ -8620,22 +8075,22 @@
         <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F22" t="s">
         <v>39</v>
       </c>
       <c r="G22" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H22" t="s">
         <v>39</v>
       </c>
       <c r="I22" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="J22" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="K22" t="s">
         <v>39</v>
@@ -8646,10 +8101,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="B23" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C23" t="s">
         <v>45</v>
@@ -8658,22 +8113,22 @@
         <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F23" t="s">
         <v>39</v>
       </c>
       <c r="G23" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H23" t="s">
         <v>39</v>
       </c>
       <c r="I23" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="J23" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="K23" t="s">
         <v>39</v>
@@ -8684,7 +8139,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
@@ -8696,22 +8151,22 @@
         <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F24" t="s">
         <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H24" t="s">
         <v>39</v>
       </c>
       <c r="I24" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="J24" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="K24" t="s">
         <v>39</v>
@@ -8722,7 +8177,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
@@ -8734,22 +8189,22 @@
         <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F25" t="s">
         <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H25" t="s">
         <v>39</v>
       </c>
       <c r="I25" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="J25" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="K25" t="s">
         <v>39</v>
@@ -8760,7 +8215,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
@@ -8772,22 +8227,22 @@
         <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F26" t="s">
         <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H26" t="s">
         <v>39</v>
       </c>
       <c r="I26" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="J26" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="K26" t="s">
         <v>39</v>
@@ -8801,7 +8256,7 @@
         <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C27" t="s">
         <v>45</v>
@@ -8810,22 +8265,22 @@
         <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F27" t="s">
         <v>39</v>
       </c>
       <c r="G27" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H27" t="s">
         <v>39</v>
       </c>
       <c r="I27" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="J27" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="K27" t="s">
         <v>39</v>
@@ -8836,10 +8291,10 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B28" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
@@ -8848,22 +8303,22 @@
         <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>201</v>
+        <v>277</v>
       </c>
       <c r="F28" t="s">
         <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H28" t="s">
         <v>39</v>
       </c>
       <c r="I28" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="J28" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K28" t="s">
         <v>39</v>
@@ -8874,10 +8329,10 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B29" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C29" t="s">
         <v>45</v>
@@ -8886,22 +8341,22 @@
         <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>201</v>
+        <v>277</v>
       </c>
       <c r="F29" t="s">
         <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H29" t="s">
         <v>39</v>
       </c>
       <c r="I29" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="J29" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K29" t="s">
         <v>39</v>
@@ -8912,10 +8367,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B30" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
@@ -8924,22 +8379,22 @@
         <v>39</v>
       </c>
       <c r="E30" t="s">
-        <v>201</v>
+        <v>277</v>
       </c>
       <c r="F30" t="s">
         <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H30" t="s">
         <v>39</v>
       </c>
       <c r="I30" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="J30" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K30" t="s">
         <v>39</v>
@@ -8950,10 +8405,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B31" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C31" t="s">
         <v>45</v>
@@ -8968,16 +8423,16 @@
         <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H31" t="s">
         <v>39</v>
       </c>
       <c r="I31" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="J31" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K31" t="s">
         <v>39</v>
@@ -8988,10 +8443,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B32" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C32" t="s">
         <v>45</v>
@@ -9000,22 +8455,22 @@
         <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F32" t="s">
         <v>39</v>
       </c>
       <c r="G32" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H32" t="s">
         <v>39</v>
       </c>
       <c r="I32" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="J32" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="K32" t="s">
         <v>39</v>
@@ -9026,10 +8481,10 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B33" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C33" t="s">
         <v>45</v>
@@ -9038,22 +8493,22 @@
         <v>39</v>
       </c>
       <c r="E33" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F33" t="s">
         <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H33" t="s">
         <v>39</v>
       </c>
       <c r="I33" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="J33" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="K33" t="s">
         <v>39</v>
@@ -9064,7 +8519,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
@@ -9076,22 +8531,22 @@
         <v>39</v>
       </c>
       <c r="E34" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F34" t="s">
         <v>39</v>
       </c>
       <c r="G34" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H34" t="s">
         <v>39</v>
       </c>
       <c r="I34" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="J34" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="K34" t="s">
         <v>39</v>
@@ -9102,7 +8557,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
@@ -9114,22 +8569,22 @@
         <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F35" t="s">
         <v>39</v>
       </c>
       <c r="G35" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H35" t="s">
         <v>39</v>
       </c>
       <c r="I35" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="J35" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="K35" t="s">
         <v>39</v>
@@ -9140,7 +8595,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
@@ -9152,19 +8607,19 @@
         <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F36" t="s">
         <v>39</v>
       </c>
       <c r="G36" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H36" t="s">
         <v>39</v>
       </c>
       <c r="I36" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="J36" t="s">
         <v>43</v>
@@ -9178,7 +8633,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
@@ -9190,19 +8645,19 @@
         <v>39</v>
       </c>
       <c r="E37" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F37" t="s">
         <v>39</v>
       </c>
       <c r="G37" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H37" t="s">
         <v>39</v>
       </c>
       <c r="I37" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="J37" t="s">
         <v>43</v>
@@ -9216,10 +8671,10 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="B38" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C38" t="s">
         <v>45</v>
@@ -9228,22 +8683,22 @@
         <v>39</v>
       </c>
       <c r="E38" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F38" t="s">
         <v>39</v>
       </c>
       <c r="G38" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H38" t="s">
         <v>39</v>
       </c>
       <c r="I38" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="J38" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="K38" t="s">
         <v>39</v>
@@ -9266,13 +8721,13 @@
         <v>39</v>
       </c>
       <c r="E39" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F39" t="s">
         <v>39</v>
       </c>
       <c r="G39" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H39" t="s">
         <v>39</v>
@@ -9290,206 +8745,6 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="203" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="204" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="209" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="210" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="213" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="214" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="217" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="218" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="219" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="221" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="224" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="225" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="226" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="227" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="230" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="231" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="232" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="233" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="234" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="4:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="8">
     <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid date" error="Please enter a valid date." sqref="A10:A239">
@@ -9531,7 +8786,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M252"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9585,7 +8840,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -9597,22 +8852,22 @@
         <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>201</v>
+        <v>277</v>
       </c>
       <c r="F2" t="s">
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H2" t="s">
         <v>39</v>
       </c>
       <c r="I2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="K2" t="s">
         <v>39</v>
@@ -9623,7 +8878,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -9635,22 +8890,22 @@
         <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>201</v>
+        <v>277</v>
       </c>
       <c r="F3" t="s">
         <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H3" t="s">
         <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="K3" t="s">
         <v>39</v>
@@ -9661,7 +8916,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -9673,22 +8928,22 @@
         <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>201</v>
+        <v>277</v>
       </c>
       <c r="F4" t="s">
         <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H4" t="s">
         <v>39</v>
       </c>
       <c r="I4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J4" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -9699,7 +8954,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -9711,22 +8966,22 @@
         <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>201</v>
+        <v>277</v>
       </c>
       <c r="F5" t="s">
         <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H5" t="s">
         <v>39</v>
       </c>
       <c r="I5" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="K5" t="s">
         <v>39</v>
@@ -9737,7 +8992,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -9749,22 +9004,22 @@
         <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H6" t="s">
         <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="J6" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="K6" t="s">
         <v>39</v>
@@ -9775,7 +9030,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -9787,22 +9042,22 @@
         <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>201</v>
+        <v>277</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H7" t="s">
         <v>39</v>
       </c>
       <c r="I7" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J7" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="K7" t="s">
         <v>39</v>
@@ -9813,7 +9068,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -9825,22 +9080,22 @@
         <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>201</v>
+        <v>277</v>
       </c>
       <c r="F8" t="s">
         <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H8" t="s">
         <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J8" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="K8" t="s">
         <v>39</v>
@@ -9860,7 +9115,7 @@
         <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F9" t="s">
         <v>39</v>
@@ -9886,7 +9141,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
@@ -9898,22 +9153,22 @@
         <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F10" t="s">
         <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H10" t="s">
         <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="J10" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K10" t="s">
         <v>39</v>
@@ -9924,7 +9179,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -9942,16 +9197,16 @@
         <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H11" t="s">
         <v>39</v>
       </c>
       <c r="I11" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="J11" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="K11" t="s">
         <v>39</v>
@@ -9962,7 +9217,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -9974,19 +9229,19 @@
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H12" t="s">
         <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="J12" t="s">
         <v>43</v>
@@ -10000,7 +9255,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -10012,22 +9267,22 @@
         <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H13" t="s">
         <v>39</v>
       </c>
       <c r="I13" t="s">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="J13" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="K13" t="s">
         <v>39</v>
@@ -10038,7 +9293,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
@@ -10050,22 +9305,22 @@
         <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F14">
         <v>-0.5</v>
       </c>
       <c r="G14" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H14" t="s">
         <v>39</v>
       </c>
       <c r="I14" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="J14" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K14" t="s">
         <v>39</v>
@@ -10076,7 +9331,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
@@ -10088,22 +9343,22 @@
         <v>39</v>
       </c>
       <c r="E15" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F15" t="s">
         <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H15" t="s">
         <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J15" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K15" t="s">
         <v>39</v>
@@ -10114,10 +9369,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B16" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C16" t="s">
         <v>51</v>
@@ -10126,22 +9381,22 @@
         <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F16" t="s">
         <v>39</v>
       </c>
       <c r="G16" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H16" t="s">
         <v>39</v>
       </c>
       <c r="I16" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="J16" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="K16" t="s">
         <v>39</v>
@@ -10152,7 +9407,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
@@ -10164,22 +9419,22 @@
         <v>39</v>
       </c>
       <c r="E17" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F17">
         <v>-0.5</v>
       </c>
       <c r="G17" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H17" t="s">
         <v>39</v>
       </c>
       <c r="I17" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="J17" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K17" t="s">
         <v>39</v>
@@ -10190,7 +9445,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -10202,22 +9457,22 @@
         <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F18" t="s">
         <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H18" t="s">
         <v>39</v>
       </c>
       <c r="I18" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J18" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K18" t="s">
         <v>39</v>
@@ -10231,7 +9486,7 @@
         <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C19" t="s">
         <v>51</v>
@@ -10240,13 +9495,13 @@
         <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F19" t="s">
         <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H19" t="s">
         <v>39</v>
@@ -10255,7 +9510,7 @@
         <v>49</v>
       </c>
       <c r="J19" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="K19" t="s">
         <v>39</v>
@@ -10266,7 +9521,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
@@ -10278,22 +9533,22 @@
         <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F20" t="s">
         <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H20" t="s">
         <v>39</v>
       </c>
       <c r="I20" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="J20" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="K20" t="s">
         <v>39</v>
@@ -10304,7 +9559,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B21" t="s">
         <v>2</v>
@@ -10316,22 +9571,22 @@
         <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F21" t="s">
         <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H21" t="s">
         <v>39</v>
       </c>
       <c r="I21" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J21" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K21" t="s">
         <v>39</v>
@@ -10354,13 +9609,13 @@
         <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F22" t="s">
         <v>39</v>
       </c>
       <c r="G22" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H22" t="s">
         <v>39</v>
@@ -10369,7 +9624,7 @@
         <v>43</v>
       </c>
       <c r="J22" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="K22" t="s">
         <v>39</v>
@@ -10380,7 +9635,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B23" t="s">
         <v>6</v>
@@ -10392,22 +9647,22 @@
         <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="F23">
         <v>-6</v>
       </c>
       <c r="G23" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H23" t="s">
         <v>39</v>
       </c>
       <c r="I23" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="J23" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="K23" t="s">
         <v>39</v>
@@ -10418,7 +9673,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B24" t="s">
         <v>2</v>
@@ -10430,22 +9685,22 @@
         <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="F24" t="s">
         <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H24" t="s">
         <v>39</v>
       </c>
       <c r="I24" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="J24" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K24" t="s">
         <v>39</v>
@@ -10456,7 +9711,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B25" t="s">
         <v>2</v>
@@ -10468,22 +9723,22 @@
         <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="F25" t="s">
         <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H25" t="s">
         <v>39</v>
       </c>
       <c r="I25" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="J25" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K25" t="s">
         <v>39</v>
@@ -10494,7 +9749,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B26" t="s">
         <v>2</v>
@@ -10506,22 +9761,22 @@
         <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="F26" t="s">
         <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H26" t="s">
         <v>39</v>
       </c>
       <c r="I26" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="J26" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="K26" t="s">
         <v>39</v>
@@ -10532,7 +9787,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
@@ -10544,22 +9799,22 @@
         <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F27" t="s">
         <v>39</v>
       </c>
       <c r="G27" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H27" t="s">
         <v>39</v>
       </c>
       <c r="I27" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="J27" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="K27" t="s">
         <v>39</v>
@@ -10570,7 +9825,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B28" t="s">
         <v>4</v>
@@ -10582,22 +9837,22 @@
         <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F28" t="s">
         <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H28" t="s">
         <v>39</v>
       </c>
       <c r="I28" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J28" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="K28" t="s">
         <v>39</v>
@@ -10608,7 +9863,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s">
         <v>6</v>
@@ -10620,22 +9875,22 @@
         <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F29" t="s">
         <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H29" t="s">
         <v>39</v>
       </c>
       <c r="I29" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="J29" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="K29" t="s">
         <v>39</v>
@@ -10646,7 +9901,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
@@ -10664,16 +9919,16 @@
         <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H30" t="s">
         <v>39</v>
       </c>
       <c r="I30" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J30" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="K30" t="s">
         <v>39</v>
@@ -10684,7 +9939,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B31" t="s">
         <v>2</v>
@@ -10696,22 +9951,22 @@
         <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F31" t="s">
         <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H31" t="s">
         <v>39</v>
       </c>
       <c r="I31" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="J31" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="K31" t="s">
         <v>39</v>
@@ -10722,7 +9977,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -10734,19 +9989,19 @@
         <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F32" t="s">
         <v>39</v>
       </c>
       <c r="G32" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H32" t="s">
         <v>39</v>
       </c>
       <c r="I32" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="J32" t="s">
         <v>43</v>
@@ -10760,7 +10015,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
@@ -10778,16 +10033,16 @@
         <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H33" t="s">
         <v>39</v>
       </c>
       <c r="I33" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="J33" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="K33" t="s">
         <v>39</v>
@@ -10798,7 +10053,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B34" t="s">
         <v>6</v>
@@ -10810,22 +10065,22 @@
         <v>39</v>
       </c>
       <c r="E34" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="F34">
         <v>-4</v>
       </c>
       <c r="G34" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H34" t="s">
         <v>39</v>
       </c>
       <c r="I34" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="J34" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K34" t="s">
         <v>39</v>
@@ -10836,7 +10091,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
@@ -10848,22 +10103,22 @@
         <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F35">
         <v>-4</v>
       </c>
       <c r="G35" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H35" t="s">
         <v>39</v>
       </c>
       <c r="I35" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J35" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K35" t="s">
         <v>39</v>
@@ -10874,7 +10129,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B36" t="s">
         <v>6</v>
@@ -10892,16 +10147,16 @@
         <v>-2</v>
       </c>
       <c r="G36" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H36" t="s">
         <v>39</v>
       </c>
       <c r="I36" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J36" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K36" t="s">
         <v>39</v>
@@ -10912,7 +10167,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
@@ -10924,22 +10179,22 @@
         <v>39</v>
       </c>
       <c r="E37" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F37">
         <v>-2</v>
       </c>
       <c r="G37" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H37" t="s">
         <v>39</v>
       </c>
       <c r="I37" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J37" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K37" t="s">
         <v>39</v>
@@ -10950,7 +10205,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B38" t="s">
         <v>6</v>
@@ -10962,22 +10217,22 @@
         <v>39</v>
       </c>
       <c r="E38" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F38">
         <v>-2</v>
       </c>
       <c r="G38" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H38" t="s">
         <v>39</v>
       </c>
       <c r="I38" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="J38" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K38" t="s">
         <v>39</v>
@@ -10988,7 +10243,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
@@ -11000,22 +10255,22 @@
         <v>39</v>
       </c>
       <c r="E39" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F39">
         <v>-4</v>
       </c>
       <c r="G39" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H39" t="s">
         <v>39</v>
       </c>
       <c r="I39" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="J39" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K39" t="s">
         <v>39</v>
@@ -11026,7 +10281,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
@@ -11038,22 +10293,22 @@
         <v>39</v>
       </c>
       <c r="E40" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="F40">
         <v>-2</v>
       </c>
       <c r="G40" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H40" t="s">
         <v>39</v>
       </c>
       <c r="I40" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="J40" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K40" t="s">
         <v>39</v>
@@ -11064,7 +10319,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
@@ -11076,22 +10331,22 @@
         <v>39</v>
       </c>
       <c r="E41" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="F41">
         <v>-2</v>
       </c>
       <c r="G41" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H41" t="s">
         <v>39</v>
       </c>
       <c r="I41" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="J41" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="K41" t="s">
         <v>39</v>
@@ -11102,7 +10357,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B42" t="s">
         <v>6</v>
@@ -11114,22 +10369,22 @@
         <v>39</v>
       </c>
       <c r="E42" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F42">
         <v>-4</v>
       </c>
       <c r="G42" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H42" t="s">
         <v>39</v>
       </c>
       <c r="I42" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="J42" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="K42" t="s">
         <v>39</v>
@@ -11140,10 +10395,10 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B43" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C43" t="s">
         <v>51</v>
@@ -11152,22 +10407,22 @@
         <v>39</v>
       </c>
       <c r="E43" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F43" t="s">
         <v>39</v>
       </c>
       <c r="G43" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H43" t="s">
         <v>39</v>
       </c>
       <c r="I43" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="J43" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="K43" t="s">
         <v>39</v>
@@ -11178,10 +10433,10 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B44" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C44" t="s">
         <v>51</v>
@@ -11190,22 +10445,22 @@
         <v>39</v>
       </c>
       <c r="E44" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F44" t="s">
         <v>39</v>
       </c>
       <c r="G44" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H44" t="s">
         <v>39</v>
       </c>
       <c r="I44" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="J44" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="K44" t="s">
         <v>39</v>
@@ -11216,10 +10471,10 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B45" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C45" t="s">
         <v>51</v>
@@ -11228,22 +10483,22 @@
         <v>39</v>
       </c>
       <c r="E45" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
       </c>
       <c r="G45" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H45" t="s">
         <v>39</v>
       </c>
       <c r="I45" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="J45" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="K45" t="s">
         <v>39</v>
@@ -11254,10 +10509,10 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B46" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C46" t="s">
         <v>51</v>
@@ -11266,22 +10521,22 @@
         <v>39</v>
       </c>
       <c r="E46" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F46" t="s">
         <v>39</v>
       </c>
       <c r="G46" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H46" t="s">
         <v>39</v>
       </c>
       <c r="I46" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="J46" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K46" t="s">
         <v>39</v>
@@ -11292,10 +10547,10 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B47" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C47" t="s">
         <v>51</v>
@@ -11304,22 +10559,22 @@
         <v>39</v>
       </c>
       <c r="E47" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F47" t="s">
         <v>39</v>
       </c>
       <c r="G47" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H47" t="s">
         <v>39</v>
       </c>
       <c r="I47" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="J47" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="K47" t="s">
         <v>39</v>
@@ -11330,10 +10585,10 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B48" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C48" t="s">
         <v>51</v>
@@ -11342,22 +10597,22 @@
         <v>39</v>
       </c>
       <c r="E48" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F48" t="s">
         <v>39</v>
       </c>
       <c r="G48" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H48" t="s">
         <v>39</v>
       </c>
       <c r="I48" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="J48" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K48" t="s">
         <v>39</v>
@@ -11368,10 +10623,10 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B49" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C49" t="s">
         <v>51</v>
@@ -11380,22 +10635,22 @@
         <v>39</v>
       </c>
       <c r="E49" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F49" t="s">
         <v>39</v>
       </c>
       <c r="G49" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H49" t="s">
         <v>39</v>
       </c>
       <c r="I49" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="J49" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="K49" t="s">
         <v>39</v>
@@ -11406,10 +10661,10 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B50" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C50" t="s">
         <v>51</v>
@@ -11418,22 +10673,22 @@
         <v>39</v>
       </c>
       <c r="E50" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F50" t="s">
         <v>39</v>
       </c>
       <c r="G50" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H50" t="s">
         <v>39</v>
       </c>
       <c r="I50" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J50" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="K50" t="s">
         <v>39</v>
@@ -11444,10 +10699,10 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B51" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C51" t="s">
         <v>51</v>
@@ -11456,22 +10711,22 @@
         <v>39</v>
       </c>
       <c r="E51" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F51" t="s">
         <v>39</v>
       </c>
       <c r="G51" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H51" t="s">
         <v>39</v>
       </c>
       <c r="I51" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J51" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="K51" t="s">
         <v>39</v>
@@ -11494,13 +10749,13 @@
         <v>39</v>
       </c>
       <c r="E52" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F52" t="s">
         <v>39</v>
       </c>
       <c r="G52" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H52" t="s">
         <v>39</v>
@@ -11518,206 +10773,6 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="203" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="204" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="209" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="210" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="213" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="214" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="217" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="218" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="219" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="221" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="224" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="225" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="226" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="227" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="230" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="231" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="232" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="233" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="234" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="240" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="241" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="242" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="243" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="244" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="245" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="246" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="247" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="248" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="249" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="250" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="251" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="252" spans="4:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="8">
     <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid date" error="Please enter a valid date." sqref="A10:A252">

--- a/src/data/FML-Data.xlsx
+++ b/src/data/FML-Data.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2705" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2622" uniqueCount="309">
   <si>
     <t>Name</t>
   </si>
@@ -509,136 +509,394 @@
     <t>Home - Videos</t>
   </si>
   <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>FNS-17</t>
+  </si>
+  <si>
     <t>2026-08-11</t>
   </si>
   <si>
+    <t>FNS-49</t>
+  </si>
+  <si>
+    <t>Stats</t>
+  </si>
+  <si>
+    <t>FNS-6</t>
+  </si>
+  <si>
+    <t>Showcase</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>FNS-13</t>
+  </si>
+  <si>
+    <t>Home - shop</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>FNS-41</t>
+  </si>
+  <si>
+    <t>Schedule</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>FNS-8</t>
+  </si>
+  <si>
+    <t>Home - Fixtures</t>
+  </si>
+  <si>
+    <t>FNS-21</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>FNS-12</t>
+  </si>
+  <si>
+    <t>Home - Players</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>FNS-19</t>
+  </si>
+  <si>
+    <t>Photos Detail</t>
+  </si>
+  <si>
+    <t>FNS-44</t>
+  </si>
+  <si>
+    <t>Players</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>FNS-45</t>
+  </si>
+  <si>
+    <t>Support Staff</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>FNS-46</t>
+  </si>
+  <si>
+    <t>player Profile</t>
+  </si>
+  <si>
+    <t>In Dev</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>FNS-5</t>
+  </si>
+  <si>
+    <t>Top Menu, Bottom Menu</t>
+  </si>
+  <si>
+    <t>Footer</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
     <t>FNS-51</t>
   </si>
   <si>
-    <t>Points Table</t>
-  </si>
-  <si>
-    <t>FNS-49</t>
-  </si>
-  <si>
-    <t>Stats</t>
-  </si>
-  <si>
-    <t>FNS-6</t>
-  </si>
-  <si>
-    <t>Showcase</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>FNS-13</t>
-  </si>
-  <si>
-    <t>Home - shop</t>
-  </si>
-  <si>
-    <t>2026-08-13</t>
-  </si>
-  <si>
-    <t>FNS-41</t>
-  </si>
-  <si>
-    <t>Schedule</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>FNS-8</t>
-  </si>
-  <si>
-    <t>Home - Fixtures</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>FNS-5</t>
-  </si>
-  <si>
-    <t>Header &amp; Footer, Sponsors</t>
-  </si>
-  <si>
-    <t>2026-08-17</t>
-  </si>
-  <si>
-    <t>FNS-12</t>
-  </si>
-  <si>
-    <t>Home - Players</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>FNS-44</t>
-  </si>
-  <si>
-    <t>Players</t>
-  </si>
-  <si>
-    <t>2026-08-24</t>
-  </si>
-  <si>
-    <t>2026-08-25</t>
-  </si>
-  <si>
-    <t>FNS-45</t>
-  </si>
-  <si>
-    <t>Support Staff</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>FNS-46</t>
-  </si>
-  <si>
-    <t>player Profile</t>
-  </si>
-  <si>
-    <t>In Dev</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>Top Menu, Bottom Menu</t>
+    <t>Both Standings css</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>HP News</t>
+  </si>
+  <si>
+    <t>HP Videos</t>
+  </si>
+  <si>
+    <t>FNS-11</t>
+  </si>
+  <si>
+    <t>HP Photos</t>
+  </si>
+  <si>
+    <t>FNS-16</t>
+  </si>
+  <si>
+    <t>FNS-20</t>
+  </si>
+  <si>
+    <t>FNS-18</t>
+  </si>
+  <si>
+    <t>Photos Listing</t>
+  </si>
+  <si>
+    <t>FNS-29</t>
+  </si>
+  <si>
+    <t>Terms and Conditions</t>
+  </si>
+  <si>
+    <t>Ready for QA</t>
+  </si>
+  <si>
+    <t>FNS-28</t>
+  </si>
+  <si>
+    <t>Privacy Policy</t>
+  </si>
+  <si>
+    <t>FNS-31</t>
+  </si>
+  <si>
+    <t>Thank you</t>
+  </si>
+  <si>
+    <t>FNS-30</t>
+  </si>
+  <si>
+    <t>FNS-32</t>
+  </si>
+  <si>
+    <t>Partnership Framework</t>
+  </si>
+  <si>
+    <t>FNS-24</t>
+  </si>
+  <si>
+    <t>Where to Watch</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>FNS-25</t>
+  </si>
+  <si>
+    <t>Womens t20 exhibition</t>
+  </si>
+  <si>
+    <t>FNS-23</t>
+  </si>
+  <si>
+    <t>Wallpapers</t>
+  </si>
+  <si>
+    <t>FNS-33</t>
+  </si>
+  <si>
+    <t>Registration form (popup)</t>
+  </si>
+  <si>
+    <t>Code Review</t>
+  </si>
+  <si>
+    <t>FNS-34</t>
+  </si>
+  <si>
+    <t>FNS-35</t>
+  </si>
+  <si>
+    <t>Contact Us</t>
+  </si>
+  <si>
+    <t>FNS-36</t>
+  </si>
+  <si>
+    <t>FNS-168</t>
+  </si>
+  <si>
+    <t>Boundary Builder page + form</t>
+  </si>
+  <si>
+    <t>FNS-43</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>Player registration embed</t>
   </si>
   <si>
     <t>pending</t>
   </si>
   <si>
-    <t>Footer</t>
-  </si>
-  <si>
-    <t>2026-09-08</t>
-  </si>
-  <si>
-    <t>Both Standings css</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>HP News</t>
-  </si>
-  <si>
-    <t>HP Videos</t>
-  </si>
-  <si>
-    <t>HP Photos</t>
-  </si>
-  <si>
-    <t>2026-09-10</t>
+    <t>HP Static Banner</t>
+  </si>
+  <si>
+    <t>Team strip</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>T&amp;C page</t>
+  </si>
+  <si>
+    <t>About us</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>Hall of fame</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Buy Tickets banner</t>
+  </si>
+  <si>
+    <t>Islander Banner</t>
+  </si>
+  <si>
+    <t>Esports</t>
+  </si>
+  <si>
+    <t>Social Hub</t>
+  </si>
+  <si>
+    <t>Esports Player Profile</t>
+  </si>
+  <si>
+    <t>Ticket T&amp;C</t>
+  </si>
+  <si>
+    <t>Community</t>
+  </si>
+  <si>
+    <t>Safeguarding</t>
+  </si>
+  <si>
+    <t>Cookie Policy</t>
+  </si>
+  <si>
+    <t>Error Page</t>
+  </si>
+  <si>
+    <t>Siddharth N</t>
+  </si>
+  <si>
+    <t>Header &amp; Footer</t>
+  </si>
+  <si>
+    <t>Standings</t>
+  </si>
+  <si>
+    <t>Squad</t>
+  </si>
+  <si>
+    <t>External links - 1 ticket maybe</t>
+  </si>
+  <si>
+    <t>Buffer Due to New Module</t>
+  </si>
+  <si>
+    <t>Fixses</t>
+  </si>
+  <si>
+    <t>Aapla 12th Man Poll</t>
+  </si>
+  <si>
+    <t>Goal of the Month</t>
+  </si>
+  <si>
+    <t>Homepage listings</t>
+  </si>
+  <si>
+    <t>All listing pages</t>
+  </si>
+  <si>
+    <t>All Detail pages</t>
+  </si>
+  <si>
+    <t>HP Showcase</t>
+  </si>
+  <si>
+    <t>Buffer Due to FIH</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>Go Live</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Top Menu, Bottom Menu/Footer</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>Fixtures</t>
+  </si>
+  <si>
+    <t>News</t>
+  </si>
+  <si>
+    <t>Subscribe to emails form</t>
+  </si>
+  <si>
+    <t>Videos</t>
+  </si>
+  <si>
+    <t>Aapla 12th Man Banner</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>Photos</t>
+  </si>
+  <si>
+    <t>Tracker</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
   </si>
   <si>
     <t>News Listing &amp; Detail</t>
@@ -647,286 +905,7 @@
     <t>Video Listing and Detail</t>
   </si>
   <si>
-    <t>2026-09-11</t>
-  </si>
-  <si>
     <t>Photos Listing &amp; Detail</t>
-  </si>
-  <si>
-    <t>FNS-29</t>
-  </si>
-  <si>
-    <t>Terms and Conditions</t>
-  </si>
-  <si>
-    <t>Ready for QA</t>
-  </si>
-  <si>
-    <t>FNS-28</t>
-  </si>
-  <si>
-    <t>Privacy Policy</t>
-  </si>
-  <si>
-    <t>FNS-31</t>
-  </si>
-  <si>
-    <t>Thank you</t>
-  </si>
-  <si>
-    <t>FNS-30</t>
-  </si>
-  <si>
-    <t>FNS-32</t>
-  </si>
-  <si>
-    <t>Partnership Framework</t>
-  </si>
-  <si>
-    <t>FNS-24</t>
-  </si>
-  <si>
-    <t>Where to Watch</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>FNS-25</t>
-  </si>
-  <si>
-    <t>Womens t20 exhibition</t>
-  </si>
-  <si>
-    <t>FNS-23</t>
-  </si>
-  <si>
-    <t>Wallpapers</t>
-  </si>
-  <si>
-    <t>FNS-33</t>
-  </si>
-  <si>
-    <t>Registration form (popup)</t>
-  </si>
-  <si>
-    <t>Code Review</t>
-  </si>
-  <si>
-    <t>FNS-34</t>
-  </si>
-  <si>
-    <t>FNS-35</t>
-  </si>
-  <si>
-    <t>Contact Us</t>
-  </si>
-  <si>
-    <t>FNS-36</t>
-  </si>
-  <si>
-    <t>FNS-168</t>
-  </si>
-  <si>
-    <t>Boundary Builder page + form</t>
-  </si>
-  <si>
-    <t>FNS-20</t>
-  </si>
-  <si>
-    <t>Videos - Listing</t>
-  </si>
-  <si>
-    <t>FNS-18</t>
-  </si>
-  <si>
-    <t>Photos - Listing</t>
-  </si>
-  <si>
-    <t>2026-08-19</t>
-  </si>
-  <si>
-    <t>FNS-16</t>
-  </si>
-  <si>
-    <t>News - Listing</t>
-  </si>
-  <si>
-    <t>FNS-19</t>
-  </si>
-  <si>
-    <t>Photos - Detail</t>
-  </si>
-  <si>
-    <t>FNS-17</t>
-  </si>
-  <si>
-    <t>News - Detail</t>
-  </si>
-  <si>
-    <t>FNS-21</t>
-  </si>
-  <si>
-    <t>Videos - Detail</t>
-  </si>
-  <si>
-    <t>FNS-43</t>
-  </si>
-  <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
-    <t>Player registration embed</t>
-  </si>
-  <si>
-    <t>HP Static Banner</t>
-  </si>
-  <si>
-    <t>Team strip</t>
-  </si>
-  <si>
-    <t>2026-09-02</t>
-  </si>
-  <si>
-    <t>T&amp;C page</t>
-  </si>
-  <si>
-    <t>About us</t>
-  </si>
-  <si>
-    <t>2026-09-03</t>
-  </si>
-  <si>
-    <t>Hall of fame</t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>Buy Tickets banner</t>
-  </si>
-  <si>
-    <t>Islander Banner</t>
-  </si>
-  <si>
-    <t>Esports</t>
-  </si>
-  <si>
-    <t>Social Hub</t>
-  </si>
-  <si>
-    <t>Esports Player Profile</t>
-  </si>
-  <si>
-    <t>Ticket T&amp;C</t>
-  </si>
-  <si>
-    <t>Community</t>
-  </si>
-  <si>
-    <t>Safeguarding</t>
-  </si>
-  <si>
-    <t>Cookie Policy</t>
-  </si>
-  <si>
-    <t>Error Page</t>
-  </si>
-  <si>
-    <t>Siddharth N</t>
-  </si>
-  <si>
-    <t>Header &amp; Footer</t>
-  </si>
-  <si>
-    <t>Standings</t>
-  </si>
-  <si>
-    <t>Squad</t>
-  </si>
-  <si>
-    <t>External links - 1 ticket maybe</t>
-  </si>
-  <si>
-    <t>Buffer Due to New Module</t>
-  </si>
-  <si>
-    <t>Fixses</t>
-  </si>
-  <si>
-    <t>Aapla 12th Man Poll</t>
-  </si>
-  <si>
-    <t>Goal of the Month</t>
-  </si>
-  <si>
-    <t>Homepage listings</t>
-  </si>
-  <si>
-    <t>All listing pages</t>
-  </si>
-  <si>
-    <t>All Detail pages</t>
-  </si>
-  <si>
-    <t>HP Showcase</t>
-  </si>
-  <si>
-    <t>Buffer Due to FIH</t>
-  </si>
-  <si>
-    <t>2026-09-21</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>Go Live</t>
-  </si>
-  <si>
-    <t>Design</t>
-  </si>
-  <si>
-    <t>Top Menu, Bottom Menu/Footer</t>
-  </si>
-  <si>
-    <t>2026-09-18</t>
-  </si>
-  <si>
-    <t>2026-08-30</t>
-  </si>
-  <si>
-    <t>Fixtures</t>
-  </si>
-  <si>
-    <t>News</t>
-  </si>
-  <si>
-    <t>Subscribe to emails form</t>
-  </si>
-  <si>
-    <t>Videos</t>
-  </si>
-  <si>
-    <t>Aapla 12th Man Banner</t>
-  </si>
-  <si>
-    <t>2026-09-17</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>Photos</t>
-  </si>
-  <si>
-    <t>Tracker</t>
-  </si>
-  <si>
-    <t>2026-09-05</t>
   </si>
   <si>
     <t>Login</t>
@@ -4949,36 +4928,24 @@
         <v>164</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
-      </c>
-      <c r="F4" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s">
         <v>44</v>
       </c>
-      <c r="H4" t="s">
-        <v>39</v>
-      </c>
       <c r="I4" t="s">
         <v>163</v>
       </c>
       <c r="J4" t="s">
         <v>163</v>
       </c>
-      <c r="K4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L4" t="s">
-        <v>39</v>
-      </c>
       <c r="M4" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -5002,10 +4969,10 @@
         <v>39</v>
       </c>
       <c r="I5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K5" t="s">
         <v>39</v>
@@ -5019,7 +4986,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -5043,10 +5010,10 @@
         <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K6" t="s">
         <v>39</v>
@@ -5183,7 +5150,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
@@ -5192,39 +5159,27 @@
         <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="G10" t="s">
         <v>44</v>
       </c>
-      <c r="H10" t="s">
-        <v>39</v>
-      </c>
       <c r="I10" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="J10" t="s">
-        <v>179</v>
-      </c>
-      <c r="K10" t="s">
-        <v>39</v>
-      </c>
-      <c r="L10" t="s">
-        <v>39</v>
+        <v>163</v>
       </c>
       <c r="M10" t="s">
-        <v>113</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -5233,10 +5188,10 @@
         <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F11" t="s">
         <v>39</v>
@@ -5248,7 +5203,7 @@
         <v>39</v>
       </c>
       <c r="I11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J11" t="s">
         <v>38</v>
@@ -5265,7 +5220,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -5274,10 +5229,10 @@
         <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
@@ -5289,7 +5244,7 @@
         <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J12" t="s">
         <v>38</v>
@@ -5304,8 +5259,36 @@
         <v>160</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
+        <v>185</v>
+      </c>
+      <c r="E13" t="s">
+        <v>186</v>
+      </c>
+      <c r="G13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" t="s">
+        <v>184</v>
+      </c>
+      <c r="J13" t="s">
+        <v>184</v>
+      </c>
+      <c r="M13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="5:5" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
@@ -5317,10 +5300,10 @@
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F15" t="s">
         <v>39</v>
@@ -5332,7 +5315,7 @@
         <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J15" t="s">
         <v>38</v>
@@ -5399,10 +5382,10 @@
         <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F17" t="s">
         <v>39</v>
@@ -5417,7 +5400,7 @@
         <v>38</v>
       </c>
       <c r="J17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K17" t="s">
         <v>39</v>
@@ -5431,7 +5414,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -5440,10 +5423,10 @@
         <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F18" t="s">
         <v>39</v>
@@ -5458,7 +5441,7 @@
         <v>38</v>
       </c>
       <c r="J18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K18" t="s">
         <v>39</v>
@@ -5472,7 +5455,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
@@ -5563,10 +5546,10 @@
         <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E21" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F21" t="s">
         <v>39</v>
@@ -5595,7 +5578,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B22" t="s">
         <v>2</v>
@@ -5604,10 +5587,10 @@
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F22" t="s">
         <v>39</v>
@@ -5619,10 +5602,10 @@
         <v>39</v>
       </c>
       <c r="I22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K22" t="s">
         <v>39</v>
@@ -5631,17 +5614,17 @@
         <v>39</v>
       </c>
       <c r="M22" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="23" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B28" t="s">
         <v>2</v>
@@ -5650,25 +5633,25 @@
         <v>40</v>
       </c>
       <c r="D28" t="s">
-        <v>39</v>
+        <v>198</v>
       </c>
       <c r="E28" t="s">
+        <v>199</v>
+      </c>
+      <c r="F28" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" t="s">
+        <v>39</v>
+      </c>
+      <c r="I28" t="s">
         <v>197</v>
       </c>
-      <c r="F28" t="s">
-        <v>39</v>
-      </c>
-      <c r="G28" t="s">
-        <v>198</v>
-      </c>
-      <c r="H28" t="s">
-        <v>39</v>
-      </c>
-      <c r="I28" t="s">
-        <v>196</v>
-      </c>
       <c r="J28" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K28" t="s">
         <v>39</v>
@@ -5676,10 +5659,13 @@
       <c r="L28" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B29" t="s">
         <v>2</v>
@@ -5688,25 +5674,25 @@
         <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>39</v>
+        <v>198</v>
       </c>
       <c r="E29" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F29" t="s">
         <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>198</v>
+        <v>44</v>
       </c>
       <c r="H29" t="s">
         <v>39</v>
       </c>
       <c r="I29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K29" t="s">
         <v>39</v>
@@ -5714,10 +5700,13 @@
       <c r="L29" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B30" t="s">
         <v>2</v>
@@ -5726,36 +5715,39 @@
         <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>39</v>
+        <v>202</v>
       </c>
       <c r="E30" t="s">
+        <v>203</v>
+      </c>
+      <c r="F30" t="s">
+        <v>39</v>
+      </c>
+      <c r="G30" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" t="s">
+        <v>39</v>
+      </c>
+      <c r="I30" t="s">
         <v>201</v>
       </c>
-      <c r="F30" t="s">
-        <v>39</v>
-      </c>
-      <c r="G30" t="s">
-        <v>198</v>
-      </c>
-      <c r="H30" t="s">
-        <v>39</v>
-      </c>
-      <c r="I30" t="s">
-        <v>200</v>
-      </c>
       <c r="J30" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K30" t="s">
         <v>39</v>
       </c>
       <c r="L30" t="s">
         <v>39</v>
+      </c>
+      <c r="M30" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B31" t="s">
         <v>2</v>
@@ -5767,7 +5759,7 @@
         <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F31" t="s">
         <v>39</v>
@@ -5779,10 +5771,10 @@
         <v>39</v>
       </c>
       <c r="I31" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J31" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K31" t="s">
         <v>39</v>
@@ -5793,7 +5785,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B32" t="s">
         <v>2</v>
@@ -5805,7 +5797,7 @@
         <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F32" t="s">
         <v>39</v>
@@ -5817,10 +5809,10 @@
         <v>39</v>
       </c>
       <c r="I32" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J32" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K32" t="s">
         <v>39</v>
@@ -5829,9 +5821,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B33" t="s">
         <v>2</v>
@@ -5840,25 +5832,25 @@
         <v>40</v>
       </c>
       <c r="D33" t="s">
-        <v>39</v>
+        <v>207</v>
       </c>
       <c r="E33" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F33" t="s">
         <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>198</v>
+        <v>44</v>
       </c>
       <c r="H33" t="s">
         <v>39</v>
       </c>
       <c r="I33" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J33" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K33" t="s">
         <v>39</v>
@@ -5866,10 +5858,13 @@
       <c r="L33" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M33" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="B34" t="s">
         <v>2</v>
@@ -5878,36 +5873,39 @@
         <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>39</v>
+        <v>209</v>
       </c>
       <c r="E34" t="s">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="F34" t="s">
         <v>39</v>
       </c>
       <c r="G34" t="s">
-        <v>198</v>
+        <v>44</v>
       </c>
       <c r="H34" t="s">
         <v>39</v>
       </c>
       <c r="I34" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="J34" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="K34" t="s">
         <v>39</v>
       </c>
       <c r="L34" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M34" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="B35" t="s">
         <v>2</v>
@@ -5916,36 +5914,39 @@
         <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>39</v>
+        <v>210</v>
       </c>
       <c r="E35" t="s">
-        <v>208</v>
+        <v>71</v>
       </c>
       <c r="F35" t="s">
         <v>39</v>
       </c>
       <c r="G35" t="s">
-        <v>198</v>
+        <v>44</v>
       </c>
       <c r="H35" t="s">
         <v>39</v>
       </c>
       <c r="I35" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="J35" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="K35" t="s">
         <v>39</v>
       </c>
       <c r="L35" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="M35" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="B36" t="s">
         <v>2</v>
@@ -5954,36 +5955,39 @@
         <v>40</v>
       </c>
       <c r="D36" t="s">
-        <v>39</v>
+        <v>211</v>
       </c>
       <c r="E36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F36" t="s">
         <v>39</v>
       </c>
       <c r="G36" t="s">
-        <v>198</v>
+        <v>44</v>
       </c>
       <c r="H36" t="s">
         <v>39</v>
       </c>
       <c r="I36" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="J36" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="K36" t="s">
         <v>39</v>
       </c>
       <c r="L36" t="s">
-        <v>209</v>
+        <v>184</v>
+      </c>
+      <c r="M36" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
@@ -5992,10 +5996,10 @@
         <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E37" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F37" t="s">
         <v>39</v>
@@ -6007,24 +6011,24 @@
         <v>39</v>
       </c>
       <c r="I37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K37" t="s">
         <v>39</v>
       </c>
       <c r="L37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M37" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B38" t="s">
         <v>6</v>
@@ -6033,10 +6037,10 @@
         <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F38" t="s">
         <v>39</v>
@@ -6048,10 +6052,10 @@
         <v>39</v>
       </c>
       <c r="I38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K38" t="s">
         <v>39</v>
@@ -6060,7 +6064,7 @@
         <v>39</v>
       </c>
       <c r="M38" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -6074,10 +6078,10 @@
         <v>40</v>
       </c>
       <c r="D39" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E39" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F39" t="s">
         <v>39</v>
@@ -6101,7 +6105,7 @@
         <v>39</v>
       </c>
       <c r="M39" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -6115,7 +6119,7 @@
         <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E40" t="s">
         <v>153</v>
@@ -6142,12 +6146,12 @@
         <v>39</v>
       </c>
       <c r="M40" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
@@ -6156,10 +6160,10 @@
         <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E41" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F41" t="s">
         <v>39</v>
@@ -6171,10 +6175,10 @@
         <v>39</v>
       </c>
       <c r="I41" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J41" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K41" t="s">
         <v>39</v>
@@ -6183,12 +6187,12 @@
         <v>39</v>
       </c>
       <c r="M41" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B42" t="s">
         <v>6</v>
@@ -6197,10 +6201,10 @@
         <v>40</v>
       </c>
       <c r="D42" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E42" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F42" t="s">
         <v>39</v>
@@ -6212,10 +6216,10 @@
         <v>39</v>
       </c>
       <c r="I42" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J42" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K42" t="s">
         <v>39</v>
@@ -6229,7 +6233,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B43" t="s">
         <v>6</v>
@@ -6238,10 +6242,10 @@
         <v>40</v>
       </c>
       <c r="D43" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E43" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F43" t="s">
         <v>39</v>
@@ -6253,10 +6257,10 @@
         <v>39</v>
       </c>
       <c r="I43" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J43" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K43" t="s">
         <v>39</v>
@@ -6265,12 +6269,12 @@
         <v>39</v>
       </c>
       <c r="M43" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B44" t="s">
         <v>6</v>
@@ -6279,10 +6283,10 @@
         <v>40</v>
       </c>
       <c r="D44" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E44" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F44" t="s">
         <v>39</v>
@@ -6294,10 +6298,10 @@
         <v>39</v>
       </c>
       <c r="I44" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J44" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K44" t="s">
         <v>39</v>
@@ -6306,12 +6310,12 @@
         <v>39</v>
       </c>
       <c r="M44" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
@@ -6320,10 +6324,10 @@
         <v>40</v>
       </c>
       <c r="D45" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E45" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
@@ -6335,10 +6339,10 @@
         <v>39</v>
       </c>
       <c r="I45" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J45" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K45" t="s">
         <v>39</v>
@@ -6347,12 +6351,12 @@
         <v>39</v>
       </c>
       <c r="M45" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
@@ -6361,7 +6365,7 @@
         <v>40</v>
       </c>
       <c r="D46" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E46" t="s">
         <v>39</v>
@@ -6376,10 +6380,10 @@
         <v>39</v>
       </c>
       <c r="I46" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J46" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K46" t="s">
         <v>39</v>
@@ -6388,12 +6392,12 @@
         <v>39</v>
       </c>
       <c r="M46" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B47" t="s">
         <v>9</v>
@@ -6402,10 +6406,10 @@
         <v>40</v>
       </c>
       <c r="D47" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E47" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F47" t="s">
         <v>39</v>
@@ -6417,10 +6421,10 @@
         <v>39</v>
       </c>
       <c r="I47" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J47" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K47" t="s">
         <v>39</v>
@@ -6429,12 +6433,12 @@
         <v>39</v>
       </c>
       <c r="M47" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
@@ -6443,7 +6447,7 @@
         <v>40</v>
       </c>
       <c r="D48" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E48" t="s">
         <v>39</v>
@@ -6458,10 +6462,10 @@
         <v>39</v>
       </c>
       <c r="I48" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J48" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K48" t="s">
         <v>39</v>
@@ -6470,7 +6474,7 @@
         <v>39</v>
       </c>
       <c r="M48" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -6484,10 +6488,10 @@
         <v>40</v>
       </c>
       <c r="D49" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E49" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F49" t="s">
         <v>39</v>
@@ -6511,301 +6515,21 @@
         <v>39</v>
       </c>
       <c r="M49" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>182</v>
-      </c>
-      <c r="B51" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" t="s">
-        <v>40</v>
-      </c>
-      <c r="D51" t="s">
-        <v>237</v>
-      </c>
-      <c r="E51" t="s">
-        <v>238</v>
-      </c>
-      <c r="F51" t="s">
-        <v>39</v>
-      </c>
-      <c r="G51" t="s">
-        <v>44</v>
-      </c>
-      <c r="H51" t="s">
-        <v>39</v>
-      </c>
-      <c r="I51" t="s">
-        <v>182</v>
-      </c>
-      <c r="J51" t="s">
-        <v>182</v>
-      </c>
-      <c r="K51" t="s">
-        <v>39</v>
-      </c>
-      <c r="L51" t="s">
-        <v>39</v>
-      </c>
-      <c r="M51" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>182</v>
-      </c>
-      <c r="B52" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" t="s">
-        <v>40</v>
-      </c>
-      <c r="D52" t="s">
-        <v>239</v>
-      </c>
-      <c r="E52" t="s">
-        <v>240</v>
-      </c>
-      <c r="F52" t="s">
-        <v>39</v>
-      </c>
-      <c r="G52" t="s">
-        <v>44</v>
-      </c>
-      <c r="H52" t="s">
-        <v>39</v>
-      </c>
-      <c r="I52" t="s">
-        <v>182</v>
-      </c>
-      <c r="J52" t="s">
-        <v>241</v>
-      </c>
-      <c r="K52" t="s">
-        <v>39</v>
-      </c>
-      <c r="L52" t="s">
-        <v>39</v>
-      </c>
-      <c r="M52" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>185</v>
-      </c>
-      <c r="B53" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" t="s">
-        <v>40</v>
-      </c>
-      <c r="D53" t="s">
-        <v>242</v>
-      </c>
-      <c r="E53" t="s">
-        <v>243</v>
-      </c>
-      <c r="F53" t="s">
-        <v>39</v>
-      </c>
-      <c r="G53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H53" t="s">
-        <v>39</v>
-      </c>
-      <c r="I53" t="s">
-        <v>185</v>
-      </c>
-      <c r="J53" t="s">
-        <v>185</v>
-      </c>
-      <c r="K53" t="s">
-        <v>39</v>
-      </c>
-      <c r="L53" t="s">
-        <v>39</v>
-      </c>
-      <c r="M53" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>241</v>
-      </c>
-      <c r="B54" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" t="s">
-        <v>40</v>
-      </c>
-      <c r="D54" t="s">
-        <v>239</v>
-      </c>
-      <c r="E54" t="s">
-        <v>240</v>
-      </c>
-      <c r="F54" t="s">
-        <v>39</v>
-      </c>
-      <c r="G54" t="s">
-        <v>44</v>
-      </c>
-      <c r="H54" t="s">
-        <v>39</v>
-      </c>
-      <c r="I54" t="s">
-        <v>182</v>
-      </c>
-      <c r="J54" t="s">
-        <v>241</v>
-      </c>
-      <c r="K54" t="s">
-        <v>39</v>
-      </c>
-      <c r="L54" t="s">
-        <v>39</v>
-      </c>
-      <c r="M54" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>241</v>
-      </c>
-      <c r="B55" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" t="s">
-        <v>40</v>
-      </c>
-      <c r="D55" t="s">
-        <v>244</v>
-      </c>
-      <c r="E55" t="s">
-        <v>245</v>
-      </c>
-      <c r="F55" t="s">
-        <v>39</v>
-      </c>
-      <c r="G55" t="s">
-        <v>44</v>
-      </c>
-      <c r="H55" t="s">
-        <v>39</v>
-      </c>
-      <c r="I55" t="s">
-        <v>241</v>
-      </c>
-      <c r="J55" t="s">
-        <v>241</v>
-      </c>
-      <c r="K55" t="s">
-        <v>39</v>
-      </c>
-      <c r="L55" t="s">
-        <v>39</v>
-      </c>
-      <c r="M55" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>110</v>
-      </c>
-      <c r="B56" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" t="s">
-        <v>40</v>
-      </c>
-      <c r="D56" t="s">
-        <v>246</v>
-      </c>
-      <c r="E56" t="s">
-        <v>247</v>
-      </c>
-      <c r="F56" t="s">
-        <v>39</v>
-      </c>
-      <c r="G56" t="s">
-        <v>44</v>
-      </c>
-      <c r="H56" t="s">
-        <v>39</v>
-      </c>
-      <c r="I56" t="s">
-        <v>110</v>
-      </c>
-      <c r="J56" t="s">
-        <v>110</v>
-      </c>
-      <c r="K56" t="s">
-        <v>39</v>
-      </c>
-      <c r="L56" t="s">
-        <v>39</v>
-      </c>
-      <c r="M56" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>188</v>
-      </c>
-      <c r="B58" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" t="s">
-        <v>40</v>
-      </c>
-      <c r="D58" t="s">
-        <v>248</v>
-      </c>
-      <c r="E58" t="s">
-        <v>249</v>
-      </c>
-      <c r="F58" t="s">
-        <v>39</v>
-      </c>
-      <c r="G58" t="s">
-        <v>44</v>
-      </c>
-      <c r="H58" t="s">
-        <v>39</v>
-      </c>
-      <c r="I58" t="s">
-        <v>188</v>
-      </c>
-      <c r="J58" t="s">
-        <v>188</v>
-      </c>
-      <c r="K58" t="s">
-        <v>39</v>
-      </c>
-      <c r="L58" t="s">
-        <v>39</v>
-      </c>
-      <c r="M58" t="s">
-        <v>160</v>
-      </c>
-    </row>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="50" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B59" t="s">
         <v>10</v>
@@ -6829,10 +6553,10 @@
         <v>39</v>
       </c>
       <c r="I59" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J59" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K59" t="s">
         <v>39</v>
@@ -6843,7 +6567,7 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B60" t="s">
         <v>10</v>
@@ -6852,7 +6576,7 @@
         <v>40</v>
       </c>
       <c r="D60" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="E60" t="s">
         <v>127</v>
@@ -6867,10 +6591,10 @@
         <v>39</v>
       </c>
       <c r="I60" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J60" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K60" t="s">
         <v>39</v>
@@ -6879,7 +6603,7 @@
         <v>39</v>
       </c>
       <c r="M60" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -6893,7 +6617,7 @@
         <v>40</v>
       </c>
       <c r="D61" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="E61" t="s">
         <v>127</v>
@@ -6908,10 +6632,10 @@
         <v>39</v>
       </c>
       <c r="I61" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J61" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K61" t="s">
         <v>39</v>
@@ -6920,12 +6644,12 @@
         <v>39</v>
       </c>
       <c r="M61" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B62" t="s">
         <v>10</v>
@@ -6934,7 +6658,7 @@
         <v>40</v>
       </c>
       <c r="D62" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="E62" t="s">
         <v>127</v>
@@ -6949,10 +6673,10 @@
         <v>39</v>
       </c>
       <c r="I62" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J62" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K62" t="s">
         <v>39</v>
@@ -6961,7 +6685,7 @@
         <v>39</v>
       </c>
       <c r="M62" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="63" spans="5:5" x14ac:dyDescent="0.25"/>
@@ -7207,42 +6931,43 @@
     <hyperlink ref="D10" r:id="rId9"/>
     <hyperlink ref="D11" r:id="rId10"/>
     <hyperlink ref="D12" r:id="rId11"/>
-    <hyperlink ref="D15" r:id="rId12"/>
-    <hyperlink ref="D16" r:id="rId13"/>
-    <hyperlink ref="D17" r:id="rId14"/>
-    <hyperlink ref="D18" r:id="rId15"/>
-    <hyperlink ref="D19" r:id="rId16"/>
-    <hyperlink ref="D20" r:id="rId17"/>
-    <hyperlink ref="D21" r:id="rId18"/>
-    <hyperlink ref="D22" r:id="rId19"/>
-    <hyperlink ref="D37" r:id="rId20"/>
-    <hyperlink ref="D38" r:id="rId21"/>
-    <hyperlink ref="D39" r:id="rId22"/>
-    <hyperlink ref="D40" r:id="rId23"/>
-    <hyperlink ref="D41" r:id="rId24"/>
-    <hyperlink ref="D42" r:id="rId25"/>
-    <hyperlink ref="D43" r:id="rId26"/>
-    <hyperlink ref="D44" r:id="rId27"/>
-    <hyperlink ref="D45" r:id="rId28"/>
-    <hyperlink ref="D46" r:id="rId29"/>
-    <hyperlink ref="D47" r:id="rId30"/>
-    <hyperlink ref="D48" r:id="rId31"/>
-    <hyperlink ref="D49" r:id="rId32"/>
-    <hyperlink ref="D51" r:id="rId33"/>
-    <hyperlink ref="D52" r:id="rId34"/>
-    <hyperlink ref="D53" r:id="rId35"/>
-    <hyperlink ref="D54" r:id="rId36"/>
-    <hyperlink ref="D55" r:id="rId37"/>
-    <hyperlink ref="D56" r:id="rId38"/>
-    <hyperlink ref="D58" r:id="rId39"/>
-    <hyperlink ref="D60" r:id="rId40"/>
-    <hyperlink ref="D61" r:id="rId41"/>
-    <hyperlink ref="D62" r:id="rId42"/>
+    <hyperlink ref="D13" r:id="rId12"/>
+    <hyperlink ref="D15" r:id="rId13"/>
+    <hyperlink ref="D16" r:id="rId14"/>
+    <hyperlink ref="D17" r:id="rId15"/>
+    <hyperlink ref="D18" r:id="rId16"/>
+    <hyperlink ref="D19" r:id="rId17"/>
+    <hyperlink ref="D20" r:id="rId18"/>
+    <hyperlink ref="D21" r:id="rId19"/>
+    <hyperlink ref="D22" r:id="rId20"/>
+    <hyperlink ref="D28" r:id="rId21"/>
+    <hyperlink ref="D29" r:id="rId22"/>
+    <hyperlink ref="D30" r:id="rId23"/>
+    <hyperlink ref="D33" r:id="rId24"/>
+    <hyperlink ref="D34" r:id="rId25"/>
+    <hyperlink ref="D35" r:id="rId26"/>
+    <hyperlink ref="D36" r:id="rId27"/>
+    <hyperlink ref="D37" r:id="rId28"/>
+    <hyperlink ref="D38" r:id="rId29"/>
+    <hyperlink ref="D39" r:id="rId30"/>
+    <hyperlink ref="D40" r:id="rId31"/>
+    <hyperlink ref="D41" r:id="rId32"/>
+    <hyperlink ref="D42" r:id="rId33"/>
+    <hyperlink ref="D43" r:id="rId34"/>
+    <hyperlink ref="D44" r:id="rId35"/>
+    <hyperlink ref="D45" r:id="rId36"/>
+    <hyperlink ref="D46" r:id="rId37"/>
+    <hyperlink ref="D47" r:id="rId38"/>
+    <hyperlink ref="D48" r:id="rId39"/>
+    <hyperlink ref="D49" r:id="rId40"/>
+    <hyperlink ref="D60" r:id="rId41"/>
+    <hyperlink ref="D61" r:id="rId42"/>
+    <hyperlink ref="D62" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <tableParts count="1">
-    <tablePart r:id="rId43"/>
+    <tablePart r:id="rId44"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7303,7 +7028,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -7315,22 +7040,22 @@
         <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F2" t="s">
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H2" t="s">
         <v>39</v>
       </c>
       <c r="I2" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="J2" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="K2" t="s">
         <v>39</v>
@@ -7341,7 +7066,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -7353,22 +7078,22 @@
         <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="F3" t="s">
         <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H3" t="s">
         <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="J3" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="K3" t="s">
         <v>39</v>
@@ -7379,7 +7104,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -7391,22 +7116,22 @@
         <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="F4" t="s">
         <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H4" t="s">
         <v>39</v>
       </c>
       <c r="I4" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="J4" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -7417,7 +7142,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -7435,16 +7160,16 @@
         <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H5" t="s">
         <v>39</v>
       </c>
       <c r="I5" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="J5" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="K5" t="s">
         <v>39</v>
@@ -7455,7 +7180,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -7467,22 +7192,22 @@
         <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H6" t="s">
         <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="J6" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="K6" t="s">
         <v>39</v>
@@ -7493,7 +7218,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -7505,22 +7230,22 @@
         <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H7" t="s">
         <v>39</v>
       </c>
       <c r="I7" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="J7" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="K7" t="s">
         <v>39</v>
@@ -7531,7 +7256,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -7543,22 +7268,22 @@
         <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="F8" t="s">
         <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H8" t="s">
         <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="J8" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="K8" t="s">
         <v>39</v>
@@ -7581,13 +7306,13 @@
         <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F9" t="s">
         <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H9" t="s">
         <v>39</v>
@@ -7607,7 +7332,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
@@ -7619,22 +7344,22 @@
         <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="F10" t="s">
         <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H10" t="s">
         <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K10" t="s">
         <v>39</v>
@@ -7645,7 +7370,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -7657,22 +7382,22 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="F11" t="s">
         <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H11" t="s">
         <v>39</v>
       </c>
       <c r="I11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K11" t="s">
         <v>39</v>
@@ -7683,7 +7408,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
@@ -7695,22 +7420,22 @@
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H12" t="s">
         <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K12" t="s">
         <v>39</v>
@@ -7721,7 +7446,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
@@ -7733,22 +7458,22 @@
         <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H13" t="s">
         <v>39</v>
       </c>
       <c r="I13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K13" t="s">
         <v>39</v>
@@ -7759,7 +7484,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
@@ -7771,22 +7496,22 @@
         <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="F14" t="s">
         <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H14" t="s">
         <v>39</v>
       </c>
       <c r="I14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K14" t="s">
         <v>39</v>
@@ -7797,7 +7522,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B15" t="s">
         <v>6</v>
@@ -7815,16 +7540,16 @@
         <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H15" t="s">
         <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K15" t="s">
         <v>39</v>
@@ -7835,7 +7560,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
@@ -7847,22 +7572,22 @@
         <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="F16" t="s">
         <v>39</v>
       </c>
       <c r="G16" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H16" t="s">
         <v>39</v>
       </c>
       <c r="I16" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J16" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K16" t="s">
         <v>39</v>
@@ -7873,7 +7598,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
@@ -7885,22 +7610,22 @@
         <v>39</v>
       </c>
       <c r="E17" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="F17" t="s">
         <v>39</v>
       </c>
       <c r="G17" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H17" t="s">
         <v>39</v>
       </c>
       <c r="I17" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="J17" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="K17" t="s">
         <v>39</v>
@@ -7911,7 +7636,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="B18" t="s">
         <v>6</v>
@@ -7923,22 +7648,22 @@
         <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="F18" t="s">
         <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H18" t="s">
         <v>39</v>
       </c>
       <c r="I18" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="J18" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="K18" t="s">
         <v>39</v>
@@ -7949,7 +7674,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
@@ -7961,22 +7686,22 @@
         <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F19" t="s">
         <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H19" t="s">
         <v>39</v>
       </c>
       <c r="I19" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="J19" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="K19" t="s">
         <v>39</v>
@@ -7987,7 +7712,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
@@ -7999,22 +7724,22 @@
         <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="F20" t="s">
         <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H20" t="s">
         <v>39</v>
       </c>
       <c r="I20" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="J20" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="K20" t="s">
         <v>39</v>
@@ -8025,7 +7750,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s">
         <v>6</v>
@@ -8037,22 +7762,22 @@
         <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="F21" t="s">
         <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H21" t="s">
         <v>39</v>
       </c>
       <c r="I21" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="J21" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="K21" t="s">
         <v>39</v>
@@ -8063,10 +7788,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C22" t="s">
         <v>45</v>
@@ -8075,22 +7800,22 @@
         <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="F22" t="s">
         <v>39</v>
       </c>
       <c r="G22" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H22" t="s">
         <v>39</v>
       </c>
       <c r="I22" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J22" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K22" t="s">
         <v>39</v>
@@ -8101,10 +7826,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C23" t="s">
         <v>45</v>
@@ -8113,22 +7838,22 @@
         <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="F23" t="s">
         <v>39</v>
       </c>
       <c r="G23" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H23" t="s">
         <v>39</v>
       </c>
       <c r="I23" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="J23" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="K23" t="s">
         <v>39</v>
@@ -8139,7 +7864,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
@@ -8151,22 +7876,22 @@
         <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="F24" t="s">
         <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H24" t="s">
         <v>39</v>
       </c>
       <c r="I24" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J24" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K24" t="s">
         <v>39</v>
@@ -8177,7 +7902,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
@@ -8189,22 +7914,22 @@
         <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="F25" t="s">
         <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H25" t="s">
         <v>39</v>
       </c>
       <c r="I25" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J25" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K25" t="s">
         <v>39</v>
@@ -8215,7 +7940,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
@@ -8227,22 +7952,22 @@
         <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="F26" t="s">
         <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H26" t="s">
         <v>39</v>
       </c>
       <c r="I26" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J26" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K26" t="s">
         <v>39</v>
@@ -8256,7 +7981,7 @@
         <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C27" t="s">
         <v>45</v>
@@ -8265,22 +7990,22 @@
         <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="F27" t="s">
         <v>39</v>
       </c>
       <c r="G27" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H27" t="s">
         <v>39</v>
       </c>
       <c r="I27" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="J27" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="K27" t="s">
         <v>39</v>
@@ -8291,10 +8016,10 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B28" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
@@ -8303,22 +8028,22 @@
         <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="F28" t="s">
         <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H28" t="s">
         <v>39</v>
       </c>
       <c r="I28" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J28" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K28" t="s">
         <v>39</v>
@@ -8329,10 +8054,10 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B29" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C29" t="s">
         <v>45</v>
@@ -8341,22 +8066,22 @@
         <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="F29" t="s">
         <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H29" t="s">
         <v>39</v>
       </c>
       <c r="I29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J29" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K29" t="s">
         <v>39</v>
@@ -8367,10 +8092,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B30" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
@@ -8379,22 +8104,22 @@
         <v>39</v>
       </c>
       <c r="E30" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="F30" t="s">
         <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H30" t="s">
         <v>39</v>
       </c>
       <c r="I30" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J30" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K30" t="s">
         <v>39</v>
@@ -8405,10 +8130,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="B31" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C31" t="s">
         <v>45</v>
@@ -8423,16 +8148,16 @@
         <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H31" t="s">
         <v>39</v>
       </c>
       <c r="I31" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="J31" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="K31" t="s">
         <v>39</v>
@@ -8443,10 +8168,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="B32" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C32" t="s">
         <v>45</v>
@@ -8455,22 +8180,22 @@
         <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="F32" t="s">
         <v>39</v>
       </c>
       <c r="G32" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H32" t="s">
         <v>39</v>
       </c>
       <c r="I32" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="J32" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="K32" t="s">
         <v>39</v>
@@ -8481,10 +8206,10 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C33" t="s">
         <v>45</v>
@@ -8493,22 +8218,22 @@
         <v>39</v>
       </c>
       <c r="E33" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="F33" t="s">
         <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H33" t="s">
         <v>39</v>
       </c>
       <c r="I33" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="J33" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="K33" t="s">
         <v>39</v>
@@ -8519,7 +8244,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
@@ -8531,22 +8256,22 @@
         <v>39</v>
       </c>
       <c r="E34" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="F34" t="s">
         <v>39</v>
       </c>
       <c r="G34" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H34" t="s">
         <v>39</v>
       </c>
       <c r="I34" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="J34" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="K34" t="s">
         <v>39</v>
@@ -8557,7 +8282,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
@@ -8569,22 +8294,22 @@
         <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F35" t="s">
         <v>39</v>
       </c>
       <c r="G35" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H35" t="s">
         <v>39</v>
       </c>
       <c r="I35" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="J35" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="K35" t="s">
         <v>39</v>
@@ -8595,7 +8320,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
@@ -8607,19 +8332,19 @@
         <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="F36" t="s">
         <v>39</v>
       </c>
       <c r="G36" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H36" t="s">
         <v>39</v>
       </c>
       <c r="I36" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="J36" t="s">
         <v>43</v>
@@ -8633,7 +8358,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
@@ -8645,19 +8370,19 @@
         <v>39</v>
       </c>
       <c r="E37" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="F37" t="s">
         <v>39</v>
       </c>
       <c r="G37" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H37" t="s">
         <v>39</v>
       </c>
       <c r="I37" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="J37" t="s">
         <v>43</v>
@@ -8671,10 +8396,10 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B38" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C38" t="s">
         <v>45</v>
@@ -8683,22 +8408,22 @@
         <v>39</v>
       </c>
       <c r="E38" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="F38" t="s">
         <v>39</v>
       </c>
       <c r="G38" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H38" t="s">
         <v>39</v>
       </c>
       <c r="I38" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="J38" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="K38" t="s">
         <v>39</v>
@@ -8721,13 +8446,13 @@
         <v>39</v>
       </c>
       <c r="E39" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="F39" t="s">
         <v>39</v>
       </c>
       <c r="G39" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H39" t="s">
         <v>39</v>
@@ -8840,7 +8565,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -8852,22 +8577,22 @@
         <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="F2" t="s">
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H2" t="s">
         <v>39</v>
       </c>
       <c r="I2" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="J2" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="K2" t="s">
         <v>39</v>
@@ -8878,7 +8603,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -8890,22 +8615,22 @@
         <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="F3" t="s">
         <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H3" t="s">
         <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="J3" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="K3" t="s">
         <v>39</v>
@@ -8916,7 +8641,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -8928,22 +8653,22 @@
         <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="F4" t="s">
         <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H4" t="s">
         <v>39</v>
       </c>
       <c r="I4" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="J4" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -8954,7 +8679,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -8966,22 +8691,22 @@
         <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="F5" t="s">
         <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H5" t="s">
         <v>39</v>
       </c>
       <c r="I5" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="J5" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="K5" t="s">
         <v>39</v>
@@ -8992,7 +8717,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -9004,22 +8729,22 @@
         <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H6" t="s">
         <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="J6" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="K6" t="s">
         <v>39</v>
@@ -9030,7 +8755,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -9042,22 +8767,22 @@
         <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H7" t="s">
         <v>39</v>
       </c>
       <c r="I7" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="J7" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="K7" t="s">
         <v>39</v>
@@ -9068,7 +8793,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -9080,22 +8805,22 @@
         <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="F8" t="s">
         <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H8" t="s">
         <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="J8" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="K8" t="s">
         <v>39</v>
@@ -9115,7 +8840,7 @@
         <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="F9" t="s">
         <v>39</v>
@@ -9141,7 +8866,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
@@ -9153,22 +8878,22 @@
         <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="F10" t="s">
         <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H10" t="s">
         <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K10" t="s">
         <v>39</v>
@@ -9179,7 +8904,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -9197,16 +8922,16 @@
         <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H11" t="s">
         <v>39</v>
       </c>
       <c r="I11" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="J11" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="K11" t="s">
         <v>39</v>
@@ -9217,7 +8942,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -9229,19 +8954,19 @@
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H12" t="s">
         <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="J12" t="s">
         <v>43</v>
@@ -9255,7 +8980,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -9267,22 +8992,22 @@
         <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H13" t="s">
         <v>39</v>
       </c>
       <c r="I13" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="J13" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="K13" t="s">
         <v>39</v>
@@ -9293,7 +9018,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
@@ -9305,22 +9030,22 @@
         <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="F14">
         <v>-0.5</v>
       </c>
       <c r="G14" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H14" t="s">
         <v>39</v>
       </c>
       <c r="I14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K14" t="s">
         <v>39</v>
@@ -9331,7 +9056,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
@@ -9343,22 +9068,22 @@
         <v>39</v>
       </c>
       <c r="E15" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="F15" t="s">
         <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H15" t="s">
         <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K15" t="s">
         <v>39</v>
@@ -9369,10 +9094,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B16" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C16" t="s">
         <v>51</v>
@@ -9381,22 +9106,22 @@
         <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="F16" t="s">
         <v>39</v>
       </c>
       <c r="G16" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H16" t="s">
         <v>39</v>
       </c>
       <c r="I16" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="J16" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="K16" t="s">
         <v>39</v>
@@ -9407,7 +9132,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
@@ -9419,22 +9144,22 @@
         <v>39</v>
       </c>
       <c r="E17" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="F17">
         <v>-0.5</v>
       </c>
       <c r="G17" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H17" t="s">
         <v>39</v>
       </c>
       <c r="I17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K17" t="s">
         <v>39</v>
@@ -9445,7 +9170,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -9457,22 +9182,22 @@
         <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="F18" t="s">
         <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H18" t="s">
         <v>39</v>
       </c>
       <c r="I18" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J18" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K18" t="s">
         <v>39</v>
@@ -9486,7 +9211,7 @@
         <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C19" t="s">
         <v>51</v>
@@ -9495,13 +9220,13 @@
         <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="F19" t="s">
         <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H19" t="s">
         <v>39</v>
@@ -9510,7 +9235,7 @@
         <v>49</v>
       </c>
       <c r="J19" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="K19" t="s">
         <v>39</v>
@@ -9521,7 +9246,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
@@ -9533,22 +9258,22 @@
         <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="F20" t="s">
         <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H20" t="s">
         <v>39</v>
       </c>
       <c r="I20" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="J20" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="K20" t="s">
         <v>39</v>
@@ -9559,7 +9284,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s">
         <v>2</v>
@@ -9571,22 +9296,22 @@
         <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="F21" t="s">
         <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H21" t="s">
         <v>39</v>
       </c>
       <c r="I21" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J21" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K21" t="s">
         <v>39</v>
@@ -9609,13 +9334,13 @@
         <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="F22" t="s">
         <v>39</v>
       </c>
       <c r="G22" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H22" t="s">
         <v>39</v>
@@ -9624,7 +9349,7 @@
         <v>43</v>
       </c>
       <c r="J22" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="K22" t="s">
         <v>39</v>
@@ -9635,7 +9360,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s">
         <v>6</v>
@@ -9647,22 +9372,22 @@
         <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="F23">
         <v>-6</v>
       </c>
       <c r="G23" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H23" t="s">
         <v>39</v>
       </c>
       <c r="I23" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J23" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K23" t="s">
         <v>39</v>
@@ -9673,7 +9398,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="B24" t="s">
         <v>2</v>
@@ -9685,22 +9410,22 @@
         <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>207</v>
+        <v>293</v>
       </c>
       <c r="F24" t="s">
         <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H24" t="s">
         <v>39</v>
       </c>
       <c r="I24" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="J24" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="K24" t="s">
         <v>39</v>
@@ -9711,7 +9436,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="B25" t="s">
         <v>2</v>
@@ -9723,22 +9448,22 @@
         <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>208</v>
+        <v>294</v>
       </c>
       <c r="F25" t="s">
         <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H25" t="s">
         <v>39</v>
       </c>
       <c r="I25" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="J25" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="K25" t="s">
         <v>39</v>
@@ -9749,7 +9474,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="B26" t="s">
         <v>2</v>
@@ -9761,22 +9486,22 @@
         <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>210</v>
+        <v>295</v>
       </c>
       <c r="F26" t="s">
         <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H26" t="s">
         <v>39</v>
       </c>
       <c r="I26" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="J26" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="K26" t="s">
         <v>39</v>
@@ -9787,7 +9512,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
@@ -9799,22 +9524,22 @@
         <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="F27" t="s">
         <v>39</v>
       </c>
       <c r="G27" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H27" t="s">
         <v>39</v>
       </c>
       <c r="I27" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J27" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K27" t="s">
         <v>39</v>
@@ -9825,7 +9550,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B28" t="s">
         <v>4</v>
@@ -9837,22 +9562,22 @@
         <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="F28" t="s">
         <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H28" t="s">
         <v>39</v>
       </c>
       <c r="I28" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J28" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="K28" t="s">
         <v>39</v>
@@ -9863,7 +9588,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s">
         <v>6</v>
@@ -9875,22 +9600,22 @@
         <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="F29" t="s">
         <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H29" t="s">
         <v>39</v>
       </c>
       <c r="I29" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="J29" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="K29" t="s">
         <v>39</v>
@@ -9901,7 +9626,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
@@ -9919,16 +9644,16 @@
         <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H30" t="s">
         <v>39</v>
       </c>
       <c r="I30" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J30" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="K30" t="s">
         <v>39</v>
@@ -9939,7 +9664,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B31" t="s">
         <v>2</v>
@@ -9951,22 +9676,22 @@
         <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="F31" t="s">
         <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H31" t="s">
         <v>39</v>
       </c>
       <c r="I31" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J31" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K31" t="s">
         <v>39</v>
@@ -9977,7 +9702,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -9989,19 +9714,19 @@
         <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="F32" t="s">
         <v>39</v>
       </c>
       <c r="G32" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H32" t="s">
         <v>39</v>
       </c>
       <c r="I32" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="J32" t="s">
         <v>43</v>
@@ -10015,7 +9740,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
@@ -10033,16 +9758,16 @@
         <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H33" t="s">
         <v>39</v>
       </c>
       <c r="I33" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="J33" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K33" t="s">
         <v>39</v>
@@ -10053,7 +9778,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B34" t="s">
         <v>6</v>
@@ -10065,22 +9790,22 @@
         <v>39</v>
       </c>
       <c r="E34" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F34">
         <v>-4</v>
       </c>
       <c r="G34" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H34" t="s">
         <v>39</v>
       </c>
       <c r="I34" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J34" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K34" t="s">
         <v>39</v>
@@ -10091,7 +9816,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
@@ -10103,22 +9828,22 @@
         <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="F35">
         <v>-4</v>
       </c>
       <c r="G35" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H35" t="s">
         <v>39</v>
       </c>
       <c r="I35" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J35" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K35" t="s">
         <v>39</v>
@@ -10129,7 +9854,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B36" t="s">
         <v>6</v>
@@ -10147,16 +9872,16 @@
         <v>-2</v>
       </c>
       <c r="G36" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H36" t="s">
         <v>39</v>
       </c>
       <c r="I36" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J36" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K36" t="s">
         <v>39</v>
@@ -10167,7 +9892,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
@@ -10179,22 +9904,22 @@
         <v>39</v>
       </c>
       <c r="E37" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="F37">
         <v>-2</v>
       </c>
       <c r="G37" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H37" t="s">
         <v>39</v>
       </c>
       <c r="I37" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J37" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K37" t="s">
         <v>39</v>
@@ -10205,7 +9930,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="B38" t="s">
         <v>6</v>
@@ -10217,22 +9942,22 @@
         <v>39</v>
       </c>
       <c r="E38" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="F38">
         <v>-2</v>
       </c>
       <c r="G38" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H38" t="s">
         <v>39</v>
       </c>
       <c r="I38" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="J38" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="K38" t="s">
         <v>39</v>
@@ -10243,7 +9968,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
@@ -10255,22 +9980,22 @@
         <v>39</v>
       </c>
       <c r="E39" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="F39">
         <v>-4</v>
       </c>
       <c r="G39" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H39" t="s">
         <v>39</v>
       </c>
       <c r="I39" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="J39" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="K39" t="s">
         <v>39</v>
@@ -10281,7 +10006,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
@@ -10293,22 +10018,22 @@
         <v>39</v>
       </c>
       <c r="E40" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F40">
         <v>-2</v>
       </c>
       <c r="G40" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H40" t="s">
         <v>39</v>
       </c>
       <c r="I40" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="J40" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="K40" t="s">
         <v>39</v>
@@ -10319,7 +10044,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
@@ -10331,22 +10056,22 @@
         <v>39</v>
       </c>
       <c r="E41" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="F41">
         <v>-2</v>
       </c>
       <c r="G41" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H41" t="s">
         <v>39</v>
       </c>
       <c r="I41" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="J41" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="K41" t="s">
         <v>39</v>
@@ -10357,7 +10082,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="B42" t="s">
         <v>6</v>
@@ -10369,22 +10094,22 @@
         <v>39</v>
       </c>
       <c r="E42" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="F42">
         <v>-4</v>
       </c>
       <c r="G42" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H42" t="s">
         <v>39</v>
       </c>
       <c r="I42" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="J42" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="K42" t="s">
         <v>39</v>
@@ -10395,10 +10120,10 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="B43" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C43" t="s">
         <v>51</v>
@@ -10407,22 +10132,22 @@
         <v>39</v>
       </c>
       <c r="E43" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="F43" t="s">
         <v>39</v>
       </c>
       <c r="G43" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H43" t="s">
         <v>39</v>
       </c>
       <c r="I43" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="J43" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="K43" t="s">
         <v>39</v>
@@ -10433,10 +10158,10 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="B44" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C44" t="s">
         <v>51</v>
@@ -10445,22 +10170,22 @@
         <v>39</v>
       </c>
       <c r="E44" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="F44" t="s">
         <v>39</v>
       </c>
       <c r="G44" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H44" t="s">
         <v>39</v>
       </c>
       <c r="I44" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="J44" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="K44" t="s">
         <v>39</v>
@@ -10471,10 +10196,10 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B45" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C45" t="s">
         <v>51</v>
@@ -10483,22 +10208,22 @@
         <v>39</v>
       </c>
       <c r="E45" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
       </c>
       <c r="G45" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H45" t="s">
         <v>39</v>
       </c>
       <c r="I45" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="J45" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="K45" t="s">
         <v>39</v>
@@ -10509,10 +10234,10 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B46" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C46" t="s">
         <v>51</v>
@@ -10521,22 +10246,22 @@
         <v>39</v>
       </c>
       <c r="E46" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="F46" t="s">
         <v>39</v>
       </c>
       <c r="G46" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H46" t="s">
         <v>39</v>
       </c>
       <c r="I46" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="J46" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="K46" t="s">
         <v>39</v>
@@ -10547,10 +10272,10 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B47" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C47" t="s">
         <v>51</v>
@@ -10559,22 +10284,22 @@
         <v>39</v>
       </c>
       <c r="E47" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F47" t="s">
         <v>39</v>
       </c>
       <c r="G47" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H47" t="s">
         <v>39</v>
       </c>
       <c r="I47" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="J47" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="K47" t="s">
         <v>39</v>
@@ -10585,10 +10310,10 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B48" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C48" t="s">
         <v>51</v>
@@ -10597,22 +10322,22 @@
         <v>39</v>
       </c>
       <c r="E48" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="F48" t="s">
         <v>39</v>
       </c>
       <c r="G48" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H48" t="s">
         <v>39</v>
       </c>
       <c r="I48" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="J48" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="K48" t="s">
         <v>39</v>
@@ -10623,10 +10348,10 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B49" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C49" t="s">
         <v>51</v>
@@ -10635,22 +10360,22 @@
         <v>39</v>
       </c>
       <c r="E49" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="F49" t="s">
         <v>39</v>
       </c>
       <c r="G49" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H49" t="s">
         <v>39</v>
       </c>
       <c r="I49" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="J49" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="K49" t="s">
         <v>39</v>
@@ -10661,10 +10386,10 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B50" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C50" t="s">
         <v>51</v>
@@ -10673,22 +10398,22 @@
         <v>39</v>
       </c>
       <c r="E50" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="F50" t="s">
         <v>39</v>
       </c>
       <c r="G50" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H50" t="s">
         <v>39</v>
       </c>
       <c r="I50" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="J50" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="K50" t="s">
         <v>39</v>
@@ -10699,10 +10424,10 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B51" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C51" t="s">
         <v>51</v>
@@ -10711,22 +10436,22 @@
         <v>39</v>
       </c>
       <c r="E51" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F51" t="s">
         <v>39</v>
       </c>
       <c r="G51" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H51" t="s">
         <v>39</v>
       </c>
       <c r="I51" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="J51" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="K51" t="s">
         <v>39</v>
@@ -10749,13 +10474,13 @@
         <v>39</v>
       </c>
       <c r="E52" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F52" t="s">
         <v>39</v>
       </c>
       <c r="G52" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="H52" t="s">
         <v>39</v>

--- a/src/data/FML-Data.xlsx
+++ b/src/data/FML-Data.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2622" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2622" uniqueCount="308">
   <si>
     <t>Name</t>
   </si>
@@ -801,9 +801,6 @@
   </si>
   <si>
     <t>Error Page</t>
-  </si>
-  <si>
-    <t>Siddharth N</t>
   </si>
   <si>
     <t>Header &amp; Footer</t>
@@ -4780,7 +4777,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M262"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -5288,7 +5285,6 @@
         <v>160</v>
       </c>
     </row>
-    <row r="14" spans="5:5" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
@@ -5617,11 +5613,6 @@
         <v>196</v>
       </c>
     </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="5:5" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>197</v>
@@ -6518,15 +6509,6 @@
         <v>196</v>
       </c>
     </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>189</v>
@@ -6688,206 +6670,6 @@
         <v>215</v>
       </c>
     </row>
-    <row r="63" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="203" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="204" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="209" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="210" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="213" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="214" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="217" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="218" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="219" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="221" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="224" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="225" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="226" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="227" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="230" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="231" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="232" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="233" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="234" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="240" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="241" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="242" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="243" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="244" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="245" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="246" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="247" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="248" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="249" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="250" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="251" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="252" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="253" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="254" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="255" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="256" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="257" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="258" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="259" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="260" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="261" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="262" spans="5:5" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="8">
     <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid date" error="Please enter a valid date." sqref="A10:A262">
@@ -7791,7 +7573,7 @@
         <v>225</v>
       </c>
       <c r="B22" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
         <v>45</v>
@@ -7800,7 +7582,7 @@
         <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F22" t="s">
         <v>39</v>
@@ -7829,7 +7611,7 @@
         <v>240</v>
       </c>
       <c r="B23" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
         <v>45</v>
@@ -7838,7 +7620,7 @@
         <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F23" t="s">
         <v>39</v>
@@ -7876,7 +7658,7 @@
         <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F24" t="s">
         <v>39</v>
@@ -7914,7 +7696,7 @@
         <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F25" t="s">
         <v>39</v>
@@ -7952,7 +7734,7 @@
         <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F26" t="s">
         <v>39</v>
@@ -7981,7 +7763,7 @@
         <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
         <v>45</v>
@@ -7990,7 +7772,7 @@
         <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F27" t="s">
         <v>39</v>
@@ -8019,7 +7801,7 @@
         <v>197</v>
       </c>
       <c r="B28" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
@@ -8028,7 +7810,7 @@
         <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F28" t="s">
         <v>39</v>
@@ -8057,7 +7839,7 @@
         <v>201</v>
       </c>
       <c r="B29" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
         <v>45</v>
@@ -8066,7 +7848,7 @@
         <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F29" t="s">
         <v>39</v>
@@ -8095,7 +7877,7 @@
         <v>204</v>
       </c>
       <c r="B30" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
@@ -8104,7 +7886,7 @@
         <v>39</v>
       </c>
       <c r="E30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F30" t="s">
         <v>39</v>
@@ -8133,7 +7915,7 @@
         <v>163</v>
       </c>
       <c r="B31" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C31" t="s">
         <v>45</v>
@@ -8171,7 +7953,7 @@
         <v>184</v>
       </c>
       <c r="B32" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C32" t="s">
         <v>45</v>
@@ -8180,7 +7962,7 @@
         <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F32" t="s">
         <v>39</v>
@@ -8209,7 +7991,7 @@
         <v>184</v>
       </c>
       <c r="B33" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C33" t="s">
         <v>45</v>
@@ -8218,7 +8000,7 @@
         <v>39</v>
       </c>
       <c r="E33" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F33" t="s">
         <v>39</v>
@@ -8256,7 +8038,7 @@
         <v>39</v>
       </c>
       <c r="E34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F34" t="s">
         <v>39</v>
@@ -8294,7 +8076,7 @@
         <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F35" t="s">
         <v>39</v>
@@ -8332,7 +8114,7 @@
         <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F36" t="s">
         <v>39</v>
@@ -8370,7 +8152,7 @@
         <v>39</v>
       </c>
       <c r="E37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F37" t="s">
         <v>39</v>
@@ -8399,7 +8181,7 @@
         <v>248</v>
       </c>
       <c r="B38" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C38" t="s">
         <v>45</v>
@@ -8408,7 +8190,7 @@
         <v>39</v>
       </c>
       <c r="E38" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F38" t="s">
         <v>39</v>
@@ -8446,7 +8228,7 @@
         <v>39</v>
       </c>
       <c r="E39" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F39" t="s">
         <v>39</v>
@@ -8565,7 +8347,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -8577,7 +8359,7 @@
         <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F2" t="s">
         <v>39</v>
@@ -8589,10 +8371,10 @@
         <v>39</v>
       </c>
       <c r="I2" t="s">
+        <v>274</v>
+      </c>
+      <c r="J2" t="s">
         <v>275</v>
-      </c>
-      <c r="J2" t="s">
-        <v>276</v>
       </c>
       <c r="K2" t="s">
         <v>39</v>
@@ -8603,7 +8385,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -8615,7 +8397,7 @@
         <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F3" t="s">
         <v>39</v>
@@ -8627,10 +8409,10 @@
         <v>39</v>
       </c>
       <c r="I3" t="s">
+        <v>274</v>
+      </c>
+      <c r="J3" t="s">
         <v>275</v>
-      </c>
-      <c r="J3" t="s">
-        <v>276</v>
       </c>
       <c r="K3" t="s">
         <v>39</v>
@@ -8641,7 +8423,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -8653,7 +8435,7 @@
         <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F4" t="s">
         <v>39</v>
@@ -8665,10 +8447,10 @@
         <v>39</v>
       </c>
       <c r="I4" t="s">
+        <v>274</v>
+      </c>
+      <c r="J4" t="s">
         <v>275</v>
-      </c>
-      <c r="J4" t="s">
-        <v>276</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
@@ -8679,7 +8461,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -8691,7 +8473,7 @@
         <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F5" t="s">
         <v>39</v>
@@ -8703,10 +8485,10 @@
         <v>39</v>
       </c>
       <c r="I5" t="s">
+        <v>274</v>
+      </c>
+      <c r="J5" t="s">
         <v>275</v>
-      </c>
-      <c r="J5" t="s">
-        <v>276</v>
       </c>
       <c r="K5" t="s">
         <v>39</v>
@@ -8717,7 +8499,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -8729,7 +8511,7 @@
         <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
@@ -8741,10 +8523,10 @@
         <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K6" t="s">
         <v>39</v>
@@ -8755,7 +8537,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -8767,7 +8549,7 @@
         <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
@@ -8779,10 +8561,10 @@
         <v>39</v>
       </c>
       <c r="I7" t="s">
+        <v>274</v>
+      </c>
+      <c r="J7" t="s">
         <v>275</v>
-      </c>
-      <c r="J7" t="s">
-        <v>276</v>
       </c>
       <c r="K7" t="s">
         <v>39</v>
@@ -8793,7 +8575,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -8805,7 +8587,7 @@
         <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F8" t="s">
         <v>39</v>
@@ -8817,10 +8599,10 @@
         <v>39</v>
       </c>
       <c r="I8" t="s">
+        <v>274</v>
+      </c>
+      <c r="J8" t="s">
         <v>275</v>
-      </c>
-      <c r="J8" t="s">
-        <v>276</v>
       </c>
       <c r="K8" t="s">
         <v>39</v>
@@ -8840,7 +8622,7 @@
         <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F9" t="s">
         <v>39</v>
@@ -8878,7 +8660,7 @@
         <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F10" t="s">
         <v>39</v>
@@ -8904,7 +8686,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -8928,10 +8710,10 @@
         <v>39</v>
       </c>
       <c r="I11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K11" t="s">
         <v>39</v>
@@ -8942,7 +8724,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -8954,7 +8736,7 @@
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
@@ -8966,7 +8748,7 @@
         <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J12" t="s">
         <v>43</v>
@@ -8992,7 +8774,7 @@
         <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
@@ -9068,7 +8850,7 @@
         <v>39</v>
       </c>
       <c r="E15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F15" t="s">
         <v>39</v>
@@ -9094,10 +8876,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B16" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
         <v>51</v>
@@ -9106,7 +8888,7 @@
         <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F16" t="s">
         <v>39</v>
@@ -9118,10 +8900,10 @@
         <v>39</v>
       </c>
       <c r="I16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K16" t="s">
         <v>39</v>
@@ -9182,7 +8964,7 @@
         <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F18" t="s">
         <v>39</v>
@@ -9211,7 +8993,7 @@
         <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
         <v>51</v>
@@ -9220,7 +9002,7 @@
         <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F19" t="s">
         <v>39</v>
@@ -9235,7 +9017,7 @@
         <v>49</v>
       </c>
       <c r="J19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K19" t="s">
         <v>39</v>
@@ -9246,7 +9028,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
@@ -9258,7 +9040,7 @@
         <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F20" t="s">
         <v>39</v>
@@ -9270,10 +9052,10 @@
         <v>39</v>
       </c>
       <c r="I20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K20" t="s">
         <v>39</v>
@@ -9296,7 +9078,7 @@
         <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F21" t="s">
         <v>39</v>
@@ -9334,7 +9116,7 @@
         <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F22" t="s">
         <v>39</v>
@@ -9349,7 +9131,7 @@
         <v>43</v>
       </c>
       <c r="J22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K22" t="s">
         <v>39</v>
@@ -9410,7 +9192,7 @@
         <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F24" t="s">
         <v>39</v>
@@ -9448,7 +9230,7 @@
         <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F25" t="s">
         <v>39</v>
@@ -9486,7 +9268,7 @@
         <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F26" t="s">
         <v>39</v>
@@ -9524,7 +9306,7 @@
         <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F27" t="s">
         <v>39</v>
@@ -9562,7 +9344,7 @@
         <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F28" t="s">
         <v>39</v>
@@ -9588,7 +9370,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s">
         <v>6</v>
@@ -9600,7 +9382,7 @@
         <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F29" t="s">
         <v>39</v>
@@ -9612,10 +9394,10 @@
         <v>39</v>
       </c>
       <c r="I29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J29" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K29" t="s">
         <v>39</v>
@@ -9676,7 +9458,7 @@
         <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F31" t="s">
         <v>39</v>
@@ -9702,7 +9484,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -9714,7 +9496,7 @@
         <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F32" t="s">
         <v>39</v>
@@ -9726,7 +9508,7 @@
         <v>39</v>
       </c>
       <c r="I32" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J32" t="s">
         <v>43</v>
@@ -10120,10 +9902,10 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B43" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C43" t="s">
         <v>51</v>
@@ -10132,7 +9914,7 @@
         <v>39</v>
       </c>
       <c r="E43" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F43" t="s">
         <v>39</v>
@@ -10144,10 +9926,10 @@
         <v>39</v>
       </c>
       <c r="I43" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J43" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K43" t="s">
         <v>39</v>
@@ -10158,10 +9940,10 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B44" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
         <v>51</v>
@@ -10170,7 +9952,7 @@
         <v>39</v>
       </c>
       <c r="E44" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F44" t="s">
         <v>39</v>
@@ -10182,10 +9964,10 @@
         <v>39</v>
       </c>
       <c r="I44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K44" t="s">
         <v>39</v>
@@ -10196,10 +9978,10 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B45" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
         <v>51</v>
@@ -10208,7 +9990,7 @@
         <v>39</v>
       </c>
       <c r="E45" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
@@ -10220,10 +10002,10 @@
         <v>39</v>
       </c>
       <c r="I45" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J45" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K45" t="s">
         <v>39</v>
@@ -10234,10 +10016,10 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B46" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C46" t="s">
         <v>51</v>
@@ -10246,7 +10028,7 @@
         <v>39</v>
       </c>
       <c r="E46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F46" t="s">
         <v>39</v>
@@ -10258,10 +10040,10 @@
         <v>39</v>
       </c>
       <c r="I46" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J46" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K46" t="s">
         <v>39</v>
@@ -10272,10 +10054,10 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B47" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C47" t="s">
         <v>51</v>
@@ -10284,7 +10066,7 @@
         <v>39</v>
       </c>
       <c r="E47" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F47" t="s">
         <v>39</v>
@@ -10296,10 +10078,10 @@
         <v>39</v>
       </c>
       <c r="I47" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J47" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K47" t="s">
         <v>39</v>
@@ -10310,10 +10092,10 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B48" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C48" t="s">
         <v>51</v>
@@ -10322,7 +10104,7 @@
         <v>39</v>
       </c>
       <c r="E48" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F48" t="s">
         <v>39</v>
@@ -10334,10 +10116,10 @@
         <v>39</v>
       </c>
       <c r="I48" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J48" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K48" t="s">
         <v>39</v>
@@ -10348,10 +10130,10 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B49" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C49" t="s">
         <v>51</v>
@@ -10360,7 +10142,7 @@
         <v>39</v>
       </c>
       <c r="E49" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F49" t="s">
         <v>39</v>
@@ -10372,10 +10154,10 @@
         <v>39</v>
       </c>
       <c r="I49" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J49" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K49" t="s">
         <v>39</v>
@@ -10386,10 +10168,10 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B50" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C50" t="s">
         <v>51</v>
@@ -10398,7 +10180,7 @@
         <v>39</v>
       </c>
       <c r="E50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F50" t="s">
         <v>39</v>
@@ -10410,10 +10192,10 @@
         <v>39</v>
       </c>
       <c r="I50" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J50" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K50" t="s">
         <v>39</v>
@@ -10424,10 +10206,10 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B51" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="C51" t="s">
         <v>51</v>
@@ -10436,7 +10218,7 @@
         <v>39</v>
       </c>
       <c r="E51" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F51" t="s">
         <v>39</v>
@@ -10448,10 +10230,10 @@
         <v>39</v>
       </c>
       <c r="I51" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J51" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K51" t="s">
         <v>39</v>
@@ -10474,7 +10256,7 @@
         <v>39</v>
       </c>
       <c r="E52" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F52" t="s">
         <v>39</v>

--- a/src/data/FML-Data.xlsx
+++ b/src/data/FML-Data.xlsx
@@ -5955,6 +5955,9 @@
         <v>105</v>
       </c>
     </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>219</v>
@@ -6851,6 +6854,15 @@
         <v>204</v>
       </c>
     </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>207</v>

--- a/src/data/FML-Data.xlsx
+++ b/src/data/FML-Data.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2719" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2721" uniqueCount="331">
   <si>
     <t>Name</t>
   </si>
@@ -2002,7 +2002,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2146,6 +2146,17 @@
       </c>
       <c r="C13">
         <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/src/data/FML-Data.xlsx
+++ b/src/data/FML-Data.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2721" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2723" uniqueCount="331">
   <si>
     <t>Name</t>
   </si>
@@ -2002,7 +2002,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2157,6 +2157,17 @@
       </c>
       <c r="C14">
         <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/src/data/FML-Data.xlsx
+++ b/src/data/FML-Data.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2723" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2721" uniqueCount="331">
   <si>
     <t>Name</t>
   </si>
@@ -2002,7 +2002,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2046,7 +2046,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>17.1</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2076,21 +2076,21 @@
         <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>56</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2098,10 +2098,10 @@
         <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>35</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2109,10 +2109,10 @@
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C10">
-        <v>66</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2120,10 +2120,10 @@
         <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>15.8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2131,10 +2131,10 @@
         <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C12">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2142,10 +2142,10 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>30</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2153,20 +2153,9 @@
         <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15">
         <v>32</v>
       </c>
     </row>
@@ -6019,6 +6008,9 @@
         <v>108</v>
       </c>
     </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>222</v>
@@ -6915,6 +6907,15 @@
         <v>207</v>
       </c>
     </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>210</v>

--- a/src/data/FML-Data.xlsx
+++ b/src/data/FML-Data.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2830" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2844" uniqueCount="376">
   <si>
     <t>Name</t>
   </si>
@@ -216,6 +216,15 @@
   </si>
   <si>
     <t>Hours</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Jira</t>
+  </si>
+  <si>
+    <t>Manual</t>
   </si>
   <si>
     <t>Date</t>
@@ -2139,10 +2148,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>63</v>
       </c>
@@ -2152,8 +2161,11 @@
       <c r="C1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -2163,8 +2175,11 @@
       <c r="C2">
         <v>83.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -2174,8 +2189,11 @@
       <c r="C3">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>48</v>
       </c>
@@ -2185,8 +2203,11 @@
       <c r="C4">
         <v>20.8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>48</v>
       </c>
@@ -2196,8 +2217,11 @@
       <c r="C5">
         <v>29</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>48</v>
       </c>
@@ -2207,8 +2231,11 @@
       <c r="C6">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>48</v>
       </c>
@@ -2218,8 +2245,11 @@
       <c r="C7">
         <v>56</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -2229,8 +2259,11 @@
       <c r="C8">
         <v>35</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -2240,8 +2273,11 @@
       <c r="C9">
         <v>66</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -2251,8 +2287,11 @@
       <c r="C10">
         <v>15.8</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -2262,8 +2301,11 @@
       <c r="C11">
         <v>47</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -2273,8 +2315,11 @@
       <c r="C12">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -2284,8 +2329,11 @@
       <c r="C13">
         <v>61</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -2294,6 +2342,9 @@
       </c>
       <c r="C14">
         <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2327,7 +2378,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B1" t="s">
         <v>64</v>
@@ -2336,39 +2387,39 @@
         <v>63</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -2377,39 +2428,39 @@
         <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F2" t="s">
         <v>5</v>
       </c>
       <c r="G2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" t="s">
         <v>80</v>
       </c>
-      <c r="H2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" t="s">
-        <v>77</v>
-      </c>
       <c r="J2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K2" t="s">
         <v>5</v>
       </c>
       <c r="L2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -2418,39 +2469,39 @@
         <v>41</v>
       </c>
       <c r="D3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
         <v>83</v>
       </c>
-      <c r="E3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
         <v>80</v>
       </c>
-      <c r="H3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" t="s">
-        <v>77</v>
-      </c>
       <c r="J3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" t="s">
+        <v>88</v>
+      </c>
+      <c r="M3" t="s">
         <v>85</v>
-      </c>
-      <c r="K3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L3" t="s">
-        <v>85</v>
-      </c>
-      <c r="M3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
@@ -2459,39 +2510,39 @@
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
       </c>
       <c r="G4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" t="s">
         <v>80</v>
       </c>
-      <c r="H4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" t="s">
-        <v>77</v>
-      </c>
       <c r="J4" t="s">
+        <v>88</v>
+      </c>
+      <c r="K4" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M4" t="s">
         <v>85</v>
-      </c>
-      <c r="K4" t="s">
-        <v>5</v>
-      </c>
-      <c r="L4" t="s">
-        <v>85</v>
-      </c>
-      <c r="M4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -2500,39 +2551,39 @@
         <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F5" t="s">
         <v>5</v>
       </c>
       <c r="G5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" t="s">
         <v>80</v>
       </c>
-      <c r="H5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" t="s">
-        <v>77</v>
-      </c>
       <c r="J5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K5" t="s">
         <v>5</v>
       </c>
       <c r="L5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
@@ -2541,39 +2592,39 @@
         <v>41</v>
       </c>
       <c r="D6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" t="s">
         <v>83</v>
       </c>
-      <c r="E6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" t="s">
         <v>80</v>
       </c>
-      <c r="H6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I6" t="s">
-        <v>77</v>
-      </c>
       <c r="J6" t="s">
+        <v>88</v>
+      </c>
+      <c r="K6" t="s">
+        <v>5</v>
+      </c>
+      <c r="L6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M6" t="s">
         <v>85</v>
-      </c>
-      <c r="K6" t="s">
-        <v>5</v>
-      </c>
-      <c r="L6" t="s">
-        <v>85</v>
-      </c>
-      <c r="M6" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
@@ -2582,39 +2633,39 @@
         <v>41</v>
       </c>
       <c r="D7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J7" t="s">
         <v>88</v>
       </c>
-      <c r="E7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7" t="s">
-        <v>81</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7" t="s">
         <v>85</v>
-      </c>
-      <c r="K7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L7" t="s">
-        <v>85</v>
-      </c>
-      <c r="M7" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
@@ -2623,34 +2674,34 @@
         <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F8" t="s">
         <v>5</v>
       </c>
       <c r="G8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" t="s">
         <v>80</v>
       </c>
-      <c r="H8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8" t="s">
-        <v>77</v>
-      </c>
       <c r="J8" t="s">
+        <v>88</v>
+      </c>
+      <c r="K8" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M8" t="s">
         <v>85</v>
-      </c>
-      <c r="K8" t="s">
-        <v>5</v>
-      </c>
-      <c r="L8" t="s">
-        <v>85</v>
-      </c>
-      <c r="M8" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -2664,16 +2715,16 @@
         <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
       <c r="G9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s">
         <v>5</v>
@@ -2682,16 +2733,16 @@
         <v>61</v>
       </c>
       <c r="J9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K9" t="s">
         <v>5</v>
       </c>
       <c r="L9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -2705,16 +2756,16 @@
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s">
         <v>5</v>
@@ -2723,16 +2774,16 @@
         <v>61</v>
       </c>
       <c r="J10" t="s">
+        <v>88</v>
+      </c>
+      <c r="K10" t="s">
+        <v>5</v>
+      </c>
+      <c r="L10" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" t="s">
         <v>85</v>
-      </c>
-      <c r="K10" t="s">
-        <v>5</v>
-      </c>
-      <c r="L10" t="s">
-        <v>85</v>
-      </c>
-      <c r="M10" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -2746,16 +2797,16 @@
         <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
@@ -2764,16 +2815,16 @@
         <v>61</v>
       </c>
       <c r="J11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K11" t="s">
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -2787,39 +2838,39 @@
         <v>41</v>
       </c>
       <c r="D12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I12" t="s">
+        <v>84</v>
+      </c>
+      <c r="J12" t="s">
         <v>88</v>
       </c>
-      <c r="E12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F12" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" t="s">
-        <v>5</v>
-      </c>
-      <c r="I12" t="s">
-        <v>81</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L12" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" t="s">
         <v>85</v>
-      </c>
-      <c r="K12" t="s">
-        <v>5</v>
-      </c>
-      <c r="L12" t="s">
-        <v>85</v>
-      </c>
-      <c r="M12" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
@@ -2828,16 +2879,16 @@
         <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
       </c>
       <c r="G13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s">
         <v>5</v>
@@ -2846,21 +2897,21 @@
         <v>61</v>
       </c>
       <c r="J13" t="s">
+        <v>88</v>
+      </c>
+      <c r="K13" t="s">
+        <v>5</v>
+      </c>
+      <c r="L13" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" t="s">
         <v>85</v>
-      </c>
-      <c r="K13" t="s">
-        <v>5</v>
-      </c>
-      <c r="L13" t="s">
-        <v>85</v>
-      </c>
-      <c r="M13" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
@@ -2869,39 +2920,39 @@
         <v>41</v>
       </c>
       <c r="D14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" t="s">
         <v>83</v>
       </c>
-      <c r="E14" t="s">
-        <v>84</v>
-      </c>
-      <c r="F14" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" t="s">
         <v>80</v>
       </c>
-      <c r="H14" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" t="s">
-        <v>77</v>
-      </c>
       <c r="J14" t="s">
+        <v>88</v>
+      </c>
+      <c r="K14" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" t="s">
         <v>85</v>
-      </c>
-      <c r="K14" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" t="s">
-        <v>85</v>
-      </c>
-      <c r="M14" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
@@ -2910,39 +2961,39 @@
         <v>41</v>
       </c>
       <c r="D15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15" t="s">
+        <v>84</v>
+      </c>
+      <c r="J15" t="s">
         <v>88</v>
       </c>
-      <c r="E15" t="s">
-        <v>89</v>
-      </c>
-      <c r="F15" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15" t="s">
-        <v>5</v>
-      </c>
-      <c r="I15" t="s">
-        <v>81</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
+        <v>5</v>
+      </c>
+      <c r="L15" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" t="s">
         <v>85</v>
-      </c>
-      <c r="K15" t="s">
-        <v>5</v>
-      </c>
-      <c r="L15" t="s">
-        <v>85</v>
-      </c>
-      <c r="M15" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
@@ -2951,39 +3002,39 @@
         <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F16" t="s">
         <v>5</v>
       </c>
       <c r="G16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" t="s">
+        <v>5</v>
+      </c>
+      <c r="I16" t="s">
         <v>80</v>
       </c>
-      <c r="H16" t="s">
-        <v>5</v>
-      </c>
-      <c r="I16" t="s">
-        <v>77</v>
-      </c>
       <c r="J16" t="s">
+        <v>88</v>
+      </c>
+      <c r="K16" t="s">
+        <v>5</v>
+      </c>
+      <c r="L16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M16" t="s">
         <v>85</v>
-      </c>
-      <c r="K16" t="s">
-        <v>5</v>
-      </c>
-      <c r="L16" t="s">
-        <v>85</v>
-      </c>
-      <c r="M16" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B17" t="s">
         <v>3</v>
@@ -2992,16 +3043,16 @@
         <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F17" t="s">
         <v>5</v>
       </c>
       <c r="G17" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H17" t="s">
         <v>5</v>
@@ -3010,21 +3061,21 @@
         <v>61</v>
       </c>
       <c r="J17" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
       </c>
       <c r="L17" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M17" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
@@ -3033,39 +3084,39 @@
         <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F18" t="s">
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H18" t="s">
         <v>5</v>
       </c>
       <c r="I18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
       </c>
       <c r="L18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M18" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
@@ -3074,39 +3125,39 @@
         <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F19" t="s">
         <v>5</v>
       </c>
       <c r="G19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H19" t="s">
         <v>5</v>
       </c>
       <c r="I19" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J19" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
       </c>
       <c r="L19" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M19" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -3115,16 +3166,16 @@
         <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F20" t="s">
         <v>5</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s">
         <v>5</v>
@@ -3133,21 +3184,21 @@
         <v>61</v>
       </c>
       <c r="J20" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
       </c>
       <c r="L20" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M20" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -3156,39 +3207,39 @@
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F21" t="s">
         <v>5</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s">
         <v>5</v>
       </c>
       <c r="I21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
       </c>
       <c r="L21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="M21" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
@@ -3197,39 +3248,39 @@
         <v>41</v>
       </c>
       <c r="D22" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" t="s">
         <v>104</v>
       </c>
-      <c r="E22" t="s">
-        <v>105</v>
-      </c>
-      <c r="F22" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" t="s">
-        <v>80</v>
-      </c>
-      <c r="H22" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" t="s">
-        <v>101</v>
-      </c>
       <c r="J22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K22" t="s">
         <v>5</v>
       </c>
       <c r="L22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="M22" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
@@ -3238,39 +3289,39 @@
         <v>41</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E23" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F23" t="s">
         <v>5</v>
       </c>
       <c r="G23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s">
         <v>5</v>
       </c>
       <c r="I23" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J23" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K23" t="s">
         <v>5</v>
       </c>
       <c r="L23" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M23" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
@@ -3279,39 +3330,39 @@
         <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E24" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F24" t="s">
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H24" t="s">
         <v>5</v>
       </c>
       <c r="I24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
       </c>
       <c r="L24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M24" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B25" t="s">
         <v>3</v>
@@ -3320,39 +3371,39 @@
         <v>41</v>
       </c>
       <c r="D25" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" t="s">
+        <v>116</v>
+      </c>
+      <c r="F25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" t="s">
+        <v>5</v>
+      </c>
+      <c r="I25" t="s">
+        <v>109</v>
+      </c>
+      <c r="J25" t="s">
+        <v>109</v>
+      </c>
+      <c r="K25" t="s">
+        <v>5</v>
+      </c>
+      <c r="L25" t="s">
+        <v>109</v>
+      </c>
+      <c r="M25" t="s">
         <v>112</v>
-      </c>
-      <c r="E25" t="s">
-        <v>113</v>
-      </c>
-      <c r="F25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G25" t="s">
-        <v>80</v>
-      </c>
-      <c r="H25" t="s">
-        <v>5</v>
-      </c>
-      <c r="I25" t="s">
-        <v>106</v>
-      </c>
-      <c r="J25" t="s">
-        <v>106</v>
-      </c>
-      <c r="K25" t="s">
-        <v>5</v>
-      </c>
-      <c r="L25" t="s">
-        <v>106</v>
-      </c>
-      <c r="M25" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
@@ -3361,39 +3412,39 @@
         <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F26" t="s">
         <v>5</v>
       </c>
       <c r="G26" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s">
         <v>5</v>
       </c>
       <c r="I26" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J26" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
       </c>
       <c r="L26" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M26" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
@@ -3402,39 +3453,39 @@
         <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E27" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F27" t="s">
         <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s">
         <v>5</v>
       </c>
       <c r="I27" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J27" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
       </c>
       <c r="L27" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M27" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B28" t="s">
         <v>3</v>
@@ -3443,10 +3494,10 @@
         <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
@@ -3458,24 +3509,24 @@
         <v>5</v>
       </c>
       <c r="I28" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J28" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
       </c>
       <c r="L28" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M28" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B29" t="s">
         <v>3</v>
@@ -3487,28 +3538,28 @@
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F29" t="s">
         <v>5</v>
       </c>
       <c r="G29" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s">
         <v>5</v>
       </c>
       <c r="I29" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J29" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K29" t="s">
         <v>5</v>
       </c>
       <c r="L29" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -3522,16 +3573,16 @@
         <v>41</v>
       </c>
       <c r="D30" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F30" t="s">
         <v>5</v>
       </c>
       <c r="G30" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s">
         <v>5</v>
@@ -3540,16 +3591,16 @@
         <v>45</v>
       </c>
       <c r="J30" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
       </c>
       <c r="L30" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="M30" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -3563,16 +3614,16 @@
         <v>41</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F31" t="s">
         <v>5</v>
       </c>
       <c r="G31" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s">
         <v>5</v>
@@ -3581,21 +3632,21 @@
         <v>45</v>
       </c>
       <c r="J31" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
       </c>
       <c r="L31" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="M31" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B32" t="s">
         <v>6</v>
@@ -3604,39 +3655,39 @@
         <v>41</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E32" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F32" t="s">
         <v>5</v>
       </c>
       <c r="G32" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s">
         <v>5</v>
       </c>
       <c r="I32" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J32" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
       </c>
       <c r="L32" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="M32" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B33" t="s">
         <v>6</v>
@@ -3645,16 +3696,16 @@
         <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F33" t="s">
         <v>5</v>
       </c>
       <c r="G33" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H33" t="s">
         <v>5</v>
@@ -3663,21 +3714,21 @@
         <v>45</v>
       </c>
       <c r="J33" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
       </c>
       <c r="L33" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="M33" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B34" t="s">
         <v>6</v>
@@ -3686,39 +3737,39 @@
         <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E34" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F34" t="s">
         <v>5</v>
       </c>
       <c r="G34" t="s">
+        <v>83</v>
+      </c>
+      <c r="H34" t="s">
+        <v>5</v>
+      </c>
+      <c r="I34" t="s">
         <v>80</v>
       </c>
-      <c r="H34" t="s">
-        <v>5</v>
-      </c>
-      <c r="I34" t="s">
-        <v>77</v>
-      </c>
       <c r="J34" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
       </c>
       <c r="L34" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M34" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
@@ -3727,34 +3778,34 @@
         <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E35" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F35" t="s">
         <v>5</v>
       </c>
       <c r="G35" t="s">
+        <v>83</v>
+      </c>
+      <c r="H35" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" t="s">
         <v>80</v>
       </c>
-      <c r="H35" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" t="s">
-        <v>77</v>
-      </c>
       <c r="J35" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K35" t="s">
         <v>5</v>
       </c>
       <c r="L35" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M35" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -3768,16 +3819,16 @@
         <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E36" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F36" t="s">
         <v>5</v>
       </c>
       <c r="G36" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s">
         <v>5</v>
@@ -3795,7 +3846,7 @@
         <v>61</v>
       </c>
       <c r="M36" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -3809,16 +3860,16 @@
         <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E37" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F37" t="s">
         <v>5</v>
       </c>
       <c r="G37" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s">
         <v>5</v>
@@ -3836,12 +3887,12 @@
         <v>61</v>
       </c>
       <c r="M37" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B38" t="s">
         <v>6</v>
@@ -3850,22 +3901,22 @@
         <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E38" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F38" t="s">
         <v>5</v>
       </c>
       <c r="G38" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s">
         <v>5</v>
       </c>
       <c r="I38" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J38" t="s">
         <v>56</v>
@@ -3877,12 +3928,12 @@
         <v>56</v>
       </c>
       <c r="M38" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
@@ -3891,22 +3942,22 @@
         <v>41</v>
       </c>
       <c r="D39" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E39" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F39" t="s">
         <v>5</v>
       </c>
       <c r="G39" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H39" t="s">
         <v>5</v>
       </c>
       <c r="I39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J39" t="s">
         <v>56</v>
@@ -3918,12 +3969,12 @@
         <v>56</v>
       </c>
       <c r="M39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
@@ -3932,22 +3983,22 @@
         <v>41</v>
       </c>
       <c r="D40" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E40" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F40" t="s">
         <v>5</v>
       </c>
       <c r="G40" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s">
         <v>5</v>
       </c>
       <c r="I40" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J40" t="s">
         <v>56</v>
@@ -3959,12 +4010,12 @@
         <v>56</v>
       </c>
       <c r="M40" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
@@ -3973,22 +4024,22 @@
         <v>41</v>
       </c>
       <c r="D41" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E41" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F41" t="s">
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s">
         <v>5</v>
       </c>
       <c r="I41" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J41" t="s">
         <v>56</v>
@@ -4000,7 +4051,7 @@
         <v>56</v>
       </c>
       <c r="M41" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
@@ -4014,22 +4065,22 @@
         <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E42" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F42" t="s">
         <v>5</v>
       </c>
       <c r="G42" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H42" t="s">
         <v>5</v>
       </c>
       <c r="I42" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J42" t="s">
         <v>56</v>
@@ -4041,7 +4092,7 @@
         <v>56</v>
       </c>
       <c r="M42" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
@@ -4055,16 +4106,16 @@
         <v>41</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E43" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F43" t="s">
         <v>5</v>
       </c>
       <c r="G43" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s">
         <v>5</v>
@@ -4073,16 +4124,16 @@
         <v>61</v>
       </c>
       <c r="J43" t="s">
+        <v>88</v>
+      </c>
+      <c r="K43" t="s">
+        <v>5</v>
+      </c>
+      <c r="L43" t="s">
+        <v>88</v>
+      </c>
+      <c r="M43" t="s">
         <v>85</v>
-      </c>
-      <c r="K43" t="s">
-        <v>5</v>
-      </c>
-      <c r="L43" t="s">
-        <v>85</v>
-      </c>
-      <c r="M43" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -4096,16 +4147,16 @@
         <v>41</v>
       </c>
       <c r="D44" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E44" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F44" t="s">
         <v>5</v>
       </c>
       <c r="G44" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s">
         <v>5</v>
@@ -4114,16 +4165,16 @@
         <v>61</v>
       </c>
       <c r="J44" t="s">
+        <v>88</v>
+      </c>
+      <c r="K44" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" t="s">
+        <v>88</v>
+      </c>
+      <c r="M44" t="s">
         <v>85</v>
-      </c>
-      <c r="K44" t="s">
-        <v>5</v>
-      </c>
-      <c r="L44" t="s">
-        <v>85</v>
-      </c>
-      <c r="M44" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -4137,16 +4188,16 @@
         <v>41</v>
       </c>
       <c r="D45" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E45" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F45" t="s">
         <v>5</v>
       </c>
       <c r="G45" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s">
         <v>5</v>
@@ -4155,21 +4206,21 @@
         <v>61</v>
       </c>
       <c r="J45" t="s">
+        <v>88</v>
+      </c>
+      <c r="K45" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" t="s">
+        <v>88</v>
+      </c>
+      <c r="M45" t="s">
         <v>85</v>
-      </c>
-      <c r="K45" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" t="s">
-        <v>85</v>
-      </c>
-      <c r="M45" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
@@ -4178,16 +4229,16 @@
         <v>41</v>
       </c>
       <c r="D46" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E46" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F46" t="s">
         <v>5</v>
       </c>
       <c r="G46" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s">
         <v>5</v>
@@ -4196,21 +4247,21 @@
         <v>61</v>
       </c>
       <c r="J46" t="s">
+        <v>88</v>
+      </c>
+      <c r="K46" t="s">
+        <v>5</v>
+      </c>
+      <c r="L46" t="s">
+        <v>88</v>
+      </c>
+      <c r="M46" t="s">
         <v>85</v>
-      </c>
-      <c r="K46" t="s">
-        <v>5</v>
-      </c>
-      <c r="L46" t="s">
-        <v>85</v>
-      </c>
-      <c r="M46" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B47" t="s">
         <v>9</v>
@@ -4219,16 +4270,16 @@
         <v>41</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E47" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F47" t="s">
         <v>5</v>
       </c>
       <c r="G47" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s">
         <v>5</v>
@@ -4237,21 +4288,21 @@
         <v>61</v>
       </c>
       <c r="J47" t="s">
+        <v>88</v>
+      </c>
+      <c r="K47" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" t="s">
+        <v>88</v>
+      </c>
+      <c r="M47" t="s">
         <v>85</v>
-      </c>
-      <c r="K47" t="s">
-        <v>5</v>
-      </c>
-      <c r="L47" t="s">
-        <v>85</v>
-      </c>
-      <c r="M47" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
@@ -4260,16 +4311,16 @@
         <v>41</v>
       </c>
       <c r="D48" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E48" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F48" t="s">
         <v>5</v>
       </c>
       <c r="G48" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s">
         <v>5</v>
@@ -4278,21 +4329,21 @@
         <v>61</v>
       </c>
       <c r="J48" t="s">
+        <v>88</v>
+      </c>
+      <c r="K48" t="s">
+        <v>5</v>
+      </c>
+      <c r="L48" t="s">
+        <v>88</v>
+      </c>
+      <c r="M48" t="s">
         <v>85</v>
-      </c>
-      <c r="K48" t="s">
-        <v>5</v>
-      </c>
-      <c r="L48" t="s">
-        <v>85</v>
-      </c>
-      <c r="M48" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
@@ -4301,39 +4352,39 @@
         <v>41</v>
       </c>
       <c r="D49" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F49" t="s">
         <v>5</v>
       </c>
       <c r="G49" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s">
         <v>5</v>
       </c>
       <c r="I49" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J49" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
       </c>
       <c r="L49" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="M49" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B50" t="s">
         <v>9</v>
@@ -4342,39 +4393,39 @@
         <v>41</v>
       </c>
       <c r="D50" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E50" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F50" t="s">
         <v>5</v>
       </c>
       <c r="G50" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H50" t="s">
         <v>5</v>
       </c>
       <c r="I50" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J50" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K50" t="s">
         <v>5</v>
       </c>
       <c r="L50" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="M50" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B51" t="s">
         <v>9</v>
@@ -4383,39 +4434,39 @@
         <v>41</v>
       </c>
       <c r="D51" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E51" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F51" t="s">
         <v>5</v>
       </c>
       <c r="G51" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s">
         <v>5</v>
       </c>
       <c r="I51" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J51" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
       </c>
       <c r="L51" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="M51" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B52" t="s">
         <v>9</v>
@@ -4424,34 +4475,34 @@
         <v>41</v>
       </c>
       <c r="D52" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E52" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F52" t="s">
         <v>5</v>
       </c>
       <c r="G52" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s">
         <v>5</v>
       </c>
       <c r="I52" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J52" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K52" t="s">
         <v>5</v>
       </c>
       <c r="L52" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="M52" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -4465,16 +4516,16 @@
         <v>41</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E53" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F53" t="s">
         <v>5</v>
       </c>
       <c r="G53" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s">
         <v>5</v>
@@ -4492,7 +4543,7 @@
         <v>45</v>
       </c>
       <c r="M53" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
@@ -4506,16 +4557,16 @@
         <v>41</v>
       </c>
       <c r="D54" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E54" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F54" t="s">
         <v>5</v>
       </c>
       <c r="G54" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s">
         <v>5</v>
@@ -4533,7 +4584,7 @@
         <v>45</v>
       </c>
       <c r="M54" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -4547,16 +4598,16 @@
         <v>41</v>
       </c>
       <c r="D55" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E55" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F55" t="s">
         <v>5</v>
       </c>
       <c r="G55" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H55" t="s">
         <v>5</v>
@@ -4574,7 +4625,7 @@
         <v>50</v>
       </c>
       <c r="M55" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -4588,16 +4639,16 @@
         <v>41</v>
       </c>
       <c r="D56" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E56" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F56" t="s">
         <v>5</v>
       </c>
       <c r="G56" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H56" t="s">
         <v>5</v>
@@ -4615,12 +4666,12 @@
         <v>50</v>
       </c>
       <c r="M56" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B57" t="s">
         <v>10</v>
@@ -4629,39 +4680,39 @@
         <v>41</v>
       </c>
       <c r="D57" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E57" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F57" t="s">
         <v>5</v>
       </c>
       <c r="G57" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H57" t="s">
         <v>5</v>
       </c>
       <c r="I57" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J57" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K57" t="s">
         <v>5</v>
       </c>
       <c r="L57" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="M57" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
@@ -4670,39 +4721,39 @@
         <v>41</v>
       </c>
       <c r="D58" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E58" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F58" t="s">
         <v>5</v>
       </c>
       <c r="G58" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H58" t="s">
         <v>5</v>
       </c>
       <c r="I58" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J58" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K58" t="s">
         <v>5</v>
       </c>
       <c r="L58" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="M58" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B59" t="s">
         <v>10</v>
@@ -4711,39 +4762,39 @@
         <v>41</v>
       </c>
       <c r="D59" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E59" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F59" t="s">
         <v>5</v>
       </c>
       <c r="G59" t="s">
+        <v>83</v>
+      </c>
+      <c r="H59" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" t="s">
         <v>80</v>
       </c>
-      <c r="H59" t="s">
-        <v>5</v>
-      </c>
-      <c r="I59" t="s">
-        <v>77</v>
-      </c>
       <c r="J59" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K59" t="s">
         <v>5</v>
       </c>
       <c r="L59" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M59" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B60" t="s">
         <v>10</v>
@@ -4752,39 +4803,39 @@
         <v>41</v>
       </c>
       <c r="D60" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E60" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F60" t="s">
         <v>5</v>
       </c>
       <c r="G60" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H60" t="s">
         <v>5</v>
       </c>
       <c r="I60" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J60" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K60" t="s">
         <v>5</v>
       </c>
       <c r="L60" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M60" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B61" t="s">
         <v>10</v>
@@ -4793,22 +4844,22 @@
         <v>41</v>
       </c>
       <c r="D61" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E61" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F61" t="s">
         <v>5</v>
       </c>
       <c r="G61" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H61" t="s">
         <v>5</v>
       </c>
       <c r="I61" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J61" t="s">
         <v>61</v>
@@ -4820,7 +4871,7 @@
         <v>61</v>
       </c>
       <c r="M61" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -4834,22 +4885,22 @@
         <v>41</v>
       </c>
       <c r="D62" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E62" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F62" t="s">
         <v>5</v>
       </c>
       <c r="G62" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s">
         <v>5</v>
       </c>
       <c r="I62" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J62" t="s">
         <v>61</v>
@@ -4861,7 +4912,7 @@
         <v>61</v>
       </c>
       <c r="M62" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -4875,16 +4926,16 @@
         <v>41</v>
       </c>
       <c r="D63" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E63" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F63" t="s">
         <v>5</v>
       </c>
       <c r="G63" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H63" t="s">
         <v>5</v>
@@ -4893,21 +4944,21 @@
         <v>61</v>
       </c>
       <c r="J63" t="s">
+        <v>88</v>
+      </c>
+      <c r="K63" t="s">
+        <v>5</v>
+      </c>
+      <c r="L63" t="s">
+        <v>88</v>
+      </c>
+      <c r="M63" t="s">
         <v>85</v>
-      </c>
-      <c r="K63" t="s">
-        <v>5</v>
-      </c>
-      <c r="L63" t="s">
-        <v>85</v>
-      </c>
-      <c r="M63" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B64" t="s">
         <v>10</v>
@@ -4916,16 +4967,16 @@
         <v>41</v>
       </c>
       <c r="D64" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E64" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F64" t="s">
         <v>5</v>
       </c>
       <c r="G64" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s">
         <v>5</v>
@@ -4934,21 +4985,21 @@
         <v>61</v>
       </c>
       <c r="J64" t="s">
+        <v>88</v>
+      </c>
+      <c r="K64" t="s">
+        <v>5</v>
+      </c>
+      <c r="L64" t="s">
+        <v>88</v>
+      </c>
+      <c r="M64" t="s">
         <v>85</v>
-      </c>
-      <c r="K64" t="s">
-        <v>5</v>
-      </c>
-      <c r="L64" t="s">
-        <v>85</v>
-      </c>
-      <c r="M64" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B65" t="s">
         <v>15</v>
@@ -4957,30 +5008,30 @@
         <v>41</v>
       </c>
       <c r="D65" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E65" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G65" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I65" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J65" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L65" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M65" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B66" t="s">
         <v>15</v>
@@ -4989,30 +5040,30 @@
         <v>41</v>
       </c>
       <c r="D66" t="s">
+        <v>172</v>
+      </c>
+      <c r="E66" t="s">
+        <v>173</v>
+      </c>
+      <c r="G66" t="s">
+        <v>83</v>
+      </c>
+      <c r="I66" t="s">
         <v>169</v>
       </c>
-      <c r="E66" t="s">
-        <v>170</v>
-      </c>
-      <c r="G66" t="s">
-        <v>80</v>
-      </c>
-      <c r="I66" t="s">
-        <v>166</v>
-      </c>
       <c r="J66" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L66" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M66" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B67" t="s">
         <v>15</v>
@@ -5021,30 +5072,30 @@
         <v>41</v>
       </c>
       <c r="D67" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E67" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G67" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I67" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J67" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L67" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M67" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B68" t="s">
         <v>15</v>
@@ -5053,30 +5104,30 @@
         <v>41</v>
       </c>
       <c r="D68" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E68" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G68" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I68" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J68" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L68" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M68" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B69" t="s">
         <v>18</v>
@@ -5085,25 +5136,25 @@
         <v>41</v>
       </c>
       <c r="D69" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E69" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G69" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I69" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J69" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L69" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M69" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -5229,7 +5280,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B1" t="s">
         <v>64</v>
@@ -5238,34 +5289,34 @@
         <v>63</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -5279,10 +5330,10 @@
         <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F2" t="s">
         <v>5</v>
@@ -5306,7 +5357,7 @@
         <v>56</v>
       </c>
       <c r="M2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -5320,10 +5371,10 @@
         <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F3" t="s">
         <v>5</v>
@@ -5347,12 +5398,12 @@
         <v>56</v>
       </c>
       <c r="M3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
@@ -5361,27 +5412,27 @@
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G4" t="s">
         <v>52</v>
       </c>
       <c r="I4" t="s">
+        <v>185</v>
+      </c>
+      <c r="J4" t="s">
+        <v>185</v>
+      </c>
+      <c r="M4" t="s">
         <v>182</v>
-      </c>
-      <c r="J4" t="s">
-        <v>182</v>
-      </c>
-      <c r="M4" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -5390,10 +5441,10 @@
         <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F5" t="s">
         <v>5</v>
@@ -5405,10 +5456,10 @@
         <v>5</v>
       </c>
       <c r="I5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K5" t="s">
         <v>5</v>
@@ -5417,12 +5468,12 @@
         <v>5</v>
       </c>
       <c r="M5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
@@ -5431,10 +5482,10 @@
         <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
@@ -5446,10 +5497,10 @@
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K6" t="s">
         <v>5</v>
@@ -5458,12 +5509,12 @@
         <v>5</v>
       </c>
       <c r="M6" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
@@ -5472,10 +5523,10 @@
         <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
@@ -5487,24 +5538,24 @@
         <v>5</v>
       </c>
       <c r="I7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K7" t="s">
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M7" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
@@ -5513,10 +5564,10 @@
         <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E8" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F8" t="s">
         <v>5</v>
@@ -5528,10 +5579,10 @@
         <v>5</v>
       </c>
       <c r="I8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="J8" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K8" t="s">
         <v>5</v>
@@ -5540,12 +5591,12 @@
         <v>5</v>
       </c>
       <c r="M8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
@@ -5554,10 +5605,10 @@
         <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E9" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
@@ -5569,10 +5620,10 @@
         <v>5</v>
       </c>
       <c r="I9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="J9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K9" t="s">
         <v>5</v>
@@ -5581,12 +5632,12 @@
         <v>5</v>
       </c>
       <c r="M9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
@@ -5595,27 +5646,27 @@
         <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G10" t="s">
         <v>52</v>
       </c>
       <c r="I10" t="s">
+        <v>185</v>
+      </c>
+      <c r="J10" t="s">
+        <v>185</v>
+      </c>
+      <c r="M10" t="s">
         <v>182</v>
-      </c>
-      <c r="J10" t="s">
-        <v>182</v>
-      </c>
-      <c r="M10" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
@@ -5624,10 +5675,10 @@
         <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -5639,7 +5690,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="J11" t="s">
         <v>47</v>
@@ -5651,12 +5702,12 @@
         <v>5</v>
       </c>
       <c r="M11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
@@ -5665,10 +5716,10 @@
         <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -5680,7 +5731,7 @@
         <v>5</v>
       </c>
       <c r="I12" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="J12" t="s">
         <v>47</v>
@@ -5692,12 +5743,12 @@
         <v>5</v>
       </c>
       <c r="M12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
@@ -5706,27 +5757,27 @@
         <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G13" t="s">
         <v>52</v>
       </c>
       <c r="I13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="M13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
@@ -5735,22 +5786,22 @@
         <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E14" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G14" t="s">
         <v>52</v>
       </c>
       <c r="I14" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J14" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -5764,10 +5815,10 @@
         <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F15" t="s">
         <v>5</v>
@@ -5779,7 +5830,7 @@
         <v>5</v>
       </c>
       <c r="I15" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="J15" t="s">
         <v>47</v>
@@ -5791,7 +5842,7 @@
         <v>5</v>
       </c>
       <c r="M15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -5805,10 +5856,10 @@
         <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E16" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F16" t="s">
         <v>5</v>
@@ -5820,10 +5871,10 @@
         <v>5</v>
       </c>
       <c r="I16" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="J16" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -5832,7 +5883,7 @@
         <v>5</v>
       </c>
       <c r="M16" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -5846,10 +5897,10 @@
         <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E17" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F17" t="s">
         <v>5</v>
@@ -5864,7 +5915,7 @@
         <v>47</v>
       </c>
       <c r="J17" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
@@ -5873,12 +5924,12 @@
         <v>5</v>
       </c>
       <c r="M17" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
@@ -5887,10 +5938,10 @@
         <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E18" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F18" t="s">
         <v>5</v>
@@ -5905,7 +5956,7 @@
         <v>47</v>
       </c>
       <c r="J18" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
@@ -5914,12 +5965,12 @@
         <v>5</v>
       </c>
       <c r="M18" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
@@ -5928,10 +5979,10 @@
         <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E19" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F19" t="s">
         <v>5</v>
@@ -5943,10 +5994,10 @@
         <v>5</v>
       </c>
       <c r="I19" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="J19" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
@@ -5955,12 +6006,12 @@
         <v>5</v>
       </c>
       <c r="M19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -5969,10 +6020,10 @@
         <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E20" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F20" t="s">
         <v>5</v>
@@ -5984,10 +6035,10 @@
         <v>5</v>
       </c>
       <c r="I20" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="J20" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
@@ -5996,12 +6047,12 @@
         <v>5</v>
       </c>
       <c r="M20" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -6010,10 +6061,10 @@
         <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E21" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F21" t="s">
         <v>5</v>
@@ -6025,10 +6076,10 @@
         <v>5</v>
       </c>
       <c r="I21" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J21" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
@@ -6037,12 +6088,12 @@
         <v>5</v>
       </c>
       <c r="M21" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
@@ -6051,10 +6102,10 @@
         <v>48</v>
       </c>
       <c r="D22" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E22" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F22" t="s">
         <v>5</v>
@@ -6066,10 +6117,10 @@
         <v>5</v>
       </c>
       <c r="I22" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J22" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K22" t="s">
         <v>5</v>
@@ -6078,12 +6129,12 @@
         <v>5</v>
       </c>
       <c r="M22" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
@@ -6092,30 +6143,30 @@
         <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E23" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I23" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J23" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L23" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M23" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
@@ -6124,30 +6175,30 @@
         <v>48</v>
       </c>
       <c r="D24" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E24" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M24" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B28" t="s">
         <v>3</v>
@@ -6156,10 +6207,10 @@
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E28" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
@@ -6171,10 +6222,10 @@
         <v>5</v>
       </c>
       <c r="I28" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J28" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
@@ -6183,12 +6234,12 @@
         <v>5</v>
       </c>
       <c r="M28" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B29" t="s">
         <v>3</v>
@@ -6197,10 +6248,10 @@
         <v>48</v>
       </c>
       <c r="D29" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E29" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F29" t="s">
         <v>5</v>
@@ -6212,10 +6263,10 @@
         <v>5</v>
       </c>
       <c r="I29" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J29" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K29" t="s">
         <v>5</v>
@@ -6224,12 +6275,12 @@
         <v>5</v>
       </c>
       <c r="M29" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B30" t="s">
         <v>3</v>
@@ -6238,10 +6289,10 @@
         <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E30" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F30" t="s">
         <v>5</v>
@@ -6253,10 +6304,10 @@
         <v>5</v>
       </c>
       <c r="I30" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J30" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
@@ -6265,12 +6316,12 @@
         <v>5</v>
       </c>
       <c r="M30" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B31" t="s">
         <v>3</v>
@@ -6282,22 +6333,22 @@
         <v>5</v>
       </c>
       <c r="E31" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F31" t="s">
         <v>5</v>
       </c>
       <c r="G31" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s">
         <v>5</v>
       </c>
       <c r="I31" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J31" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
@@ -6308,7 +6359,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B32" t="s">
         <v>3</v>
@@ -6320,22 +6371,22 @@
         <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F32" t="s">
         <v>5</v>
       </c>
       <c r="G32" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s">
         <v>5</v>
       </c>
       <c r="I32" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J32" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
@@ -6346,7 +6397,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B33" t="s">
         <v>3</v>
@@ -6355,10 +6406,10 @@
         <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E33" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F33" t="s">
         <v>5</v>
@@ -6370,10 +6421,10 @@
         <v>5</v>
       </c>
       <c r="I33" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J33" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
@@ -6382,12 +6433,12 @@
         <v>5</v>
       </c>
       <c r="M33" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B34" t="s">
         <v>3</v>
@@ -6396,10 +6447,10 @@
         <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E34" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F34" t="s">
         <v>5</v>
@@ -6411,24 +6462,24 @@
         <v>5</v>
       </c>
       <c r="I34" t="s">
+        <v>185</v>
+      </c>
+      <c r="J34" t="s">
+        <v>185</v>
+      </c>
+      <c r="K34" t="s">
+        <v>5</v>
+      </c>
+      <c r="L34" t="s">
+        <v>185</v>
+      </c>
+      <c r="M34" t="s">
         <v>182</v>
-      </c>
-      <c r="J34" t="s">
-        <v>182</v>
-      </c>
-      <c r="K34" t="s">
-        <v>5</v>
-      </c>
-      <c r="L34" t="s">
-        <v>182</v>
-      </c>
-      <c r="M34" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B35" t="s">
         <v>3</v>
@@ -6437,10 +6488,10 @@
         <v>48</v>
       </c>
       <c r="D35" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E35" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F35" t="s">
         <v>5</v>
@@ -6452,24 +6503,24 @@
         <v>5</v>
       </c>
       <c r="I35" t="s">
+        <v>185</v>
+      </c>
+      <c r="J35" t="s">
+        <v>185</v>
+      </c>
+      <c r="K35" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" t="s">
+        <v>185</v>
+      </c>
+      <c r="M35" t="s">
         <v>182</v>
-      </c>
-      <c r="J35" t="s">
-        <v>182</v>
-      </c>
-      <c r="K35" t="s">
-        <v>5</v>
-      </c>
-      <c r="L35" t="s">
-        <v>182</v>
-      </c>
-      <c r="M35" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B36" t="s">
         <v>3</v>
@@ -6478,10 +6529,10 @@
         <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E36" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F36" t="s">
         <v>5</v>
@@ -6493,24 +6544,24 @@
         <v>5</v>
       </c>
       <c r="I36" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J36" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K36" t="s">
         <v>5</v>
       </c>
       <c r="L36" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="M36" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
@@ -6519,10 +6570,10 @@
         <v>48</v>
       </c>
       <c r="D37" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E37" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F37" t="s">
         <v>5</v>
@@ -6534,24 +6585,24 @@
         <v>5</v>
       </c>
       <c r="I37" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J37" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K37" t="s">
         <v>5</v>
       </c>
       <c r="L37" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="M37" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B38" t="s">
         <v>8</v>
@@ -6560,10 +6611,10 @@
         <v>48</v>
       </c>
       <c r="D38" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E38" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F38" t="s">
         <v>5</v>
@@ -6575,10 +6626,10 @@
         <v>5</v>
       </c>
       <c r="I38" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J38" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K38" t="s">
         <v>5</v>
@@ -6587,12 +6638,12 @@
         <v>5</v>
       </c>
       <c r="M38" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
@@ -6601,10 +6652,10 @@
         <v>48</v>
       </c>
       <c r="D39" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E39" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F39" t="s">
         <v>5</v>
@@ -6616,10 +6667,10 @@
         <v>5</v>
       </c>
       <c r="I39" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J39" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K39" t="s">
         <v>5</v>
@@ -6628,12 +6679,12 @@
         <v>5</v>
       </c>
       <c r="M39" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s">
         <v>8</v>
@@ -6642,10 +6693,10 @@
         <v>48</v>
       </c>
       <c r="D40" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E40" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F40" t="s">
         <v>5</v>
@@ -6657,10 +6708,10 @@
         <v>5</v>
       </c>
       <c r="I40" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J40" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K40" t="s">
         <v>5</v>
@@ -6669,12 +6720,12 @@
         <v>5</v>
       </c>
       <c r="M40" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B41" t="s">
         <v>8</v>
@@ -6683,10 +6734,10 @@
         <v>48</v>
       </c>
       <c r="D41" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E41" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F41" t="s">
         <v>5</v>
@@ -6698,10 +6749,10 @@
         <v>5</v>
       </c>
       <c r="I41" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J41" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K41" t="s">
         <v>5</v>
@@ -6710,12 +6761,12 @@
         <v>5</v>
       </c>
       <c r="M41" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -6724,10 +6775,10 @@
         <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E42" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F42" t="s">
         <v>5</v>
@@ -6739,10 +6790,10 @@
         <v>5</v>
       </c>
       <c r="I42" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J42" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K42" t="s">
         <v>5</v>
@@ -6751,12 +6802,12 @@
         <v>5</v>
       </c>
       <c r="M42" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B43" t="s">
         <v>8</v>
@@ -6765,10 +6816,10 @@
         <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E43" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F43" t="s">
         <v>5</v>
@@ -6780,10 +6831,10 @@
         <v>5</v>
       </c>
       <c r="I43" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J43" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K43" t="s">
         <v>5</v>
@@ -6792,12 +6843,12 @@
         <v>5</v>
       </c>
       <c r="M43" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
@@ -6806,10 +6857,10 @@
         <v>48</v>
       </c>
       <c r="D44" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E44" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F44" t="s">
         <v>5</v>
@@ -6821,10 +6872,10 @@
         <v>5</v>
       </c>
       <c r="I44" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J44" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K44" t="s">
         <v>5</v>
@@ -6833,12 +6884,12 @@
         <v>5</v>
       </c>
       <c r="M44" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
@@ -6847,10 +6898,10 @@
         <v>48</v>
       </c>
       <c r="D45" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E45" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F45" t="s">
         <v>5</v>
@@ -6862,10 +6913,10 @@
         <v>5</v>
       </c>
       <c r="I45" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J45" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K45" t="s">
         <v>5</v>
@@ -6874,12 +6925,12 @@
         <v>5</v>
       </c>
       <c r="M45" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B46" t="s">
         <v>11</v>
@@ -6888,7 +6939,7 @@
         <v>48</v>
       </c>
       <c r="D46" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E46" t="s">
         <v>5</v>
@@ -6903,10 +6954,10 @@
         <v>5</v>
       </c>
       <c r="I46" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J46" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K46" t="s">
         <v>5</v>
@@ -6915,12 +6966,12 @@
         <v>5</v>
       </c>
       <c r="M46" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
@@ -6929,10 +6980,10 @@
         <v>48</v>
       </c>
       <c r="D47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E47" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F47" t="s">
         <v>5</v>
@@ -6944,10 +6995,10 @@
         <v>5</v>
       </c>
       <c r="I47" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J47" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K47" t="s">
         <v>5</v>
@@ -6956,12 +7007,12 @@
         <v>5</v>
       </c>
       <c r="M47" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B48" t="s">
         <v>11</v>
@@ -6970,7 +7021,7 @@
         <v>48</v>
       </c>
       <c r="D48" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E48" t="s">
         <v>5</v>
@@ -6985,10 +7036,10 @@
         <v>5</v>
       </c>
       <c r="I48" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J48" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K48" t="s">
         <v>5</v>
@@ -6997,12 +7048,12 @@
         <v>5</v>
       </c>
       <c r="M48" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
@@ -7011,10 +7062,10 @@
         <v>48</v>
       </c>
       <c r="D49" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E49" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F49" t="s">
         <v>5</v>
@@ -7026,10 +7077,10 @@
         <v>5</v>
       </c>
       <c r="I49" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J49" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
@@ -7038,12 +7089,12 @@
         <v>5</v>
       </c>
       <c r="M49" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
@@ -7055,22 +7106,22 @@
         <v>5</v>
       </c>
       <c r="E59" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F59" t="s">
         <v>5</v>
       </c>
       <c r="G59" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H59" t="s">
         <v>5</v>
       </c>
       <c r="I59" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J59" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K59" t="s">
         <v>5</v>
@@ -7081,7 +7132,7 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B60" t="s">
         <v>12</v>
@@ -7090,10 +7141,10 @@
         <v>48</v>
       </c>
       <c r="D60" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E60" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F60" t="s">
         <v>5</v>
@@ -7105,10 +7156,10 @@
         <v>5</v>
       </c>
       <c r="I60" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J60" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K60" t="s">
         <v>5</v>
@@ -7117,12 +7168,12 @@
         <v>5</v>
       </c>
       <c r="M60" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
@@ -7131,10 +7182,10 @@
         <v>48</v>
       </c>
       <c r="D61" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E61" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F61" t="s">
         <v>5</v>
@@ -7146,10 +7197,10 @@
         <v>5</v>
       </c>
       <c r="I61" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J61" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K61" t="s">
         <v>5</v>
@@ -7158,12 +7209,12 @@
         <v>5</v>
       </c>
       <c r="M61" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
@@ -7172,10 +7223,10 @@
         <v>48</v>
       </c>
       <c r="D62" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E62" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F62" t="s">
         <v>5</v>
@@ -7187,10 +7238,10 @@
         <v>5</v>
       </c>
       <c r="I62" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J62" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K62" t="s">
         <v>5</v>
@@ -7199,7 +7250,7 @@
         <v>5</v>
       </c>
       <c r="M62" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -7304,7 +7355,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B1" t="s">
         <v>64</v>
@@ -7313,39 +7364,39 @@
         <v>63</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -7354,25 +7405,25 @@
         <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F2" t="s">
         <v>5</v>
       </c>
       <c r="G2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" t="s">
         <v>268</v>
       </c>
-      <c r="H2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" t="s">
-        <v>265</v>
-      </c>
       <c r="J2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K2" t="s">
         <v>5</v>
@@ -7381,12 +7432,12 @@
         <v>5</v>
       </c>
       <c r="M2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -7395,25 +7446,25 @@
         <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
         <v>271</v>
       </c>
-      <c r="F3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
         <v>268</v>
       </c>
-      <c r="H3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" t="s">
-        <v>265</v>
-      </c>
       <c r="J3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K3" t="s">
         <v>5</v>
@@ -7422,12 +7473,12 @@
         <v>5</v>
       </c>
       <c r="M3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -7436,39 +7487,39 @@
         <v>53</v>
       </c>
       <c r="D4" t="s">
+        <v>275</v>
+      </c>
+      <c r="E4" t="s">
+        <v>276</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>271</v>
+      </c>
+      <c r="H4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" t="s">
+        <v>268</v>
+      </c>
+      <c r="J4" t="s">
+        <v>268</v>
+      </c>
+      <c r="K4" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" t="s">
         <v>272</v>
-      </c>
-      <c r="E4" t="s">
-        <v>273</v>
-      </c>
-      <c r="F4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
-        <v>268</v>
-      </c>
-      <c r="H4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" t="s">
-        <v>265</v>
-      </c>
-      <c r="J4" t="s">
-        <v>265</v>
-      </c>
-      <c r="K4" t="s">
-        <v>5</v>
-      </c>
-      <c r="L4" t="s">
-        <v>5</v>
-      </c>
-      <c r="M4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -7477,25 +7528,25 @@
         <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F5" t="s">
         <v>5</v>
       </c>
       <c r="G5" t="s">
+        <v>271</v>
+      </c>
+      <c r="H5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" t="s">
         <v>268</v>
       </c>
-      <c r="H5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" t="s">
-        <v>265</v>
-      </c>
       <c r="J5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K5" t="s">
         <v>5</v>
@@ -7504,12 +7555,12 @@
         <v>5</v>
       </c>
       <c r="M5" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -7518,25 +7569,25 @@
         <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H6" t="s">
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="J6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="K6" t="s">
         <v>5</v>
@@ -7545,12 +7596,12 @@
         <v>5</v>
       </c>
       <c r="M6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -7559,25 +7610,25 @@
         <v>53</v>
       </c>
       <c r="D7" t="s">
+        <v>281</v>
+      </c>
+      <c r="E7" t="s">
+        <v>282</v>
+      </c>
+      <c r="F7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s">
+        <v>271</v>
+      </c>
+      <c r="H7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7" t="s">
         <v>278</v>
       </c>
-      <c r="E7" t="s">
-        <v>279</v>
-      </c>
-      <c r="F7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" t="s">
-        <v>268</v>
-      </c>
-      <c r="H7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7" t="s">
-        <v>275</v>
-      </c>
       <c r="J7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="K7" t="s">
         <v>5</v>
@@ -7586,12 +7637,12 @@
         <v>5</v>
       </c>
       <c r="M7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -7600,25 +7651,25 @@
         <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F8" t="s">
         <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H8" t="s">
         <v>5</v>
       </c>
       <c r="I8" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J8" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K8" t="s">
         <v>5</v>
@@ -7627,7 +7678,7 @@
         <v>5</v>
       </c>
       <c r="M8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -7644,13 +7695,13 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
       <c r="G9" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H9" t="s">
         <v>5</v>
@@ -7670,7 +7721,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -7682,22 +7733,22 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H10" t="s">
         <v>5</v>
       </c>
       <c r="I10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K10" t="s">
         <v>5</v>
@@ -7708,7 +7759,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
@@ -7720,22 +7771,22 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
       </c>
       <c r="I11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K11" t="s">
         <v>5</v>
@@ -7746,7 +7797,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -7758,22 +7809,22 @@
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
       </c>
       <c r="G12" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H12" t="s">
         <v>5</v>
       </c>
       <c r="I12" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J12" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K12" t="s">
         <v>5</v>
@@ -7784,7 +7835,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -7796,22 +7847,22 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
       </c>
       <c r="G13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H13" t="s">
         <v>5</v>
       </c>
       <c r="I13" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J13" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K13" t="s">
         <v>5</v>
@@ -7822,7 +7873,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -7834,22 +7885,22 @@
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F14" t="s">
         <v>5</v>
       </c>
       <c r="G14" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H14" t="s">
         <v>5</v>
       </c>
       <c r="I14" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J14" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
@@ -7860,7 +7911,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
@@ -7872,22 +7923,22 @@
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F15" t="s">
         <v>5</v>
       </c>
       <c r="G15" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H15" t="s">
         <v>5</v>
       </c>
       <c r="I15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K15" t="s">
         <v>5</v>
@@ -7898,7 +7949,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
@@ -7910,22 +7961,22 @@
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F16" t="s">
         <v>5</v>
       </c>
       <c r="G16" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H16" t="s">
         <v>5</v>
       </c>
       <c r="I16" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J16" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -7936,7 +7987,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
@@ -7948,22 +7999,22 @@
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F17" t="s">
         <v>5</v>
       </c>
       <c r="G17" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H17" t="s">
         <v>5</v>
       </c>
       <c r="I17" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J17" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
@@ -7974,7 +8025,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
@@ -7986,22 +8037,22 @@
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F18" t="s">
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H18" t="s">
         <v>5</v>
       </c>
       <c r="I18" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J18" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
@@ -8012,7 +8063,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
@@ -8021,25 +8072,25 @@
         <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E19" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F19" t="s">
         <v>5</v>
       </c>
       <c r="G19" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H19" t="s">
         <v>5</v>
       </c>
       <c r="I19" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J19" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
@@ -8048,12 +8099,12 @@
         <v>5</v>
       </c>
       <c r="M19" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
@@ -8062,25 +8113,25 @@
         <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E20" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F20" t="s">
         <v>5</v>
       </c>
       <c r="G20" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H20" t="s">
         <v>5</v>
       </c>
       <c r="I20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
@@ -8089,12 +8140,12 @@
         <v>5</v>
       </c>
       <c r="M20" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
@@ -8106,22 +8157,22 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F21" t="s">
         <v>5</v>
       </c>
       <c r="G21" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H21" t="s">
         <v>5</v>
       </c>
       <c r="I21" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J21" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
@@ -8132,7 +8183,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B22" t="s">
         <v>11</v>
@@ -8141,25 +8192,25 @@
         <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E22" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F22" t="s">
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H22" t="s">
         <v>5</v>
       </c>
       <c r="I22" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J22" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K22" t="s">
         <v>5</v>
@@ -8168,12 +8219,12 @@
         <v>5</v>
       </c>
       <c r="M22" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
@@ -8182,25 +8233,25 @@
         <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E23" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F23" t="s">
         <v>5</v>
       </c>
       <c r="G23" t="s">
+        <v>271</v>
+      </c>
+      <c r="H23" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" t="s">
         <v>268</v>
       </c>
-      <c r="H23" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" t="s">
-        <v>265</v>
-      </c>
       <c r="J23" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K23" t="s">
         <v>5</v>
@@ -8209,12 +8260,12 @@
         <v>5</v>
       </c>
       <c r="M23" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
@@ -8223,25 +8274,25 @@
         <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E24" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F24" t="s">
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H24" t="s">
         <v>5</v>
       </c>
       <c r="I24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
@@ -8250,12 +8301,12 @@
         <v>5</v>
       </c>
       <c r="M24" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
@@ -8264,25 +8315,25 @@
         <v>53</v>
       </c>
       <c r="D25" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E25" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F25" t="s">
         <v>5</v>
       </c>
       <c r="G25" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H25" t="s">
         <v>5</v>
       </c>
       <c r="I25" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J25" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
@@ -8291,12 +8342,12 @@
         <v>5</v>
       </c>
       <c r="M25" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
@@ -8308,22 +8359,22 @@
         <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F26" t="s">
         <v>5</v>
       </c>
       <c r="G26" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H26" t="s">
         <v>5</v>
       </c>
       <c r="I26" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J26" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
@@ -8346,22 +8397,22 @@
         <v>5</v>
       </c>
       <c r="E27" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F27" t="s">
         <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H27" t="s">
         <v>5</v>
       </c>
       <c r="I27" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="J27" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
@@ -8372,7 +8423,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
@@ -8384,22 +8435,22 @@
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
       </c>
       <c r="G28" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H28" t="s">
         <v>5</v>
       </c>
       <c r="I28" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J28" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
@@ -8410,7 +8461,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B29" t="s">
         <v>11</v>
@@ -8422,22 +8473,22 @@
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F29" t="s">
         <v>5</v>
       </c>
       <c r="G29" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H29" t="s">
         <v>5</v>
       </c>
       <c r="I29" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J29" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K29" t="s">
         <v>5</v>
@@ -8448,7 +8499,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
@@ -8460,22 +8511,22 @@
         <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F30" t="s">
         <v>5</v>
       </c>
       <c r="G30" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H30" t="s">
         <v>5</v>
       </c>
       <c r="I30" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J30" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
@@ -8486,7 +8537,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s">
         <v>11</v>
@@ -8498,22 +8549,22 @@
         <v>5</v>
       </c>
       <c r="E31" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F31" t="s">
         <v>5</v>
       </c>
       <c r="G31" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H31" t="s">
         <v>5</v>
       </c>
       <c r="I31" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J31" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
@@ -8524,7 +8575,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
@@ -8536,22 +8587,22 @@
         <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F32" t="s">
         <v>5</v>
       </c>
       <c r="G32" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H32" t="s">
         <v>5</v>
       </c>
       <c r="I32" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J32" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
@@ -8562,7 +8613,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B33" t="s">
         <v>11</v>
@@ -8574,22 +8625,22 @@
         <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F33" t="s">
         <v>5</v>
       </c>
       <c r="G33" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H33" t="s">
         <v>5</v>
       </c>
       <c r="I33" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J33" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
@@ -8600,7 +8651,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
@@ -8609,25 +8660,25 @@
         <v>53</v>
       </c>
       <c r="D34" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E34" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F34" t="s">
         <v>5</v>
       </c>
       <c r="G34" t="s">
+        <v>271</v>
+      </c>
+      <c r="H34" t="s">
+        <v>5</v>
+      </c>
+      <c r="I34" t="s">
         <v>268</v>
       </c>
-      <c r="H34" t="s">
-        <v>5</v>
-      </c>
-      <c r="I34" t="s">
-        <v>265</v>
-      </c>
       <c r="J34" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
@@ -8636,12 +8687,12 @@
         <v>5</v>
       </c>
       <c r="M34" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B35" t="s">
         <v>19</v>
@@ -8650,30 +8701,30 @@
         <v>53</v>
       </c>
       <c r="D35" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E35" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G35" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I35" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J35" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L35" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M35" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
@@ -8682,27 +8733,27 @@
         <v>53</v>
       </c>
       <c r="D36" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E36" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G36" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I36" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J36" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M36" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
@@ -8711,27 +8762,27 @@
         <v>53</v>
       </c>
       <c r="D37" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E37" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G37" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I37" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J37" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M37" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
@@ -8740,25 +8791,25 @@
         <v>53</v>
       </c>
       <c r="D38" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E38" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F38" t="s">
         <v>5</v>
       </c>
       <c r="G38" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H38" t="s">
         <v>5</v>
       </c>
       <c r="I38" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="J38" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="K38" t="s">
         <v>5</v>
@@ -8767,7 +8818,7 @@
         <v>5</v>
       </c>
       <c r="M38" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -8784,13 +8835,13 @@
         <v>5</v>
       </c>
       <c r="E39" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F39" t="s">
         <v>5</v>
       </c>
       <c r="G39" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H39" t="s">
         <v>5</v>
@@ -8810,7 +8861,7 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
@@ -8819,27 +8870,27 @@
         <v>53</v>
       </c>
       <c r="D40" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E40" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G40" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I40" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J40" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M40" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
@@ -8848,27 +8899,27 @@
         <v>53</v>
       </c>
       <c r="D41" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E41" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G41" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I41" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J41" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M41" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
@@ -8877,27 +8928,27 @@
         <v>53</v>
       </c>
       <c r="D42" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E42" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G42" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I42" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J42" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M42" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
@@ -8906,27 +8957,27 @@
         <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E43" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G43" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I43" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J43" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M43" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
@@ -8935,27 +8986,27 @@
         <v>53</v>
       </c>
       <c r="D44" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E44" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G44" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I44" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J44" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M44" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
@@ -8964,27 +9015,27 @@
         <v>53</v>
       </c>
       <c r="D45" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E45" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G45" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I45" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J45" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M45" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
@@ -8993,27 +9044,27 @@
         <v>53</v>
       </c>
       <c r="D46" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E46" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G46" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I46" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J46" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M46" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
@@ -9022,27 +9073,27 @@
         <v>53</v>
       </c>
       <c r="D47" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E47" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G47" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I47" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J47" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M47" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
@@ -9051,27 +9102,27 @@
         <v>53</v>
       </c>
       <c r="D48" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E48" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G48" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I48" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J48" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M48" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
@@ -9080,27 +9131,27 @@
         <v>53</v>
       </c>
       <c r="D49" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E49" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G49" t="s">
         <v>52</v>
       </c>
       <c r="I49" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J49" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M49" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B50" t="s">
         <v>8</v>
@@ -9109,22 +9160,22 @@
         <v>53</v>
       </c>
       <c r="D50" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E50" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G50" t="s">
         <v>52</v>
       </c>
       <c r="I50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M50" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -9212,7 +9263,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B1" t="s">
         <v>64</v>
@@ -9221,39 +9272,39 @@
         <v>63</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -9265,22 +9316,22 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F2" t="s">
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H2" t="s">
         <v>5</v>
       </c>
       <c r="I2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="K2" t="s">
         <v>5</v>
@@ -9291,7 +9342,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -9303,22 +9354,22 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F3" t="s">
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H3" t="s">
         <v>5</v>
       </c>
       <c r="I3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="K3" t="s">
         <v>5</v>
@@ -9329,7 +9380,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
@@ -9341,22 +9392,22 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
       </c>
       <c r="G4" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H4" t="s">
         <v>5</v>
       </c>
       <c r="I4" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="K4" t="s">
         <v>5</v>
@@ -9367,7 +9418,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -9379,22 +9430,22 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F5" t="s">
         <v>5</v>
       </c>
       <c r="G5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H5" t="s">
         <v>5</v>
       </c>
       <c r="I5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="K5" t="s">
         <v>5</v>
@@ -9405,7 +9456,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
@@ -9417,22 +9468,22 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H6" t="s">
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J6" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K6" t="s">
         <v>5</v>
@@ -9443,7 +9494,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -9455,22 +9506,22 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H7" t="s">
         <v>5</v>
       </c>
       <c r="I7" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J7" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="K7" t="s">
         <v>5</v>
@@ -9481,7 +9532,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -9493,22 +9544,22 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F8" t="s">
         <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H8" t="s">
         <v>5</v>
       </c>
       <c r="I8" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J8" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="K8" t="s">
         <v>5</v>
@@ -9534,7 +9585,7 @@
         <v>5</v>
       </c>
       <c r="G9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s">
         <v>5</v>
@@ -9554,7 +9605,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
@@ -9566,22 +9617,22 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H10" t="s">
         <v>5</v>
       </c>
       <c r="I10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K10" t="s">
         <v>5</v>
@@ -9592,7 +9643,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
@@ -9604,22 +9655,22 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
       </c>
       <c r="I11" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="J11" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K11" t="s">
         <v>5</v>
@@ -9630,7 +9681,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -9642,19 +9693,19 @@
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
       </c>
       <c r="G12" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H12" t="s">
         <v>5</v>
       </c>
       <c r="I12" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J12" t="s">
         <v>51</v>
@@ -9668,7 +9719,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -9680,22 +9731,22 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
       </c>
       <c r="G13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H13" t="s">
         <v>5</v>
       </c>
       <c r="I13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="J13" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K13" t="s">
         <v>5</v>
@@ -9706,7 +9757,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -9718,22 +9769,22 @@
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F14">
         <v>-0.5</v>
       </c>
       <c r="G14" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H14" t="s">
         <v>5</v>
       </c>
       <c r="I14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
@@ -9744,7 +9795,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
@@ -9756,22 +9807,22 @@
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F15" t="s">
         <v>5</v>
       </c>
       <c r="G15" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H15" t="s">
         <v>5</v>
       </c>
       <c r="I15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K15" t="s">
         <v>5</v>
@@ -9782,7 +9833,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
@@ -9794,22 +9845,22 @@
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F16" t="s">
         <v>5</v>
       </c>
       <c r="G16" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H16" t="s">
         <v>5</v>
       </c>
       <c r="I16" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="J16" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -9820,7 +9871,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
@@ -9832,22 +9883,22 @@
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F17">
         <v>-0.5</v>
       </c>
       <c r="G17" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H17" t="s">
         <v>5</v>
       </c>
       <c r="I17" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J17" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
@@ -9858,7 +9909,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
@@ -9870,22 +9921,22 @@
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F18" t="s">
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H18" t="s">
         <v>5</v>
       </c>
       <c r="I18" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J18" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
@@ -9908,13 +9959,13 @@
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F19" t="s">
         <v>5</v>
       </c>
       <c r="G19" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H19" t="s">
         <v>5</v>
@@ -9923,7 +9974,7 @@
         <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
@@ -9934,7 +9985,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
@@ -9946,22 +9997,22 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F20" t="s">
         <v>5</v>
       </c>
       <c r="G20" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H20" t="s">
         <v>5</v>
       </c>
       <c r="I20" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J20" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
@@ -9972,7 +10023,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -9984,22 +10035,22 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F21" t="s">
         <v>5</v>
       </c>
       <c r="G21" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H21" t="s">
         <v>5</v>
       </c>
       <c r="I21" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J21" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
@@ -10022,13 +10073,13 @@
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F22" t="s">
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H22" t="s">
         <v>5</v>
@@ -10037,7 +10088,7 @@
         <v>51</v>
       </c>
       <c r="J22" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K22" t="s">
         <v>5</v>
@@ -10048,7 +10099,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
@@ -10060,22 +10111,22 @@
         <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F23">
         <v>-6</v>
       </c>
       <c r="G23" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H23" t="s">
         <v>5</v>
       </c>
       <c r="I23" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J23" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K23" t="s">
         <v>5</v>
@@ -10086,7 +10137,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
@@ -10098,22 +10149,22 @@
         <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F24" t="s">
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H24" t="s">
         <v>5</v>
       </c>
       <c r="I24" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J24" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
@@ -10124,7 +10175,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B25" t="s">
         <v>3</v>
@@ -10136,22 +10187,22 @@
         <v>5</v>
       </c>
       <c r="E25" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F25" t="s">
         <v>5</v>
       </c>
       <c r="G25" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H25" t="s">
         <v>5</v>
       </c>
       <c r="I25" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J25" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
@@ -10162,7 +10213,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
@@ -10174,22 +10225,22 @@
         <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F26" t="s">
         <v>5</v>
       </c>
       <c r="G26" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H26" t="s">
         <v>5</v>
       </c>
       <c r="I26" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J26" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
@@ -10200,7 +10251,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
@@ -10212,22 +10263,22 @@
         <v>5</v>
       </c>
       <c r="E27" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F27" t="s">
         <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H27" t="s">
         <v>5</v>
       </c>
       <c r="I27" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J27" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
@@ -10238,7 +10289,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B28" t="s">
         <v>6</v>
@@ -10250,22 +10301,22 @@
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
       </c>
       <c r="G28" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H28" t="s">
         <v>5</v>
       </c>
       <c r="I28" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J28" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
@@ -10276,7 +10327,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
@@ -10288,22 +10339,22 @@
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F29" t="s">
         <v>5</v>
       </c>
       <c r="G29" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H29" t="s">
         <v>5</v>
       </c>
       <c r="I29" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J29" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="K29" t="s">
         <v>5</v>
@@ -10314,7 +10365,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B30" t="s">
         <v>6</v>
@@ -10326,22 +10377,22 @@
         <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F30" t="s">
         <v>5</v>
       </c>
       <c r="G30" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H30" t="s">
         <v>5</v>
       </c>
       <c r="I30" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J30" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
@@ -10352,7 +10403,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B31" t="s">
         <v>3</v>
@@ -10364,22 +10415,22 @@
         <v>5</v>
       </c>
       <c r="E31" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F31" t="s">
         <v>5</v>
       </c>
       <c r="G31" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H31" t="s">
         <v>5</v>
       </c>
       <c r="I31" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J31" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
@@ -10390,7 +10441,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
@@ -10402,19 +10453,19 @@
         <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F32" t="s">
         <v>5</v>
       </c>
       <c r="G32" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H32" t="s">
         <v>5</v>
       </c>
       <c r="I32" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J32" t="s">
         <v>51</v>
@@ -10428,7 +10479,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s">
         <v>6</v>
@@ -10440,22 +10491,22 @@
         <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F33" t="s">
         <v>5</v>
       </c>
       <c r="G33" t="s">
+        <v>271</v>
+      </c>
+      <c r="H33" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" t="s">
         <v>268</v>
       </c>
-      <c r="H33" t="s">
-        <v>5</v>
-      </c>
-      <c r="I33" t="s">
-        <v>265</v>
-      </c>
       <c r="J33" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
@@ -10466,7 +10517,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
@@ -10478,22 +10529,22 @@
         <v>5</v>
       </c>
       <c r="E34" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F34">
         <v>-4</v>
       </c>
       <c r="G34" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H34" t="s">
         <v>5</v>
       </c>
       <c r="I34" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J34" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
@@ -10504,7 +10555,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B35" t="s">
         <v>8</v>
@@ -10516,22 +10567,22 @@
         <v>5</v>
       </c>
       <c r="E35" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F35">
         <v>-4</v>
       </c>
       <c r="G35" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H35" t="s">
         <v>5</v>
       </c>
       <c r="I35" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J35" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K35" t="s">
         <v>5</v>
@@ -10542,7 +10593,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
@@ -10554,22 +10605,22 @@
         <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F36">
         <v>-2</v>
       </c>
       <c r="G36" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H36" t="s">
         <v>5</v>
       </c>
       <c r="I36" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J36" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K36" t="s">
         <v>5</v>
@@ -10580,7 +10631,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
@@ -10592,22 +10643,22 @@
         <v>5</v>
       </c>
       <c r="E37" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F37">
         <v>-2</v>
       </c>
       <c r="G37" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H37" t="s">
         <v>5</v>
       </c>
       <c r="I37" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J37" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K37" t="s">
         <v>5</v>
@@ -10618,7 +10669,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B38" t="s">
         <v>8</v>
@@ -10630,22 +10681,22 @@
         <v>5</v>
       </c>
       <c r="E38" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F38">
         <v>-2</v>
       </c>
       <c r="G38" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H38" t="s">
         <v>5</v>
       </c>
       <c r="I38" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J38" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K38" t="s">
         <v>5</v>
@@ -10656,7 +10707,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
@@ -10668,22 +10719,22 @@
         <v>5</v>
       </c>
       <c r="E39" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F39">
         <v>-4</v>
       </c>
       <c r="G39" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H39" t="s">
         <v>5</v>
       </c>
       <c r="I39" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J39" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K39" t="s">
         <v>5</v>
@@ -10694,7 +10745,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B40" t="s">
         <v>8</v>
@@ -10706,22 +10757,22 @@
         <v>5</v>
       </c>
       <c r="E40" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F40">
         <v>-2</v>
       </c>
       <c r="G40" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H40" t="s">
         <v>5</v>
       </c>
       <c r="I40" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J40" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K40" t="s">
         <v>5</v>
@@ -10732,7 +10783,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B41" t="s">
         <v>8</v>
@@ -10744,22 +10795,22 @@
         <v>5</v>
       </c>
       <c r="E41" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F41">
         <v>-2</v>
       </c>
       <c r="G41" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H41" t="s">
         <v>5</v>
       </c>
       <c r="I41" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J41" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K41" t="s">
         <v>5</v>
@@ -10770,7 +10821,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -10782,22 +10833,22 @@
         <v>5</v>
       </c>
       <c r="E42" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F42">
         <v>-4</v>
       </c>
       <c r="G42" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H42" t="s">
         <v>5</v>
       </c>
       <c r="I42" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J42" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K42" t="s">
         <v>5</v>
@@ -10808,7 +10859,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s">
         <v>11</v>
@@ -10820,22 +10871,22 @@
         <v>5</v>
       </c>
       <c r="E43" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F43" t="s">
         <v>5</v>
       </c>
       <c r="G43" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H43" t="s">
         <v>5</v>
       </c>
       <c r="I43" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J43" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="K43" t="s">
         <v>5</v>
@@ -10846,7 +10897,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
@@ -10858,22 +10909,22 @@
         <v>5</v>
       </c>
       <c r="E44" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F44" t="s">
         <v>5</v>
       </c>
       <c r="G44" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H44" t="s">
         <v>5</v>
       </c>
       <c r="I44" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J44" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="K44" t="s">
         <v>5</v>
@@ -10884,7 +10935,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
@@ -10896,22 +10947,22 @@
         <v>5</v>
       </c>
       <c r="E45" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F45" t="s">
         <v>5</v>
       </c>
       <c r="G45" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H45" t="s">
         <v>5</v>
       </c>
       <c r="I45" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="J45" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K45" t="s">
         <v>5</v>
@@ -10922,7 +10973,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s">
         <v>11</v>
@@ -10934,22 +10985,22 @@
         <v>5</v>
       </c>
       <c r="E46" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F46" t="s">
         <v>5</v>
       </c>
       <c r="G46" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H46" t="s">
         <v>5</v>
       </c>
       <c r="I46" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="J46" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="K46" t="s">
         <v>5</v>
@@ -10960,7 +11011,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
@@ -10972,22 +11023,22 @@
         <v>5</v>
       </c>
       <c r="E47" t="s">
+        <v>370</v>
+      </c>
+      <c r="F47" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" t="s">
+        <v>271</v>
+      </c>
+      <c r="H47" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" t="s">
         <v>367</v>
       </c>
-      <c r="F47" t="s">
-        <v>5</v>
-      </c>
-      <c r="G47" t="s">
-        <v>268</v>
-      </c>
-      <c r="H47" t="s">
-        <v>5</v>
-      </c>
-      <c r="I47" t="s">
-        <v>364</v>
-      </c>
       <c r="J47" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K47" t="s">
         <v>5</v>
@@ -10998,7 +11049,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s">
         <v>11</v>
@@ -11010,22 +11061,22 @@
         <v>5</v>
       </c>
       <c r="E48" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F48" t="s">
         <v>5</v>
       </c>
       <c r="G48" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H48" t="s">
         <v>5</v>
       </c>
       <c r="I48" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="J48" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="K48" t="s">
         <v>5</v>
@@ -11036,7 +11087,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
@@ -11048,22 +11099,22 @@
         <v>5</v>
       </c>
       <c r="E49" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F49" t="s">
         <v>5</v>
       </c>
       <c r="G49" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H49" t="s">
         <v>5</v>
       </c>
       <c r="I49" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="J49" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
@@ -11074,7 +11125,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B50" t="s">
         <v>11</v>
@@ -11086,22 +11137,22 @@
         <v>5</v>
       </c>
       <c r="E50" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F50" t="s">
         <v>5</v>
       </c>
       <c r="G50" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H50" t="s">
         <v>5</v>
       </c>
       <c r="I50" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J50" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K50" t="s">
         <v>5</v>
@@ -11112,7 +11163,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B51" t="s">
         <v>11</v>
@@ -11124,22 +11175,22 @@
         <v>5</v>
       </c>
       <c r="E51" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F51" t="s">
         <v>5</v>
       </c>
       <c r="G51" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H51" t="s">
         <v>5</v>
       </c>
       <c r="I51" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J51" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
@@ -11162,13 +11213,13 @@
         <v>5</v>
       </c>
       <c r="E52" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F52" t="s">
         <v>5</v>
       </c>
       <c r="G52" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H52" t="s">
         <v>5</v>

--- a/src/data/FML-Data.xlsx
+++ b/src/data/FML-Data.xlsx
@@ -1959,7 +1959,7 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>398</v>
+        <v>438</v>
       </c>
       <c r="F3" t="s">
         <v>50</v>

--- a/src/data/FML-Data.xlsx
+++ b/src/data/FML-Data.xlsx
@@ -1974,19 +1974,19 @@
         <v>52</v>
       </c>
       <c r="J3">
-        <v>52</v>
+        <v>60.5</v>
       </c>
       <c r="K3">
         <v>50</v>
       </c>
       <c r="L3">
-        <v>152</v>
+        <v>176.9</v>
       </c>
       <c r="M3">
         <v>80</v>
       </c>
       <c r="N3">
-        <v>40</v>
+        <v>46.6</v>
       </c>
       <c r="O3">
         <v>24</v>

--- a/src/data/FML-Data.xlsx
+++ b/src/data/FML-Data.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2844" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2853" uniqueCount="377">
   <si>
     <t>Name</t>
   </si>
@@ -392,348 +392,354 @@
     <t>QA sanity fixes</t>
   </si>
   <si>
+    <t>Ready for QA</t>
+  </si>
+  <si>
+    <t>GO Live</t>
+  </si>
+  <si>
+    <t>FNS-61</t>
+  </si>
+  <si>
+    <t>Homepage Header &amp; Footer</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>FNS-63</t>
+  </si>
+  <si>
+    <t>Homepage Static Banner</t>
+  </si>
+  <si>
+    <t>FNS-64</t>
+  </si>
+  <si>
+    <t>Homepage Schedule Widget</t>
+  </si>
+  <si>
+    <t>FNS-88</t>
+  </si>
+  <si>
+    <t>Buy Tickets URL JSON</t>
+  </si>
+  <si>
+    <t>FNS-87</t>
+  </si>
+  <si>
+    <t>Fixtures &amp; Results</t>
+  </si>
+  <si>
+    <t>FNS-93</t>
+  </si>
+  <si>
+    <t>Matchcentre</t>
+  </si>
+  <si>
+    <t>FNS-92</t>
+  </si>
+  <si>
+    <t>Standing UI development</t>
+  </si>
+  <si>
+    <t>FNS-91</t>
+  </si>
+  <si>
+    <t>Standings API integration</t>
+  </si>
+  <si>
+    <t>FNS-65</t>
+  </si>
+  <si>
+    <t>Homepage Standings widget</t>
+  </si>
+  <si>
+    <t>FNS-90</t>
+  </si>
+  <si>
+    <t>Stats UI</t>
+  </si>
+  <si>
+    <t>FNS-89</t>
+  </si>
+  <si>
+    <t>Stats API integration</t>
+  </si>
+  <si>
+    <t>FNS-62</t>
+  </si>
+  <si>
+    <t>Homepage Showcase Carousel</t>
+  </si>
+  <si>
+    <t>FNS-66</t>
+  </si>
+  <si>
+    <t>Homepage News &amp; Videos</t>
+  </si>
+  <si>
+    <t>FNS-67</t>
+  </si>
+  <si>
+    <t>Homepage Photos</t>
+  </si>
+  <si>
+    <t>FNS-68</t>
+  </si>
+  <si>
+    <t>Homepage Squad</t>
+  </si>
+  <si>
+    <t>FNS-69</t>
+  </si>
+  <si>
+    <t>Homepage Shop Widget</t>
+  </si>
+  <si>
+    <t>FNS-70</t>
+  </si>
+  <si>
+    <t>Homepage Newsletter Widget</t>
+  </si>
+  <si>
+    <t>FNS-94</t>
+  </si>
+  <si>
+    <t>Squad Page</t>
+  </si>
+  <si>
+    <t>FNS-84</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>FNS-96</t>
+  </si>
+  <si>
+    <t>Custom JSON</t>
+  </si>
+  <si>
+    <t>FNS-95</t>
+  </si>
+  <si>
+    <t>Player Profile</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>FNS-56</t>
+  </si>
+  <si>
+    <t>WF Homepage design modifications</t>
+  </si>
+  <si>
+    <t>FNS-57</t>
+  </si>
+  <si>
+    <t>WF Content Pages design modifications</t>
+  </si>
+  <si>
+    <t>FNS-58</t>
+  </si>
+  <si>
+    <t>WF Data Pages design modifications</t>
+  </si>
+  <si>
+    <t>FNS-59</t>
+  </si>
+  <si>
+    <t>WF Static Pages design modifications</t>
+  </si>
+  <si>
+    <t>FNS-187</t>
+  </si>
+  <si>
+    <t>WF QA Testing</t>
+  </si>
+  <si>
+    <t>FNS-10</t>
+  </si>
+  <si>
+    <t>Home - News</t>
+  </si>
+  <si>
+    <t>In QA</t>
+  </si>
+  <si>
+    <t>FNS-101</t>
+  </si>
+  <si>
+    <t>Home - Videos</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>FNS-17</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>FNS-49</t>
+  </si>
+  <si>
+    <t>Stats</t>
+  </si>
+  <si>
+    <t>FNS-6</t>
+  </si>
+  <si>
+    <t>Showcase</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>FNS-13</t>
+  </si>
+  <si>
+    <t>Home - shop</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>FNS-41</t>
+  </si>
+  <si>
+    <t>Schedule</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>In Dev</t>
+  </si>
+  <si>
+    <t>FNS-8</t>
+  </si>
+  <si>
+    <t>Home - Fixtures</t>
+  </si>
+  <si>
+    <t>FNS-21</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>FNS-12</t>
+  </si>
+  <si>
+    <t>Home - Players</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>FNS-19</t>
+  </si>
+  <si>
+    <t>Photos Detail</t>
+  </si>
+  <si>
+    <t>FNS-14</t>
+  </si>
+  <si>
+    <t>SO Homepage Social Wall (Taggbox)</t>
+  </si>
+  <si>
+    <t>FNS-44</t>
+  </si>
+  <si>
+    <t>Players</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>FNS-45</t>
+  </si>
+  <si>
+    <t>Support Staff</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>FNS-46</t>
+  </si>
+  <si>
+    <t>player Profile</t>
+  </si>
+  <si>
+    <t>Code Review</t>
+  </si>
+  <si>
+    <t>FNS-48</t>
+  </si>
+  <si>
+    <t>SO Stats API Integration</t>
+  </si>
+  <si>
+    <t>Rejected</t>
+  </si>
+  <si>
+    <t>FNS-98</t>
+  </si>
+  <si>
+    <t>SO Design System</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>FNS-5</t>
+  </si>
+  <si>
+    <t>Top Menu, Bottom Menu</t>
+  </si>
+  <si>
+    <t>Footer</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>FNS-51</t>
+  </si>
+  <si>
+    <t>Both Standings css</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>HP News</t>
+  </si>
+  <si>
+    <t>HP Videos</t>
+  </si>
+  <si>
+    <t>FNS-11</t>
+  </si>
+  <si>
+    <t>HP Photos</t>
+  </si>
+  <si>
     <t>Need Clarification</t>
   </si>
   <si>
-    <t>GO Live</t>
-  </si>
-  <si>
-    <t>FNS-61</t>
-  </si>
-  <si>
-    <t>Homepage Header &amp; Footer</t>
-  </si>
-  <si>
-    <t>2026-07-29</t>
-  </si>
-  <si>
-    <t>FNS-63</t>
-  </si>
-  <si>
-    <t>Homepage Static Banner</t>
-  </si>
-  <si>
-    <t>FNS-64</t>
-  </si>
-  <si>
-    <t>Homepage Schedule Widget</t>
-  </si>
-  <si>
-    <t>FNS-88</t>
-  </si>
-  <si>
-    <t>Buy Tickets URL JSON</t>
-  </si>
-  <si>
-    <t>FNS-87</t>
-  </si>
-  <si>
-    <t>Fixtures &amp; Results</t>
-  </si>
-  <si>
-    <t>FNS-93</t>
-  </si>
-  <si>
-    <t>Matchcentre</t>
-  </si>
-  <si>
-    <t>FNS-92</t>
-  </si>
-  <si>
-    <t>Standing UI development</t>
-  </si>
-  <si>
-    <t>FNS-91</t>
-  </si>
-  <si>
-    <t>Standings API integration</t>
-  </si>
-  <si>
-    <t>FNS-65</t>
-  </si>
-  <si>
-    <t>Homepage Standings widget</t>
-  </si>
-  <si>
-    <t>FNS-90</t>
-  </si>
-  <si>
-    <t>Stats UI</t>
-  </si>
-  <si>
-    <t>FNS-89</t>
-  </si>
-  <si>
-    <t>Stats API integration</t>
-  </si>
-  <si>
-    <t>FNS-62</t>
-  </si>
-  <si>
-    <t>Homepage Showcase Carousel</t>
-  </si>
-  <si>
-    <t>FNS-66</t>
-  </si>
-  <si>
-    <t>Homepage News &amp; Videos</t>
-  </si>
-  <si>
-    <t>FNS-67</t>
-  </si>
-  <si>
-    <t>Homepage Photos</t>
-  </si>
-  <si>
-    <t>FNS-68</t>
-  </si>
-  <si>
-    <t>Homepage Squad</t>
-  </si>
-  <si>
-    <t>FNS-69</t>
-  </si>
-  <si>
-    <t>Homepage Shop Widget</t>
-  </si>
-  <si>
-    <t>FNS-70</t>
-  </si>
-  <si>
-    <t>Homepage Newsletter Widget</t>
-  </si>
-  <si>
-    <t>FNS-94</t>
-  </si>
-  <si>
-    <t>Squad Page</t>
-  </si>
-  <si>
-    <t>FNS-84</t>
-  </si>
-  <si>
-    <t>404</t>
-  </si>
-  <si>
-    <t>FNS-96</t>
-  </si>
-  <si>
-    <t>Custom JSON</t>
-  </si>
-  <si>
-    <t>FNS-95</t>
-  </si>
-  <si>
-    <t>Player Profile</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>FNS-56</t>
-  </si>
-  <si>
-    <t>WF Homepage design modifications</t>
-  </si>
-  <si>
-    <t>FNS-57</t>
-  </si>
-  <si>
-    <t>WF Content Pages design modifications</t>
-  </si>
-  <si>
-    <t>FNS-58</t>
-  </si>
-  <si>
-    <t>WF Data Pages design modifications</t>
-  </si>
-  <si>
-    <t>FNS-59</t>
-  </si>
-  <si>
-    <t>WF Static Pages design modifications</t>
-  </si>
-  <si>
-    <t>FNS-187</t>
-  </si>
-  <si>
-    <t>WF QA Testing</t>
-  </si>
-  <si>
-    <t>FNS-10</t>
-  </si>
-  <si>
-    <t>Home - News</t>
-  </si>
-  <si>
-    <t>In QA</t>
-  </si>
-  <si>
-    <t>FNS-101</t>
-  </si>
-  <si>
-    <t>Home - Videos</t>
-  </si>
-  <si>
-    <t>2026-09-10</t>
-  </si>
-  <si>
-    <t>FNS-17</t>
-  </si>
-  <si>
-    <t>2026-08-11</t>
-  </si>
-  <si>
-    <t>FNS-49</t>
-  </si>
-  <si>
-    <t>Stats</t>
-  </si>
-  <si>
-    <t>FNS-6</t>
-  </si>
-  <si>
-    <t>Showcase</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>FNS-13</t>
-  </si>
-  <si>
-    <t>Home - shop</t>
-  </si>
-  <si>
-    <t>2026-08-13</t>
-  </si>
-  <si>
-    <t>FNS-41</t>
-  </si>
-  <si>
-    <t>Schedule</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>FNS-8</t>
-  </si>
-  <si>
-    <t>Home - Fixtures</t>
-  </si>
-  <si>
-    <t>FNS-21</t>
-  </si>
-  <si>
-    <t>2026-08-17</t>
-  </si>
-  <si>
-    <t>FNS-12</t>
-  </si>
-  <si>
-    <t>Home - Players</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
-  </si>
-  <si>
-    <t>FNS-19</t>
-  </si>
-  <si>
-    <t>Photos Detail</t>
-  </si>
-  <si>
-    <t>FNS-14</t>
-  </si>
-  <si>
-    <t>SO Homepage Social Wall (Taggbox)</t>
-  </si>
-  <si>
-    <t>In Dev</t>
-  </si>
-  <si>
-    <t>FNS-44</t>
-  </si>
-  <si>
-    <t>Players</t>
-  </si>
-  <si>
-    <t>2026-08-24</t>
-  </si>
-  <si>
-    <t>2026-08-25</t>
-  </si>
-  <si>
-    <t>FNS-45</t>
-  </si>
-  <si>
-    <t>Support Staff</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>FNS-46</t>
-  </si>
-  <si>
-    <t>player Profile</t>
-  </si>
-  <si>
-    <t>FNS-48</t>
-  </si>
-  <si>
-    <t>SO Stats API Integration</t>
-  </si>
-  <si>
-    <t>Rejected</t>
-  </si>
-  <si>
-    <t>FNS-98</t>
-  </si>
-  <si>
-    <t>SO Design System</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>FNS-5</t>
-  </si>
-  <si>
-    <t>Top Menu, Bottom Menu</t>
-  </si>
-  <si>
-    <t>Footer</t>
-  </si>
-  <si>
-    <t>2026-09-08</t>
-  </si>
-  <si>
-    <t>FNS-51</t>
-  </si>
-  <si>
-    <t>Both Standings css</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
-  </si>
-  <si>
-    <t>HP News</t>
-  </si>
-  <si>
-    <t>HP Videos</t>
-  </si>
-  <si>
-    <t>FNS-11</t>
-  </si>
-  <si>
-    <t>HP Photos</t>
-  </si>
-  <si>
     <t>FNS-16</t>
   </si>
   <si>
@@ -752,9 +758,6 @@
     <t>Terms and Conditions</t>
   </si>
   <si>
-    <t>Ready for QA</t>
-  </si>
-  <si>
     <t>FNS-28</t>
   </si>
   <si>
@@ -800,9 +803,6 @@
     <t>Registration form (popup)</t>
   </si>
   <si>
-    <t>Code Review</t>
-  </si>
-  <si>
     <t>FNS-34</t>
   </si>
   <si>
@@ -833,135 +833,258 @@
     <t>Player registration embed</t>
   </si>
   <si>
+    <t>FNS-218</t>
+  </si>
+  <si>
+    <t>Team strip</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>FNS-234</t>
+  </si>
+  <si>
+    <t>About us</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
     <t>pending</t>
   </si>
   <si>
+    <t>Buy Tickets banner</t>
+  </si>
+  <si>
+    <t>Islander Banner</t>
+  </si>
+  <si>
+    <t>Esports</t>
+  </si>
+  <si>
+    <t>Social Hub</t>
+  </si>
+  <si>
+    <t>Esports Player Profile</t>
+  </si>
+  <si>
+    <t>Ticket T&amp;C</t>
+  </si>
+  <si>
+    <t>Community</t>
+  </si>
+  <si>
+    <t>Safeguarding</t>
+  </si>
+  <si>
+    <t>FNS-240</t>
+  </si>
+  <si>
+    <t>Cookie Policy</t>
+  </si>
+  <si>
+    <t>Ready for Dev</t>
+  </si>
+  <si>
+    <t>Error Page</t>
+  </si>
+  <si>
+    <t>FNS-215</t>
+  </si>
+  <si>
+    <t>Header &amp; Footer</t>
+  </si>
+  <si>
     <t>To Do</t>
   </si>
   <si>
+    <t>FNS-219</t>
+  </si>
+  <si>
+    <t>Standings</t>
+  </si>
+  <si>
+    <t>FNS-241</t>
+  </si>
+  <si>
+    <t>Squad</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>External links - 1 ticket maybe</t>
+  </si>
+  <si>
+    <t>Buffer Due to New Module</t>
+  </si>
+  <si>
+    <t>Fixses</t>
+  </si>
+  <si>
+    <t>Aapla 12th Man Poll</t>
+  </si>
+  <si>
+    <t>Goal of the Month</t>
+  </si>
+  <si>
+    <t>FNS-223</t>
+  </si>
+  <si>
+    <t>Homepage listings</t>
+  </si>
+  <si>
+    <t>FNS-100</t>
+  </si>
+  <si>
+    <t>PVL Design System</t>
+  </si>
+  <si>
+    <t>FNS-216</t>
+  </si>
+  <si>
+    <t>HP Showcase</t>
+  </si>
+  <si>
+    <t>Buffer Due to FIH</t>
+  </si>
+  <si>
+    <t>FNS-15</t>
+  </si>
+  <si>
+    <t>Newsletter Subscribe Block (API)</t>
+  </si>
+  <si>
+    <t>FNS-22</t>
+  </si>
+  <si>
+    <t>Podsquad Page</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>Go Live</t>
+  </si>
+  <si>
+    <t>Top Menu, Bottom Menu/Footer</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>Fixtures</t>
+  </si>
+  <si>
+    <t>News</t>
+  </si>
+  <si>
+    <t>Subscribe to emails form</t>
+  </si>
+  <si>
+    <t>Videos</t>
+  </si>
+  <si>
+    <t>Aapla 12th Man Banner</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>Photos</t>
+  </si>
+  <si>
+    <t>Tracker</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>News Listing &amp; Detail</t>
+  </si>
+  <si>
+    <t>Video Listing and Detail</t>
+  </si>
+  <si>
+    <t>Photos Listing &amp; Detail</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>New Crest</t>
+  </si>
+  <si>
+    <t>New Crest Contest Terms and Conditions</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>Islander of the match</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>Goal of the season</t>
+  </si>
+  <si>
+    <t>Islander of the month</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>Save of the Month</t>
+  </si>
+  <si>
+    <t>Save of the Season</t>
+  </si>
+  <si>
+    <t>Shop</t>
+  </si>
+  <si>
     <t>FNS-217</t>
   </si>
   <si>
     <t>HP Static Banner</t>
   </si>
   <si>
-    <t>FNS-218</t>
-  </si>
-  <si>
-    <t>Team strip</t>
-  </si>
-  <si>
     <t>FNS-235</t>
   </si>
   <si>
-    <t>2026-09-02</t>
-  </si>
-  <si>
     <t>FNS-238</t>
   </si>
   <si>
     <t>T&amp;C page</t>
   </si>
   <si>
-    <t>FNS-234</t>
-  </si>
-  <si>
-    <t>About us</t>
-  </si>
-  <si>
-    <t>2026-09-03</t>
-  </si>
-  <si>
     <t>FNS-236</t>
   </si>
   <si>
     <t>Hall of fame</t>
   </si>
   <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>Buy Tickets banner</t>
-  </si>
-  <si>
-    <t>Islander Banner</t>
-  </si>
-  <si>
-    <t>Esports</t>
-  </si>
-  <si>
-    <t>Social Hub</t>
-  </si>
-  <si>
-    <t>Esports Player Profile</t>
-  </si>
-  <si>
-    <t>Ticket T&amp;C</t>
-  </si>
-  <si>
-    <t>Community</t>
-  </si>
-  <si>
-    <t>Safeguarding</t>
-  </si>
-  <si>
     <t>FNS-239</t>
   </si>
   <si>
-    <t>FNS-240</t>
-  </si>
-  <si>
-    <t>Cookie Policy</t>
-  </si>
-  <si>
-    <t>Error Page</t>
-  </si>
-  <si>
-    <t>FNS-215</t>
-  </si>
-  <si>
-    <t>Header &amp; Footer</t>
-  </si>
-  <si>
-    <t>FNS-219</t>
-  </si>
-  <si>
-    <t>Standings</t>
-  </si>
-  <si>
-    <t>FNS-241</t>
-  </si>
-  <si>
-    <t>Squad</t>
-  </si>
-  <si>
-    <t>External links - 1 ticket maybe</t>
-  </si>
-  <si>
-    <t>Buffer Due to New Module</t>
-  </si>
-  <si>
-    <t>Fixses</t>
-  </si>
-  <si>
-    <t>Aapla 12th Man Poll</t>
-  </si>
-  <si>
-    <t>Goal of the Month</t>
-  </si>
-  <si>
-    <t>FNS-223</t>
-  </si>
-  <si>
-    <t>Homepage listings</t>
-  </si>
-  <si>
-    <t>FNS-100</t>
-  </si>
-  <si>
-    <t>PVL Design System</t>
-  </si>
-  <si>
     <t>FNS-220</t>
   </si>
   <si>
@@ -974,15 +1097,6 @@
     <t>Homepage News Widget</t>
   </si>
   <si>
-    <t>FNS-216</t>
-  </si>
-  <si>
-    <t>HP Showcase</t>
-  </si>
-  <si>
-    <t>Buffer Due to FIH</t>
-  </si>
-  <si>
     <t>FNS-222</t>
   </si>
   <si>
@@ -1035,117 +1149,6 @@
   </si>
   <si>
     <t>Photos Detail Page</t>
-  </si>
-  <si>
-    <t>FNS-15</t>
-  </si>
-  <si>
-    <t>Newsletter Subscribe Block (API)</t>
-  </si>
-  <si>
-    <t>FNS-22</t>
-  </si>
-  <si>
-    <t>Podsquad Page</t>
-  </si>
-  <si>
-    <t>2026-09-21</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>Go Live</t>
-  </si>
-  <si>
-    <t>Top Menu, Bottom Menu/Footer</t>
-  </si>
-  <si>
-    <t>2026-09-18</t>
-  </si>
-  <si>
-    <t>2026-08-30</t>
-  </si>
-  <si>
-    <t>Fixtures</t>
-  </si>
-  <si>
-    <t>News</t>
-  </si>
-  <si>
-    <t>Subscribe to emails form</t>
-  </si>
-  <si>
-    <t>Videos</t>
-  </si>
-  <si>
-    <t>Aapla 12th Man Banner</t>
-  </si>
-  <si>
-    <t>2026-09-17</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>Photos</t>
-  </si>
-  <si>
-    <t>Tracker</t>
-  </si>
-  <si>
-    <t>2026-09-05</t>
-  </si>
-  <si>
-    <t>News Listing &amp; Detail</t>
-  </si>
-  <si>
-    <t>Video Listing and Detail</t>
-  </si>
-  <si>
-    <t>Photos Listing &amp; Detail</t>
-  </si>
-  <si>
-    <t>Login</t>
-  </si>
-  <si>
-    <t>Profile</t>
-  </si>
-  <si>
-    <t>New Crest</t>
-  </si>
-  <si>
-    <t>New Crest Contest Terms and Conditions</t>
-  </si>
-  <si>
-    <t>2026-09-19</t>
-  </si>
-  <si>
-    <t>Islander of the match</t>
-  </si>
-  <si>
-    <t>2026-09-14</t>
-  </si>
-  <si>
-    <t>Goal of the season</t>
-  </si>
-  <si>
-    <t>Islander of the month</t>
-  </si>
-  <si>
-    <t>2026-09-22</t>
-  </si>
-  <si>
-    <t>Save of the Month</t>
-  </si>
-  <si>
-    <t>Save of the Season</t>
-  </si>
-  <si>
-    <t>Shop</t>
   </si>
 </sst>
 </file>
@@ -2148,7 +2151,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2167,13 +2170,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2">
-        <v>83.5</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
         <v>67</v>
@@ -2181,13 +2184,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
         <v>67</v>
@@ -2195,13 +2198,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4">
-        <v>20.8</v>
+        <v>15.75</v>
       </c>
       <c r="D4" t="s">
         <v>67</v>
@@ -2209,13 +2212,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
         <v>67</v>
@@ -2223,13 +2226,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>67</v>
@@ -2240,10 +2243,10 @@
         <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>56</v>
+        <v>91.5</v>
       </c>
       <c r="D7" t="s">
         <v>67</v>
@@ -2251,13 +2254,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>35</v>
+        <v>38.83</v>
       </c>
       <c r="D8" t="s">
         <v>67</v>
@@ -2265,13 +2268,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C9">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
         <v>67</v>
@@ -2279,13 +2282,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C10">
-        <v>15.8</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
         <v>67</v>
@@ -2293,13 +2296,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
         <v>67</v>
@@ -2307,13 +2310,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
         <v>67</v>
@@ -2321,29 +2324,71 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C13">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>41</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>61</v>
+      </c>
+      <c r="D16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
         <v>9</v>
       </c>
-      <c r="C14">
+      <c r="C17">
         <v>32</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D17" t="s">
         <v>68</v>
       </c>
     </row>
@@ -5468,7 +5513,7 @@
         <v>5</v>
       </c>
       <c r="M5" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -5591,7 +5636,7 @@
         <v>5</v>
       </c>
       <c r="M8" t="s">
-        <v>124</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -5605,10 +5650,10 @@
         <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
@@ -5646,7 +5691,7 @@
         <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E10" t="s">
         <v>97</v>
@@ -5666,7 +5711,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
@@ -5675,10 +5720,10 @@
         <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -5690,7 +5735,7 @@
         <v>5</v>
       </c>
       <c r="I11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J11" t="s">
         <v>47</v>
@@ -5707,7 +5752,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
@@ -5716,10 +5761,10 @@
         <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -5731,7 +5776,7 @@
         <v>5</v>
       </c>
       <c r="I12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J12" t="s">
         <v>47</v>
@@ -5748,7 +5793,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
@@ -5757,19 +5802,19 @@
         <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G13" t="s">
         <v>52</v>
       </c>
       <c r="I13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M13" t="s">
         <v>182</v>
@@ -5786,10 +5831,10 @@
         <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G14" t="s">
         <v>52</v>
@@ -5801,7 +5846,7 @@
         <v>169</v>
       </c>
       <c r="M14" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -5815,10 +5860,10 @@
         <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F15" t="s">
         <v>5</v>
@@ -5830,7 +5875,7 @@
         <v>5</v>
       </c>
       <c r="I15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J15" t="s">
         <v>47</v>
@@ -5883,7 +5928,7 @@
         <v>5</v>
       </c>
       <c r="M16" t="s">
-        <v>124</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -5924,7 +5969,7 @@
         <v>5</v>
       </c>
       <c r="M17" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -5965,7 +6010,7 @@
         <v>5</v>
       </c>
       <c r="M18" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -6006,7 +6051,7 @@
         <v>5</v>
       </c>
       <c r="M19" t="s">
-        <v>124</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -6047,7 +6092,7 @@
         <v>5</v>
       </c>
       <c r="M20" t="s">
-        <v>124</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -6129,7 +6174,7 @@
         <v>5</v>
       </c>
       <c r="M22" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -6143,10 +6188,10 @@
         <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G23" t="s">
         <v>83</v>
@@ -6161,7 +6206,7 @@
         <v>169</v>
       </c>
       <c r="M23" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -6175,10 +6220,10 @@
         <v>48</v>
       </c>
       <c r="D24" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E24" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G24" t="s">
         <v>83</v>
@@ -6196,9 +6241,12 @@
         <v>112</v>
       </c>
     </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B28" t="s">
         <v>3</v>
@@ -6207,10 +6255,10 @@
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
@@ -6222,10 +6270,10 @@
         <v>5</v>
       </c>
       <c r="I28" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J28" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
@@ -6234,12 +6282,12 @@
         <v>5</v>
       </c>
       <c r="M28" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B29" t="s">
         <v>3</v>
@@ -6248,10 +6296,10 @@
         <v>48</v>
       </c>
       <c r="D29" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E29" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F29" t="s">
         <v>5</v>
@@ -6263,10 +6311,10 @@
         <v>5</v>
       </c>
       <c r="I29" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J29" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K29" t="s">
         <v>5</v>
@@ -6275,12 +6323,12 @@
         <v>5</v>
       </c>
       <c r="M29" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B30" t="s">
         <v>3</v>
@@ -6289,10 +6337,10 @@
         <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E30" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F30" t="s">
         <v>5</v>
@@ -6304,10 +6352,10 @@
         <v>5</v>
       </c>
       <c r="I30" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J30" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
@@ -6321,7 +6369,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B31" t="s">
         <v>3</v>
@@ -6333,7 +6381,7 @@
         <v>5</v>
       </c>
       <c r="E31" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F31" t="s">
         <v>5</v>
@@ -6345,10 +6393,10 @@
         <v>5</v>
       </c>
       <c r="I31" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J31" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
@@ -6359,7 +6407,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B32" t="s">
         <v>3</v>
@@ -6371,7 +6419,7 @@
         <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F32" t="s">
         <v>5</v>
@@ -6383,10 +6431,10 @@
         <v>5</v>
       </c>
       <c r="I32" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J32" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
@@ -6397,7 +6445,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B33" t="s">
         <v>3</v>
@@ -6406,10 +6454,10 @@
         <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E33" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F33" t="s">
         <v>5</v>
@@ -6421,10 +6469,10 @@
         <v>5</v>
       </c>
       <c r="I33" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J33" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
@@ -6433,7 +6481,7 @@
         <v>5</v>
       </c>
       <c r="M33" t="s">
-        <v>124</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
@@ -6447,7 +6495,7 @@
         <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E34" t="s">
         <v>90</v>
@@ -6488,7 +6536,7 @@
         <v>48</v>
       </c>
       <c r="D35" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E35" t="s">
         <v>82</v>
@@ -6520,7 +6568,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B36" t="s">
         <v>3</v>
@@ -6529,10 +6577,10 @@
         <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E36" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F36" t="s">
         <v>5</v>
@@ -6544,16 +6592,16 @@
         <v>5</v>
       </c>
       <c r="I36" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J36" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K36" t="s">
         <v>5</v>
       </c>
       <c r="L36" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M36" t="s">
         <v>182</v>
@@ -6570,10 +6618,10 @@
         <v>48</v>
       </c>
       <c r="D37" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E37" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F37" t="s">
         <v>5</v>
@@ -6597,7 +6645,7 @@
         <v>215</v>
       </c>
       <c r="M37" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -6611,10 +6659,10 @@
         <v>48</v>
       </c>
       <c r="D38" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E38" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F38" t="s">
         <v>5</v>
@@ -6638,7 +6686,7 @@
         <v>5</v>
       </c>
       <c r="M38" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -6652,10 +6700,10 @@
         <v>48</v>
       </c>
       <c r="D39" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E39" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F39" t="s">
         <v>5</v>
@@ -6679,7 +6727,7 @@
         <v>5</v>
       </c>
       <c r="M39" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -6693,7 +6741,7 @@
         <v>48</v>
       </c>
       <c r="D40" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E40" t="s">
         <v>164</v>
@@ -6720,7 +6768,7 @@
         <v>5</v>
       </c>
       <c r="M40" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -6734,10 +6782,10 @@
         <v>48</v>
       </c>
       <c r="D41" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E41" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F41" t="s">
         <v>5</v>
@@ -6761,7 +6809,7 @@
         <v>5</v>
       </c>
       <c r="M41" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
@@ -6775,10 +6823,10 @@
         <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E42" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F42" t="s">
         <v>5</v>
@@ -6816,10 +6864,10 @@
         <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E43" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F43" t="s">
         <v>5</v>
@@ -6843,7 +6891,7 @@
         <v>5</v>
       </c>
       <c r="M43" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -6857,10 +6905,10 @@
         <v>48</v>
       </c>
       <c r="D44" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E44" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F44" t="s">
         <v>5</v>
@@ -6884,7 +6932,7 @@
         <v>5</v>
       </c>
       <c r="M44" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -6898,10 +6946,10 @@
         <v>48</v>
       </c>
       <c r="D45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F45" t="s">
         <v>5</v>
@@ -6925,7 +6973,7 @@
         <v>5</v>
       </c>
       <c r="M45" t="s">
-        <v>260</v>
+        <v>221</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
@@ -6966,7 +7014,7 @@
         <v>5</v>
       </c>
       <c r="M46" t="s">
-        <v>260</v>
+        <v>221</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -7007,7 +7055,7 @@
         <v>5</v>
       </c>
       <c r="M47" t="s">
-        <v>260</v>
+        <v>221</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
@@ -7048,7 +7096,7 @@
         <v>5</v>
       </c>
       <c r="M48" t="s">
-        <v>260</v>
+        <v>182</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -7089,9 +7137,18 @@
         <v>5</v>
       </c>
       <c r="M49" t="s">
-        <v>211</v>
-      </c>
-    </row>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>214</v>
@@ -7168,7 +7225,7 @@
         <v>5</v>
       </c>
       <c r="M60" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -7209,7 +7266,7 @@
         <v>5</v>
       </c>
       <c r="M61" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -7250,7 +7307,7 @@
         <v>5</v>
       </c>
       <c r="M62" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -7342,7 +7399,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -7414,7 +7471,7 @@
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>271</v>
+        <v>52</v>
       </c>
       <c r="H2" t="s">
         <v>5</v>
@@ -7432,7 +7489,7 @@
         <v>5</v>
       </c>
       <c r="M2" t="s">
-        <v>272</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -7440,22 +7497,22 @@
         <v>268</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
         <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F3" t="s">
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>271</v>
+        <v>52</v>
       </c>
       <c r="H3" t="s">
         <v>5</v>
@@ -7473,39 +7530,39 @@
         <v>5</v>
       </c>
       <c r="M3" t="s">
-        <v>272</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>53</v>
       </c>
       <c r="D4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E4" t="s">
         <v>275</v>
       </c>
-      <c r="E4" t="s">
-        <v>276</v>
-      </c>
       <c r="F4" t="s">
         <v>5</v>
       </c>
       <c r="G4" t="s">
-        <v>271</v>
+        <v>52</v>
       </c>
       <c r="H4" t="s">
         <v>5</v>
       </c>
       <c r="I4" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="J4" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K4" t="s">
         <v>5</v>
@@ -7514,12 +7571,12 @@
         <v>5</v>
       </c>
       <c r="M4" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>268</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -7528,25 +7585,25 @@
         <v>53</v>
       </c>
       <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>276</v>
+      </c>
+      <c r="F5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" t="s">
         <v>277</v>
       </c>
-      <c r="E5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" t="s">
-        <v>271</v>
-      </c>
       <c r="H5" t="s">
         <v>5</v>
       </c>
       <c r="I5" t="s">
-        <v>268</v>
+        <v>51</v>
       </c>
       <c r="J5" t="s">
-        <v>268</v>
+        <v>51</v>
       </c>
       <c r="K5" t="s">
         <v>5</v>
@@ -7554,13 +7611,10 @@
       <c r="L5" t="s">
         <v>5</v>
       </c>
-      <c r="M5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -7569,25 +7623,25 @@
         <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>279</v>
+        <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H6" t="s">
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="J6" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="K6" t="s">
         <v>5</v>
@@ -7595,13 +7649,10 @@
       <c r="L6" t="s">
         <v>5</v>
       </c>
-      <c r="M6" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -7610,25 +7661,25 @@
         <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>281</v>
+        <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H7" t="s">
         <v>5</v>
       </c>
       <c r="I7" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="J7" t="s">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="K7" t="s">
         <v>5</v>
@@ -7636,13 +7687,10 @@
       <c r="L7" t="s">
         <v>5</v>
       </c>
-      <c r="M7" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>283</v>
+        <v>227</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -7651,39 +7699,36 @@
         <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>284</v>
+        <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F8" t="s">
         <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H8" t="s">
         <v>5</v>
       </c>
       <c r="I8" t="s">
-        <v>283</v>
+        <v>227</v>
       </c>
       <c r="J8" t="s">
-        <v>283</v>
+        <v>227</v>
       </c>
       <c r="K8" t="s">
         <v>5</v>
       </c>
       <c r="L8" t="s">
         <v>5</v>
-      </c>
-      <c r="M8" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>231</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -7695,22 +7740,22 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
       <c r="G9" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H9" t="s">
         <v>5</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>231</v>
       </c>
       <c r="J9" t="s">
-        <v>51</v>
+        <v>231</v>
       </c>
       <c r="K9" t="s">
         <v>5</v>
@@ -7721,7 +7766,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -7733,22 +7778,22 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H10" t="s">
         <v>5</v>
       </c>
       <c r="I10" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="J10" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="K10" t="s">
         <v>5</v>
@@ -7759,7 +7804,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
@@ -7771,22 +7816,22 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>288</v>
+        <v>106</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
       </c>
       <c r="I11" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="J11" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="K11" t="s">
         <v>5</v>
@@ -7797,7 +7842,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -7809,22 +7854,22 @@
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
       </c>
       <c r="G12" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H12" t="s">
         <v>5</v>
       </c>
       <c r="I12" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="J12" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="K12" t="s">
         <v>5</v>
@@ -7835,7 +7880,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -7847,22 +7892,22 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
       </c>
       <c r="G13" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H13" t="s">
         <v>5</v>
       </c>
       <c r="I13" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
       <c r="J13" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
       <c r="K13" t="s">
         <v>5</v>
@@ -7873,7 +7918,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>233</v>
+        <v>185</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -7885,22 +7930,22 @@
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="F14" t="s">
         <v>5</v>
       </c>
       <c r="G14" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H14" t="s">
         <v>5</v>
       </c>
       <c r="I14" t="s">
-        <v>233</v>
+        <v>185</v>
       </c>
       <c r="J14" t="s">
-        <v>233</v>
+        <v>185</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
@@ -7909,9 +7954,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
@@ -7920,36 +7965,39 @@
         <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>5</v>
+        <v>286</v>
       </c>
       <c r="E15" t="s">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="F15" t="s">
         <v>5</v>
       </c>
       <c r="G15" t="s">
-        <v>271</v>
+        <v>52</v>
       </c>
       <c r="H15" t="s">
         <v>5</v>
       </c>
       <c r="I15" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="J15" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="K15" t="s">
         <v>5</v>
       </c>
       <c r="L15" t="s">
         <v>5</v>
+      </c>
+      <c r="M15" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
@@ -7961,22 +8009,22 @@
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F16" t="s">
         <v>5</v>
       </c>
       <c r="G16" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H16" t="s">
         <v>5</v>
       </c>
       <c r="I16" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="J16" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -7985,36 +8033,36 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
         <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>5</v>
+        <v>290</v>
       </c>
       <c r="E17" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F17" t="s">
         <v>5</v>
       </c>
       <c r="G17" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H17" t="s">
         <v>5</v>
       </c>
       <c r="I17" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="J17" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
@@ -8022,19 +8070,22 @@
       <c r="L17" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M17" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>185</v>
+        <v>268</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
         <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>293</v>
       </c>
       <c r="E18" t="s">
         <v>294</v>
@@ -8043,30 +8094,33 @@
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H18" t="s">
         <v>5</v>
       </c>
       <c r="I18" t="s">
-        <v>185</v>
+        <v>268</v>
       </c>
       <c r="J18" t="s">
-        <v>185</v>
+        <v>268</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
       </c>
       <c r="L18" t="s">
         <v>5</v>
+      </c>
+      <c r="M18" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>185</v>
+        <v>273</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
         <v>53</v>
@@ -8075,22 +8129,22 @@
         <v>295</v>
       </c>
       <c r="E19" t="s">
-        <v>246</v>
+        <v>296</v>
       </c>
       <c r="F19" t="s">
         <v>5</v>
       </c>
       <c r="G19" t="s">
-        <v>271</v>
+        <v>52</v>
       </c>
       <c r="H19" t="s">
         <v>5</v>
       </c>
       <c r="I19" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="J19" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
@@ -8099,39 +8153,39 @@
         <v>5</v>
       </c>
       <c r="M19" t="s">
-        <v>272</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>206</v>
+        <v>297</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
         <v>53</v>
       </c>
       <c r="D20" t="s">
+        <v>295</v>
+      </c>
+      <c r="E20" t="s">
         <v>296</v>
       </c>
-      <c r="E20" t="s">
-        <v>297</v>
-      </c>
       <c r="F20" t="s">
         <v>5</v>
       </c>
       <c r="G20" t="s">
-        <v>271</v>
+        <v>52</v>
       </c>
       <c r="H20" t="s">
         <v>5</v>
       </c>
       <c r="I20" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="J20" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
@@ -8140,15 +8194,15 @@
         <v>5</v>
       </c>
       <c r="M20" t="s">
-        <v>272</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>206</v>
+        <v>297</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
         <v>53</v>
@@ -8163,16 +8217,16 @@
         <v>5</v>
       </c>
       <c r="G21" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H21" t="s">
         <v>5</v>
       </c>
       <c r="I21" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="J21" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
@@ -8181,9 +8235,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
         <v>11</v>
@@ -8192,25 +8246,25 @@
         <v>53</v>
       </c>
       <c r="D22" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
         <v>299</v>
       </c>
-      <c r="E22" t="s">
-        <v>300</v>
-      </c>
       <c r="F22" t="s">
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H22" t="s">
         <v>5</v>
       </c>
       <c r="I22" t="s">
-        <v>169</v>
+        <v>297</v>
       </c>
       <c r="J22" t="s">
-        <v>169</v>
+        <v>297</v>
       </c>
       <c r="K22" t="s">
         <v>5</v>
@@ -8218,13 +8272,10 @@
       <c r="L22" t="s">
         <v>5</v>
       </c>
-      <c r="M22" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>268</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
@@ -8233,25 +8284,25 @@
         <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>301</v>
+        <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F23" t="s">
         <v>5</v>
       </c>
       <c r="G23" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H23" t="s">
         <v>5</v>
       </c>
       <c r="I23" t="s">
-        <v>268</v>
+        <v>227</v>
       </c>
       <c r="J23" t="s">
-        <v>268</v>
+        <v>234</v>
       </c>
       <c r="K23" t="s">
         <v>5</v>
@@ -8259,40 +8310,37 @@
       <c r="L23" t="s">
         <v>5</v>
       </c>
-      <c r="M23" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>278</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24" t="s">
         <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>303</v>
+        <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F24" t="s">
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H24" t="s">
         <v>5</v>
       </c>
       <c r="I24" t="s">
-        <v>169</v>
+        <v>227</v>
       </c>
       <c r="J24" t="s">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
@@ -8300,57 +8348,51 @@
       <c r="L24" t="s">
         <v>5</v>
       </c>
-      <c r="M24" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>283</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
         <v>53</v>
       </c>
       <c r="D25" t="s">
-        <v>303</v>
+        <v>5</v>
       </c>
       <c r="E25" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F25" t="s">
         <v>5</v>
       </c>
       <c r="G25" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H25" t="s">
         <v>5</v>
       </c>
       <c r="I25" t="s">
-        <v>169</v>
+        <v>227</v>
       </c>
       <c r="J25" t="s">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
       </c>
       <c r="L25" t="s">
         <v>5</v>
-      </c>
-      <c r="M25" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>283</v>
+        <v>185</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C26" t="s">
         <v>53</v>
@@ -8359,22 +8401,22 @@
         <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>305</v>
+        <v>125</v>
       </c>
       <c r="F26" t="s">
         <v>5</v>
       </c>
       <c r="G26" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H26" t="s">
         <v>5</v>
       </c>
       <c r="I26" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="J26" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
@@ -8385,7 +8427,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>207</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
@@ -8397,22 +8439,22 @@
         <v>5</v>
       </c>
       <c r="E27" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="F27" t="s">
         <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H27" t="s">
         <v>5</v>
       </c>
       <c r="I27" t="s">
-        <v>283</v>
+        <v>207</v>
       </c>
       <c r="J27" t="s">
-        <v>283</v>
+        <v>207</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
@@ -8423,7 +8465,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
@@ -8435,22 +8477,22 @@
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
       </c>
       <c r="G28" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H28" t="s">
         <v>5</v>
       </c>
       <c r="I28" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="J28" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
@@ -8459,36 +8501,36 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>230</v>
+        <v>169</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C29" t="s">
         <v>53</v>
       </c>
       <c r="D29" t="s">
-        <v>5</v>
+        <v>303</v>
       </c>
       <c r="E29" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F29" t="s">
         <v>5</v>
       </c>
       <c r="G29" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H29" t="s">
         <v>5</v>
       </c>
       <c r="I29" t="s">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="J29" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="K29" t="s">
         <v>5</v>
@@ -8496,48 +8538,45 @@
       <c r="L29" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M29" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>233</v>
+        <v>169</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C30" t="s">
         <v>53</v>
       </c>
       <c r="D30" t="s">
-        <v>5</v>
+        <v>305</v>
       </c>
       <c r="E30" t="s">
-        <v>307</v>
-      </c>
-      <c r="F30" t="s">
-        <v>5</v>
+        <v>306</v>
       </c>
       <c r="G30" t="s">
-        <v>271</v>
-      </c>
-      <c r="H30" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="I30" t="s">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="J30" t="s">
-        <v>233</v>
-      </c>
-      <c r="K30" t="s">
-        <v>5</v>
+        <v>169</v>
       </c>
       <c r="L30" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="M30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>185</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s">
         <v>11</v>
@@ -8546,39 +8585,42 @@
         <v>53</v>
       </c>
       <c r="D31" t="s">
-        <v>5</v>
+        <v>307</v>
       </c>
       <c r="E31" t="s">
-        <v>125</v>
+        <v>308</v>
       </c>
       <c r="F31" t="s">
         <v>5</v>
       </c>
       <c r="G31" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H31" t="s">
         <v>5</v>
       </c>
       <c r="I31" t="s">
-        <v>185</v>
+        <v>273</v>
       </c>
       <c r="J31" t="s">
-        <v>185</v>
+        <v>273</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
       </c>
       <c r="L31" t="s">
         <v>5</v>
+      </c>
+      <c r="M31" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>206</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
         <v>53</v>
@@ -8587,22 +8629,22 @@
         <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F32" t="s">
         <v>5</v>
       </c>
       <c r="G32" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H32" t="s">
         <v>5</v>
       </c>
       <c r="I32" t="s">
-        <v>206</v>
+        <v>51</v>
       </c>
       <c r="J32" t="s">
-        <v>206</v>
+        <v>51</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
@@ -8611,9 +8653,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="B33" t="s">
         <v>11</v>
@@ -8622,31 +8664,22 @@
         <v>53</v>
       </c>
       <c r="D33" t="s">
-        <v>5</v>
+        <v>310</v>
       </c>
       <c r="E33" t="s">
-        <v>309</v>
-      </c>
-      <c r="F33" t="s">
-        <v>5</v>
+        <v>311</v>
       </c>
       <c r="G33" t="s">
-        <v>271</v>
-      </c>
-      <c r="H33" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="I33" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="J33" t="s">
-        <v>206</v>
-      </c>
-      <c r="K33" t="s">
-        <v>5</v>
-      </c>
-      <c r="L33" t="s">
-        <v>5</v>
+        <v>169</v>
+      </c>
+      <c r="M33" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
@@ -8654,528 +8687,28 @@
         <v>169</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C34" t="s">
         <v>53</v>
       </c>
       <c r="D34" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E34" t="s">
-        <v>311</v>
-      </c>
-      <c r="F34" t="s">
-        <v>5</v>
+        <v>313</v>
       </c>
       <c r="G34" t="s">
-        <v>271</v>
-      </c>
-      <c r="H34" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="I34" t="s">
-        <v>268</v>
+        <v>169</v>
       </c>
       <c r="J34" t="s">
-        <v>268</v>
-      </c>
-      <c r="K34" t="s">
-        <v>5</v>
-      </c>
-      <c r="L34" t="s">
-        <v>5</v>
+        <v>169</v>
       </c>
       <c r="M34" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>169</v>
-      </c>
-      <c r="B35" t="s">
-        <v>19</v>
-      </c>
-      <c r="C35" t="s">
-        <v>53</v>
-      </c>
-      <c r="D35" t="s">
-        <v>312</v>
-      </c>
-      <c r="E35" t="s">
-        <v>313</v>
-      </c>
-      <c r="G35" t="s">
-        <v>83</v>
-      </c>
-      <c r="I35" t="s">
-        <v>169</v>
-      </c>
-      <c r="J35" t="s">
-        <v>169</v>
-      </c>
-      <c r="L35" t="s">
-        <v>169</v>
-      </c>
-      <c r="M35" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>169</v>
-      </c>
-      <c r="B36" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" t="s">
-        <v>53</v>
-      </c>
-      <c r="D36" t="s">
-        <v>314</v>
-      </c>
-      <c r="E36" t="s">
-        <v>315</v>
-      </c>
-      <c r="G36" t="s">
-        <v>271</v>
-      </c>
-      <c r="I36" t="s">
-        <v>169</v>
-      </c>
-      <c r="J36" t="s">
-        <v>169</v>
-      </c>
-      <c r="M36" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>169</v>
-      </c>
-      <c r="B37" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" t="s">
-        <v>53</v>
-      </c>
-      <c r="D37" t="s">
-        <v>316</v>
-      </c>
-      <c r="E37" t="s">
-        <v>317</v>
-      </c>
-      <c r="G37" t="s">
-        <v>271</v>
-      </c>
-      <c r="I37" t="s">
-        <v>169</v>
-      </c>
-      <c r="J37" t="s">
-        <v>169</v>
-      </c>
-      <c r="M37" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>283</v>
-      </c>
-      <c r="B38" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" t="s">
-        <v>53</v>
-      </c>
-      <c r="D38" t="s">
-        <v>318</v>
-      </c>
-      <c r="E38" t="s">
-        <v>319</v>
-      </c>
-      <c r="F38" t="s">
-        <v>5</v>
-      </c>
-      <c r="G38" t="s">
-        <v>271</v>
-      </c>
-      <c r="H38" t="s">
-        <v>5</v>
-      </c>
-      <c r="I38" t="s">
-        <v>278</v>
-      </c>
-      <c r="J38" t="s">
-        <v>278</v>
-      </c>
-      <c r="K38" t="s">
-        <v>5</v>
-      </c>
-      <c r="L38" t="s">
-        <v>5</v>
-      </c>
-      <c r="M38" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" t="s">
-        <v>53</v>
-      </c>
-      <c r="D39" t="s">
-        <v>5</v>
-      </c>
-      <c r="E39" t="s">
-        <v>320</v>
-      </c>
-      <c r="F39" t="s">
-        <v>5</v>
-      </c>
-      <c r="G39" t="s">
-        <v>271</v>
-      </c>
-      <c r="H39" t="s">
-        <v>5</v>
-      </c>
-      <c r="I39" t="s">
-        <v>51</v>
-      </c>
-      <c r="J39" t="s">
-        <v>51</v>
-      </c>
-      <c r="K39" t="s">
-        <v>5</v>
-      </c>
-      <c r="L39" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>169</v>
-      </c>
-      <c r="B40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" t="s">
-        <v>53</v>
-      </c>
-      <c r="D40" t="s">
-        <v>321</v>
-      </c>
-      <c r="E40" t="s">
-        <v>322</v>
-      </c>
-      <c r="G40" t="s">
-        <v>271</v>
-      </c>
-      <c r="I40" t="s">
-        <v>169</v>
-      </c>
-      <c r="J40" t="s">
-        <v>169</v>
-      </c>
-      <c r="M40" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>169</v>
-      </c>
-      <c r="B41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" t="s">
-        <v>53</v>
-      </c>
-      <c r="D41" t="s">
-        <v>323</v>
-      </c>
-      <c r="E41" t="s">
-        <v>324</v>
-      </c>
-      <c r="G41" t="s">
-        <v>271</v>
-      </c>
-      <c r="I41" t="s">
-        <v>169</v>
-      </c>
-      <c r="J41" t="s">
-        <v>169</v>
-      </c>
-      <c r="M41" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>169</v>
-      </c>
-      <c r="B42" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" t="s">
-        <v>53</v>
-      </c>
-      <c r="D42" t="s">
-        <v>325</v>
-      </c>
-      <c r="E42" t="s">
-        <v>326</v>
-      </c>
-      <c r="G42" t="s">
-        <v>271</v>
-      </c>
-      <c r="I42" t="s">
-        <v>169</v>
-      </c>
-      <c r="J42" t="s">
-        <v>169</v>
-      </c>
-      <c r="M42" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>169</v>
-      </c>
-      <c r="B43" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" t="s">
-        <v>53</v>
-      </c>
-      <c r="D43" t="s">
-        <v>327</v>
-      </c>
-      <c r="E43" t="s">
-        <v>328</v>
-      </c>
-      <c r="G43" t="s">
-        <v>271</v>
-      </c>
-      <c r="I43" t="s">
-        <v>169</v>
-      </c>
-      <c r="J43" t="s">
-        <v>169</v>
-      </c>
-      <c r="M43" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>169</v>
-      </c>
-      <c r="B44" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" t="s">
-        <v>53</v>
-      </c>
-      <c r="D44" t="s">
-        <v>329</v>
-      </c>
-      <c r="E44" t="s">
-        <v>330</v>
-      </c>
-      <c r="G44" t="s">
-        <v>271</v>
-      </c>
-      <c r="I44" t="s">
-        <v>169</v>
-      </c>
-      <c r="J44" t="s">
-        <v>169</v>
-      </c>
-      <c r="M44" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>169</v>
-      </c>
-      <c r="B45" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" t="s">
-        <v>53</v>
-      </c>
-      <c r="D45" t="s">
-        <v>331</v>
-      </c>
-      <c r="E45" t="s">
-        <v>332</v>
-      </c>
-      <c r="G45" t="s">
-        <v>271</v>
-      </c>
-      <c r="I45" t="s">
-        <v>169</v>
-      </c>
-      <c r="J45" t="s">
-        <v>169</v>
-      </c>
-      <c r="M45" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>169</v>
-      </c>
-      <c r="B46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46" t="s">
-        <v>53</v>
-      </c>
-      <c r="D46" t="s">
-        <v>333</v>
-      </c>
-      <c r="E46" t="s">
-        <v>334</v>
-      </c>
-      <c r="G46" t="s">
-        <v>271</v>
-      </c>
-      <c r="I46" t="s">
-        <v>169</v>
-      </c>
-      <c r="J46" t="s">
-        <v>169</v>
-      </c>
-      <c r="M46" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>169</v>
-      </c>
-      <c r="B47" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" t="s">
-        <v>53</v>
-      </c>
-      <c r="D47" t="s">
-        <v>335</v>
-      </c>
-      <c r="E47" t="s">
-        <v>336</v>
-      </c>
-      <c r="G47" t="s">
-        <v>271</v>
-      </c>
-      <c r="I47" t="s">
-        <v>169</v>
-      </c>
-      <c r="J47" t="s">
-        <v>169</v>
-      </c>
-      <c r="M47" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>169</v>
-      </c>
-      <c r="B48" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" t="s">
-        <v>53</v>
-      </c>
-      <c r="D48" t="s">
-        <v>337</v>
-      </c>
-      <c r="E48" t="s">
-        <v>338</v>
-      </c>
-      <c r="G48" t="s">
-        <v>271</v>
-      </c>
-      <c r="I48" t="s">
-        <v>169</v>
-      </c>
-      <c r="J48" t="s">
-        <v>169</v>
-      </c>
-      <c r="M48" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>169</v>
-      </c>
-      <c r="B49" t="s">
-        <v>11</v>
-      </c>
-      <c r="C49" t="s">
-        <v>53</v>
-      </c>
-      <c r="D49" t="s">
-        <v>339</v>
-      </c>
-      <c r="E49" t="s">
-        <v>340</v>
-      </c>
-      <c r="G49" t="s">
-        <v>52</v>
-      </c>
-      <c r="I49" t="s">
-        <v>169</v>
-      </c>
-      <c r="J49" t="s">
-        <v>169</v>
-      </c>
-      <c r="M49" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>169</v>
-      </c>
-      <c r="B50" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" t="s">
-        <v>53</v>
-      </c>
-      <c r="D50" t="s">
-        <v>341</v>
-      </c>
-      <c r="E50" t="s">
-        <v>342</v>
-      </c>
-      <c r="G50" t="s">
-        <v>52</v>
-      </c>
-      <c r="I50" t="s">
-        <v>169</v>
-      </c>
-      <c r="J50" t="s">
-        <v>169</v>
-      </c>
-      <c r="M50" t="s">
-        <v>124</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -9213,44 +8746,28 @@
     <hyperlink ref="D2" r:id="rId1"/>
     <hyperlink ref="D3" r:id="rId2"/>
     <hyperlink ref="D4" r:id="rId3"/>
-    <hyperlink ref="D5" r:id="rId4"/>
-    <hyperlink ref="D6" r:id="rId5"/>
-    <hyperlink ref="D7" r:id="rId6"/>
-    <hyperlink ref="D8" r:id="rId7"/>
-    <hyperlink ref="D19" r:id="rId8"/>
-    <hyperlink ref="D20" r:id="rId9"/>
-    <hyperlink ref="D22" r:id="rId10"/>
-    <hyperlink ref="D23" r:id="rId11"/>
-    <hyperlink ref="D24" r:id="rId12"/>
-    <hyperlink ref="D25" r:id="rId13"/>
-    <hyperlink ref="D34" r:id="rId14"/>
-    <hyperlink ref="D35" r:id="rId15"/>
-    <hyperlink ref="D36" r:id="rId16"/>
-    <hyperlink ref="D37" r:id="rId17"/>
-    <hyperlink ref="D38" r:id="rId18"/>
-    <hyperlink ref="D40" r:id="rId19"/>
-    <hyperlink ref="D41" r:id="rId20"/>
-    <hyperlink ref="D42" r:id="rId21"/>
-    <hyperlink ref="D43" r:id="rId22"/>
-    <hyperlink ref="D44" r:id="rId23"/>
-    <hyperlink ref="D45" r:id="rId24"/>
-    <hyperlink ref="D46" r:id="rId25"/>
-    <hyperlink ref="D47" r:id="rId26"/>
-    <hyperlink ref="D48" r:id="rId27"/>
-    <hyperlink ref="D49" r:id="rId28"/>
-    <hyperlink ref="D50" r:id="rId29"/>
+    <hyperlink ref="D15" r:id="rId4"/>
+    <hyperlink ref="D17" r:id="rId5"/>
+    <hyperlink ref="D18" r:id="rId6"/>
+    <hyperlink ref="D19" r:id="rId7"/>
+    <hyperlink ref="D20" r:id="rId8"/>
+    <hyperlink ref="D29" r:id="rId9"/>
+    <hyperlink ref="D30" r:id="rId10"/>
+    <hyperlink ref="D31" r:id="rId11"/>
+    <hyperlink ref="D33" r:id="rId12"/>
+    <hyperlink ref="D34" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <tableParts count="1">
-    <tablePart r:id="rId30"/>
+    <tablePart r:id="rId14"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9304,7 +8821,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -9316,22 +8833,22 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F2" t="s">
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H2" t="s">
         <v>5</v>
       </c>
       <c r="I2" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="J2" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="K2" t="s">
         <v>5</v>
@@ -9342,7 +8859,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -9354,22 +8871,22 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F3" t="s">
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H3" t="s">
         <v>5</v>
       </c>
       <c r="I3" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="J3" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="K3" t="s">
         <v>5</v>
@@ -9380,7 +8897,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
@@ -9392,22 +8909,22 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
       </c>
       <c r="G4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H4" t="s">
         <v>5</v>
       </c>
       <c r="I4" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="J4" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="K4" t="s">
         <v>5</v>
@@ -9418,7 +8935,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -9430,22 +8947,22 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F5" t="s">
         <v>5</v>
       </c>
       <c r="G5" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H5" t="s">
         <v>5</v>
       </c>
       <c r="I5" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="J5" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="K5" t="s">
         <v>5</v>
@@ -9456,7 +8973,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
@@ -9468,22 +8985,22 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H6" t="s">
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="J6" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="K6" t="s">
         <v>5</v>
@@ -9494,7 +9011,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -9506,22 +9023,22 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H7" t="s">
         <v>5</v>
       </c>
       <c r="I7" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="J7" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="K7" t="s">
         <v>5</v>
@@ -9532,7 +9049,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -9544,22 +9061,22 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F8" t="s">
         <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H8" t="s">
         <v>5</v>
       </c>
       <c r="I8" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="J8" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="K8" t="s">
         <v>5</v>
@@ -9605,7 +9122,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
@@ -9617,22 +9134,22 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>347</v>
+        <v>318</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H10" t="s">
         <v>5</v>
       </c>
       <c r="I10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K10" t="s">
         <v>5</v>
@@ -9643,7 +9160,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
@@ -9661,16 +9178,16 @@
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
       </c>
       <c r="I11" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="J11" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="K11" t="s">
         <v>5</v>
@@ -9681,7 +9198,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>349</v>
+        <v>320</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -9693,19 +9210,19 @@
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>350</v>
+        <v>321</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
       </c>
       <c r="G12" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H12" t="s">
         <v>5</v>
       </c>
       <c r="I12" t="s">
-        <v>349</v>
+        <v>320</v>
       </c>
       <c r="J12" t="s">
         <v>51</v>
@@ -9719,7 +9236,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -9731,22 +9248,22 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
       </c>
       <c r="G13" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H13" t="s">
         <v>5</v>
       </c>
       <c r="I13" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="J13" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="K13" t="s">
         <v>5</v>
@@ -9757,7 +9274,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -9769,22 +9286,22 @@
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="F14">
         <v>-0.5</v>
       </c>
       <c r="G14" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H14" t="s">
         <v>5</v>
       </c>
       <c r="I14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
@@ -9795,7 +9312,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
@@ -9807,22 +9324,22 @@
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>351</v>
+        <v>322</v>
       </c>
       <c r="F15" t="s">
         <v>5</v>
       </c>
       <c r="G15" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H15" t="s">
         <v>5</v>
       </c>
       <c r="I15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K15" t="s">
         <v>5</v>
@@ -9833,7 +9350,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
@@ -9845,22 +9362,22 @@
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>352</v>
+        <v>323</v>
       </c>
       <c r="F16" t="s">
         <v>5</v>
       </c>
       <c r="G16" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H16" t="s">
         <v>5</v>
       </c>
       <c r="I16" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="J16" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -9871,7 +9388,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
@@ -9883,22 +9400,22 @@
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="F17">
         <v>-0.5</v>
       </c>
       <c r="G17" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H17" t="s">
         <v>5</v>
       </c>
       <c r="I17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
@@ -9909,7 +9426,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
@@ -9921,22 +9438,22 @@
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="F18" t="s">
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H18" t="s">
         <v>5</v>
       </c>
       <c r="I18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
@@ -9959,13 +9476,13 @@
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>354</v>
+        <v>325</v>
       </c>
       <c r="F19" t="s">
         <v>5</v>
       </c>
       <c r="G19" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H19" t="s">
         <v>5</v>
@@ -9974,7 +9491,7 @@
         <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
@@ -9985,7 +9502,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
@@ -9997,22 +9514,22 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="F20" t="s">
         <v>5</v>
       </c>
       <c r="G20" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H20" t="s">
         <v>5</v>
       </c>
       <c r="I20" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="J20" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
@@ -10023,7 +9540,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -10035,22 +9552,22 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="F21" t="s">
         <v>5</v>
       </c>
       <c r="G21" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H21" t="s">
         <v>5</v>
       </c>
       <c r="I21" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J21" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
@@ -10073,13 +9590,13 @@
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="F22" t="s">
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H22" t="s">
         <v>5</v>
@@ -10088,7 +9605,7 @@
         <v>51</v>
       </c>
       <c r="J22" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="K22" t="s">
         <v>5</v>
@@ -10099,7 +9616,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
@@ -10111,22 +9628,22 @@
         <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="F23">
         <v>-6</v>
       </c>
       <c r="G23" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H23" t="s">
         <v>5</v>
       </c>
       <c r="I23" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J23" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K23" t="s">
         <v>5</v>
@@ -10149,13 +9666,13 @@
         <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="F24" t="s">
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H24" t="s">
         <v>5</v>
@@ -10187,13 +9704,13 @@
         <v>5</v>
       </c>
       <c r="E25" t="s">
-        <v>361</v>
+        <v>332</v>
       </c>
       <c r="F25" t="s">
         <v>5</v>
       </c>
       <c r="G25" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H25" t="s">
         <v>5</v>
@@ -10213,7 +9730,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
@@ -10225,22 +9742,22 @@
         <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>362</v>
+        <v>333</v>
       </c>
       <c r="F26" t="s">
         <v>5</v>
       </c>
       <c r="G26" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H26" t="s">
         <v>5</v>
       </c>
       <c r="I26" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J26" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
@@ -10251,7 +9768,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
@@ -10263,22 +9780,22 @@
         <v>5</v>
       </c>
       <c r="E27" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="F27" t="s">
         <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H27" t="s">
         <v>5</v>
       </c>
       <c r="I27" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J27" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
@@ -10289,7 +9806,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B28" t="s">
         <v>6</v>
@@ -10301,22 +9818,22 @@
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>364</v>
+        <v>335</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
       </c>
       <c r="G28" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H28" t="s">
         <v>5</v>
       </c>
       <c r="I28" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
@@ -10327,7 +9844,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
@@ -10339,22 +9856,22 @@
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="F29" t="s">
         <v>5</v>
       </c>
       <c r="G29" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H29" t="s">
         <v>5</v>
       </c>
       <c r="I29" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="J29" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="K29" t="s">
         <v>5</v>
@@ -10365,7 +9882,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B30" t="s">
         <v>6</v>
@@ -10383,16 +9900,16 @@
         <v>5</v>
       </c>
       <c r="G30" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H30" t="s">
         <v>5</v>
       </c>
       <c r="I30" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J30" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
@@ -10403,7 +9920,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B31" t="s">
         <v>3</v>
@@ -10415,22 +9932,22 @@
         <v>5</v>
       </c>
       <c r="E31" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F31" t="s">
         <v>5</v>
       </c>
       <c r="G31" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H31" t="s">
         <v>5</v>
       </c>
       <c r="I31" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J31" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
@@ -10441,7 +9958,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>349</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
@@ -10453,19 +9970,19 @@
         <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>350</v>
+        <v>321</v>
       </c>
       <c r="F32" t="s">
         <v>5</v>
       </c>
       <c r="G32" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H32" t="s">
         <v>5</v>
       </c>
       <c r="I32" t="s">
-        <v>349</v>
+        <v>320</v>
       </c>
       <c r="J32" t="s">
         <v>51</v>
@@ -10497,7 +10014,7 @@
         <v>5</v>
       </c>
       <c r="G33" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H33" t="s">
         <v>5</v>
@@ -10506,7 +10023,7 @@
         <v>268</v>
       </c>
       <c r="J33" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
@@ -10517,7 +10034,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
@@ -10529,22 +10046,22 @@
         <v>5</v>
       </c>
       <c r="E34" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F34">
         <v>-4</v>
       </c>
       <c r="G34" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H34" t="s">
         <v>5</v>
       </c>
       <c r="I34" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J34" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
@@ -10555,7 +10072,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B35" t="s">
         <v>8</v>
@@ -10567,22 +10084,22 @@
         <v>5</v>
       </c>
       <c r="E35" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="F35">
         <v>-4</v>
       </c>
       <c r="G35" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H35" t="s">
         <v>5</v>
       </c>
       <c r="I35" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J35" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K35" t="s">
         <v>5</v>
@@ -10593,7 +10110,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
@@ -10611,16 +10128,16 @@
         <v>-2</v>
       </c>
       <c r="G36" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H36" t="s">
         <v>5</v>
       </c>
       <c r="I36" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J36" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K36" t="s">
         <v>5</v>
@@ -10631,7 +10148,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
@@ -10643,22 +10160,22 @@
         <v>5</v>
       </c>
       <c r="E37" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="F37">
         <v>-2</v>
       </c>
       <c r="G37" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H37" t="s">
         <v>5</v>
       </c>
       <c r="I37" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J37" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K37" t="s">
         <v>5</v>
@@ -10681,13 +10198,13 @@
         <v>5</v>
       </c>
       <c r="E38" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F38">
         <v>-2</v>
       </c>
       <c r="G38" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H38" t="s">
         <v>5</v>
@@ -10719,13 +10236,13 @@
         <v>5</v>
       </c>
       <c r="E39" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="F39">
         <v>-4</v>
       </c>
       <c r="G39" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H39" t="s">
         <v>5</v>
@@ -10757,13 +10274,13 @@
         <v>5</v>
       </c>
       <c r="E40" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F40">
         <v>-2</v>
       </c>
       <c r="G40" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H40" t="s">
         <v>5</v>
@@ -10783,7 +10300,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B41" t="s">
         <v>8</v>
@@ -10795,22 +10312,22 @@
         <v>5</v>
       </c>
       <c r="E41" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="F41">
         <v>-2</v>
       </c>
       <c r="G41" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H41" t="s">
         <v>5</v>
       </c>
       <c r="I41" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J41" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K41" t="s">
         <v>5</v>
@@ -10821,7 +10338,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -10833,22 +10350,22 @@
         <v>5</v>
       </c>
       <c r="E42" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="F42">
         <v>-4</v>
       </c>
       <c r="G42" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H42" t="s">
         <v>5</v>
       </c>
       <c r="I42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K42" t="s">
         <v>5</v>
@@ -10859,7 +10376,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s">
         <v>11</v>
@@ -10871,22 +10388,22 @@
         <v>5</v>
       </c>
       <c r="E43" t="s">
-        <v>365</v>
+        <v>336</v>
       </c>
       <c r="F43" t="s">
         <v>5</v>
       </c>
       <c r="G43" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H43" t="s">
         <v>5</v>
       </c>
       <c r="I43" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="J43" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="K43" t="s">
         <v>5</v>
@@ -10897,7 +10414,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
@@ -10909,22 +10426,22 @@
         <v>5</v>
       </c>
       <c r="E44" t="s">
-        <v>366</v>
+        <v>337</v>
       </c>
       <c r="F44" t="s">
         <v>5</v>
       </c>
       <c r="G44" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H44" t="s">
         <v>5</v>
       </c>
       <c r="I44" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="J44" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="K44" t="s">
         <v>5</v>
@@ -10935,7 +10452,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
@@ -10947,22 +10464,22 @@
         <v>5</v>
       </c>
       <c r="E45" t="s">
-        <v>368</v>
+        <v>339</v>
       </c>
       <c r="F45" t="s">
         <v>5</v>
       </c>
       <c r="G45" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H45" t="s">
         <v>5</v>
       </c>
       <c r="I45" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="J45" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="K45" t="s">
         <v>5</v>
@@ -10973,7 +10490,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="B46" t="s">
         <v>11</v>
@@ -10985,22 +10502,22 @@
         <v>5</v>
       </c>
       <c r="E46" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="F46" t="s">
         <v>5</v>
       </c>
       <c r="G46" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H46" t="s">
         <v>5</v>
       </c>
       <c r="I46" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="J46" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="K46" t="s">
         <v>5</v>
@@ -11011,7 +10528,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
@@ -11023,22 +10540,22 @@
         <v>5</v>
       </c>
       <c r="E47" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="F47" t="s">
         <v>5</v>
       </c>
       <c r="G47" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H47" t="s">
         <v>5</v>
       </c>
       <c r="I47" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="J47" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="K47" t="s">
         <v>5</v>
@@ -11049,7 +10566,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="B48" t="s">
         <v>11</v>
@@ -11061,22 +10578,22 @@
         <v>5</v>
       </c>
       <c r="E48" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="F48" t="s">
         <v>5</v>
       </c>
       <c r="G48" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H48" t="s">
         <v>5</v>
       </c>
       <c r="I48" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="J48" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="K48" t="s">
         <v>5</v>
@@ -11087,7 +10604,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
@@ -11099,22 +10616,22 @@
         <v>5</v>
       </c>
       <c r="E49" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="F49" t="s">
         <v>5</v>
       </c>
       <c r="G49" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H49" t="s">
         <v>5</v>
       </c>
       <c r="I49" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="J49" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
@@ -11125,7 +10642,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="B50" t="s">
         <v>11</v>
@@ -11137,22 +10654,22 @@
         <v>5</v>
       </c>
       <c r="E50" t="s">
-        <v>373</v>
+        <v>344</v>
       </c>
       <c r="F50" t="s">
         <v>5</v>
       </c>
       <c r="G50" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H50" t="s">
         <v>5</v>
       </c>
       <c r="I50" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="J50" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="K50" t="s">
         <v>5</v>
@@ -11163,7 +10680,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="B51" t="s">
         <v>11</v>
@@ -11175,22 +10692,22 @@
         <v>5</v>
       </c>
       <c r="E51" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="F51" t="s">
         <v>5</v>
       </c>
       <c r="G51" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H51" t="s">
         <v>5</v>
       </c>
       <c r="I51" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="J51" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
@@ -11213,28 +10730,552 @@
         <v>5</v>
       </c>
       <c r="E52" t="s">
+        <v>346</v>
+      </c>
+      <c r="F52" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" t="s">
+        <v>277</v>
+      </c>
+      <c r="H52" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" t="s">
+        <v>5</v>
+      </c>
+      <c r="L52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>268</v>
+      </c>
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" t="s">
+        <v>59</v>
+      </c>
+      <c r="D53" t="s">
+        <v>347</v>
+      </c>
+      <c r="E53" t="s">
+        <v>348</v>
+      </c>
+      <c r="F53" t="s">
+        <v>5</v>
+      </c>
+      <c r="G53" t="s">
+        <v>52</v>
+      </c>
+      <c r="H53" t="s">
+        <v>5</v>
+      </c>
+      <c r="I53" t="s">
+        <v>268</v>
+      </c>
+      <c r="J53" t="s">
+        <v>268</v>
+      </c>
+      <c r="K53" t="s">
+        <v>5</v>
+      </c>
+      <c r="L53" t="s">
+        <v>5</v>
+      </c>
+      <c r="M53" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>268</v>
+      </c>
+      <c r="B54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" t="s">
+        <v>59</v>
+      </c>
+      <c r="D54" t="s">
+        <v>349</v>
+      </c>
+      <c r="E54" t="s">
+        <v>164</v>
+      </c>
+      <c r="F54" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" t="s">
+        <v>52</v>
+      </c>
+      <c r="H54" t="s">
+        <v>5</v>
+      </c>
+      <c r="I54" t="s">
+        <v>268</v>
+      </c>
+      <c r="J54" t="s">
+        <v>268</v>
+      </c>
+      <c r="K54" t="s">
+        <v>5</v>
+      </c>
+      <c r="L54" t="s">
+        <v>5</v>
+      </c>
+      <c r="M54" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>273</v>
+      </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>59</v>
+      </c>
+      <c r="D55" t="s">
+        <v>350</v>
+      </c>
+      <c r="E55" t="s">
+        <v>351</v>
+      </c>
+      <c r="F55" t="s">
+        <v>5</v>
+      </c>
+      <c r="G55" t="s">
+        <v>52</v>
+      </c>
+      <c r="H55" t="s">
+        <v>5</v>
+      </c>
+      <c r="I55" t="s">
+        <v>273</v>
+      </c>
+      <c r="J55" t="s">
+        <v>273</v>
+      </c>
+      <c r="K55" t="s">
+        <v>5</v>
+      </c>
+      <c r="L55" t="s">
+        <v>5</v>
+      </c>
+      <c r="M55" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>297</v>
+      </c>
+      <c r="B56" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" t="s">
+        <v>59</v>
+      </c>
+      <c r="D56" t="s">
+        <v>352</v>
+      </c>
+      <c r="E56" t="s">
+        <v>353</v>
+      </c>
+      <c r="F56" t="s">
+        <v>5</v>
+      </c>
+      <c r="G56" t="s">
+        <v>52</v>
+      </c>
+      <c r="H56" t="s">
+        <v>5</v>
+      </c>
+      <c r="I56" t="s">
+        <v>297</v>
+      </c>
+      <c r="J56" t="s">
+        <v>297</v>
+      </c>
+      <c r="K56" t="s">
+        <v>5</v>
+      </c>
+      <c r="L56" t="s">
+        <v>5</v>
+      </c>
+      <c r="M56" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>185</v>
+      </c>
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" t="s">
+        <v>59</v>
+      </c>
+      <c r="D57" t="s">
+        <v>354</v>
+      </c>
+      <c r="E57" t="s">
+        <v>247</v>
+      </c>
+      <c r="F57" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" t="s">
+        <v>52</v>
+      </c>
+      <c r="H57" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" t="s">
+        <v>185</v>
+      </c>
+      <c r="J57" t="s">
+        <v>185</v>
+      </c>
+      <c r="K57" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" t="s">
+        <v>5</v>
+      </c>
+      <c r="M57" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>169</v>
+      </c>
+      <c r="B58" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" t="s">
+        <v>59</v>
+      </c>
+      <c r="D58" t="s">
+        <v>355</v>
+      </c>
+      <c r="E58" t="s">
+        <v>356</v>
+      </c>
+      <c r="G58" t="s">
+        <v>52</v>
+      </c>
+      <c r="I58" t="s">
+        <v>169</v>
+      </c>
+      <c r="J58" t="s">
+        <v>169</v>
+      </c>
+      <c r="M58" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>169</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" t="s">
+        <v>59</v>
+      </c>
+      <c r="D59" t="s">
+        <v>357</v>
+      </c>
+      <c r="E59" t="s">
+        <v>358</v>
+      </c>
+      <c r="G59" t="s">
+        <v>52</v>
+      </c>
+      <c r="I59" t="s">
+        <v>169</v>
+      </c>
+      <c r="J59" t="s">
+        <v>169</v>
+      </c>
+      <c r="M59" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>169</v>
+      </c>
+      <c r="B60" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" t="s">
+        <v>59</v>
+      </c>
+      <c r="D60" t="s">
+        <v>359</v>
+      </c>
+      <c r="E60" t="s">
+        <v>360</v>
+      </c>
+      <c r="G60" t="s">
+        <v>52</v>
+      </c>
+      <c r="I60" t="s">
+        <v>169</v>
+      </c>
+      <c r="J60" t="s">
+        <v>169</v>
+      </c>
+      <c r="M60" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>169</v>
+      </c>
+      <c r="B61" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" t="s">
+        <v>59</v>
+      </c>
+      <c r="D61" t="s">
+        <v>361</v>
+      </c>
+      <c r="E61" t="s">
+        <v>362</v>
+      </c>
+      <c r="G61" t="s">
+        <v>52</v>
+      </c>
+      <c r="I61" t="s">
+        <v>169</v>
+      </c>
+      <c r="J61" t="s">
+        <v>169</v>
+      </c>
+      <c r="M61" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>169</v>
+      </c>
+      <c r="B62" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" t="s">
+        <v>59</v>
+      </c>
+      <c r="D62" t="s">
+        <v>363</v>
+      </c>
+      <c r="E62" t="s">
+        <v>364</v>
+      </c>
+      <c r="G62" t="s">
+        <v>52</v>
+      </c>
+      <c r="I62" t="s">
+        <v>169</v>
+      </c>
+      <c r="J62" t="s">
+        <v>169</v>
+      </c>
+      <c r="M62" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>169</v>
+      </c>
+      <c r="B63" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" t="s">
+        <v>59</v>
+      </c>
+      <c r="D63" t="s">
+        <v>365</v>
+      </c>
+      <c r="E63" t="s">
+        <v>366</v>
+      </c>
+      <c r="G63" t="s">
+        <v>52</v>
+      </c>
+      <c r="I63" t="s">
+        <v>169</v>
+      </c>
+      <c r="J63" t="s">
+        <v>169</v>
+      </c>
+      <c r="M63" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>169</v>
+      </c>
+      <c r="B64" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" t="s">
+        <v>59</v>
+      </c>
+      <c r="D64" t="s">
+        <v>367</v>
+      </c>
+      <c r="E64" t="s">
+        <v>368</v>
+      </c>
+      <c r="G64" t="s">
+        <v>52</v>
+      </c>
+      <c r="I64" t="s">
+        <v>169</v>
+      </c>
+      <c r="J64" t="s">
+        <v>169</v>
+      </c>
+      <c r="M64" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>169</v>
+      </c>
+      <c r="B65" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" t="s">
+        <v>59</v>
+      </c>
+      <c r="D65" t="s">
+        <v>369</v>
+      </c>
+      <c r="E65" t="s">
+        <v>370</v>
+      </c>
+      <c r="G65" t="s">
+        <v>52</v>
+      </c>
+      <c r="I65" t="s">
+        <v>169</v>
+      </c>
+      <c r="J65" t="s">
+        <v>169</v>
+      </c>
+      <c r="M65" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>169</v>
+      </c>
+      <c r="B66" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" t="s">
+        <v>59</v>
+      </c>
+      <c r="D66" t="s">
+        <v>371</v>
+      </c>
+      <c r="E66" t="s">
+        <v>372</v>
+      </c>
+      <c r="G66" t="s">
+        <v>52</v>
+      </c>
+      <c r="I66" t="s">
+        <v>169</v>
+      </c>
+      <c r="J66" t="s">
+        <v>169</v>
+      </c>
+      <c r="M66" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>169</v>
+      </c>
+      <c r="B67" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" t="s">
+        <v>59</v>
+      </c>
+      <c r="D67" t="s">
+        <v>373</v>
+      </c>
+      <c r="E67" t="s">
+        <v>374</v>
+      </c>
+      <c r="G67" t="s">
+        <v>52</v>
+      </c>
+      <c r="I67" t="s">
+        <v>169</v>
+      </c>
+      <c r="J67" t="s">
+        <v>169</v>
+      </c>
+      <c r="M67" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>169</v>
+      </c>
+      <c r="B68" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" t="s">
+        <v>59</v>
+      </c>
+      <c r="D68" t="s">
         <v>375</v>
       </c>
-      <c r="F52" t="s">
-        <v>5</v>
-      </c>
-      <c r="G52" t="s">
-        <v>271</v>
-      </c>
-      <c r="H52" t="s">
-        <v>5</v>
-      </c>
-      <c r="I52" t="s">
-        <v>5</v>
-      </c>
-      <c r="J52" t="s">
-        <v>5</v>
-      </c>
-      <c r="K52" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" t="s">
-        <v>5</v>
+      <c r="E68" t="s">
+        <v>376</v>
+      </c>
+      <c r="G68" t="s">
+        <v>52</v>
+      </c>
+      <c r="I68" t="s">
+        <v>169</v>
+      </c>
+      <c r="J68" t="s">
+        <v>169</v>
+      </c>
+      <c r="M68" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -11268,10 +11309,28 @@
       <formula2>49673.77083333333</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="D53" r:id="rId1"/>
+    <hyperlink ref="D54" r:id="rId2"/>
+    <hyperlink ref="D55" r:id="rId3"/>
+    <hyperlink ref="D56" r:id="rId4"/>
+    <hyperlink ref="D57" r:id="rId5"/>
+    <hyperlink ref="D58" r:id="rId6"/>
+    <hyperlink ref="D59" r:id="rId7"/>
+    <hyperlink ref="D60" r:id="rId8"/>
+    <hyperlink ref="D61" r:id="rId9"/>
+    <hyperlink ref="D62" r:id="rId10"/>
+    <hyperlink ref="D63" r:id="rId11"/>
+    <hyperlink ref="D64" r:id="rId12"/>
+    <hyperlink ref="D65" r:id="rId13"/>
+    <hyperlink ref="D66" r:id="rId14"/>
+    <hyperlink ref="D67" r:id="rId15"/>
+    <hyperlink ref="D68" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId17"/>
   </tableParts>
 </worksheet>
 </file>